--- a/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,6 +447,11 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>aggregates_standardized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>multifunctionality</t>
         </is>
       </c>
@@ -511,7 +516,10 @@
         <v>0.3095837336681162</v>
       </c>
       <c r="S2">
-        <v>0.4215383554812951</v>
+        <v>0.5329067273494283</v>
+      </c>
+      <c r="T2">
+        <v>0.4354594019648118</v>
       </c>
     </row>
     <row r="3">
@@ -574,7 +582,10 @@
         <v>0.4538193710537792</v>
       </c>
       <c r="S3">
-        <v>0.461066545030265</v>
+        <v>0.5349234617545326</v>
+      </c>
+      <c r="T3">
+        <v>0.4702986596207985</v>
       </c>
     </row>
     <row r="4">
@@ -637,7 +648,10 @@
         <v>0.1763512235540355</v>
       </c>
       <c r="S4">
-        <v>0.3714098387163036</v>
+        <v>0.3687207077501685</v>
+      </c>
+      <c r="T4">
+        <v>0.3710736973455367</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +714,10 @@
         <v>0.2901661958320036</v>
       </c>
       <c r="S5">
-        <v>0.4200355115336585</v>
+        <v>0.9078847592894224</v>
+      </c>
+      <c r="T5">
+        <v>0.4810166675031289</v>
       </c>
     </row>
     <row r="6">
@@ -763,7 +780,10 @@
         <v>0.08272192028282797</v>
       </c>
       <c r="S6">
-        <v>0.319465497888607</v>
+        <v>0.8102154638078963</v>
+      </c>
+      <c r="T6">
+        <v>0.3808092436285181</v>
       </c>
     </row>
     <row r="7">
@@ -826,7 +846,10 @@
         <v>0.6061769173633896</v>
       </c>
       <c r="S7">
-        <v>0.4987447381356599</v>
+        <v>0.6360493681792212</v>
+      </c>
+      <c r="T7">
+        <v>0.5159078168911051</v>
       </c>
     </row>
     <row r="8">
@@ -889,7 +912,10 @@
         <v>0.1482407307513151</v>
       </c>
       <c r="S8">
-        <v>0.3487925912606095</v>
+        <v>0.577888345759738</v>
+      </c>
+      <c r="T8">
+        <v>0.3774295605730006</v>
       </c>
     </row>
     <row r="9">
@@ -952,7 +978,10 @@
         <v>0.3666128102901184</v>
       </c>
       <c r="S9">
-        <v>0.3021566695904399</v>
+        <v>0.5269623043811215</v>
+      </c>
+      <c r="T9">
+        <v>0.3302573739392751</v>
       </c>
     </row>
     <row r="10">
@@ -1015,7 +1044,10 @@
         <v>0.6466931295555873</v>
       </c>
       <c r="S10">
-        <v>0.5032935955932154</v>
+        <v>0.6286899729640903</v>
+      </c>
+      <c r="T10">
+        <v>0.5189681427645747</v>
       </c>
     </row>
     <row r="11">
@@ -1078,7 +1110,10 @@
         <v>0.3387981378390733</v>
       </c>
       <c r="S11">
-        <v>0.4091025520582937</v>
+        <v>0.5786033147410633</v>
+      </c>
+      <c r="T11">
+        <v>0.4302901473936399</v>
       </c>
     </row>
     <row r="12">
@@ -1141,7 +1176,10 @@
         <v>0.3231240314170564</v>
       </c>
       <c r="S12">
-        <v>0.3958902404124733</v>
+        <v>0.5881104701166693</v>
+      </c>
+      <c r="T12">
+        <v>0.4199177691254978</v>
       </c>
     </row>
     <row r="13">
@@ -1204,7 +1242,10 @@
         <v>0.3613628349666473</v>
       </c>
       <c r="S13">
-        <v>0.5484006910517366</v>
+        <v>0.3967074045852518</v>
+      </c>
+      <c r="T13">
+        <v>0.529439030243426</v>
       </c>
     </row>
     <row r="14">
@@ -1267,7 +1308,10 @@
         <v>0.002517386384649483</v>
       </c>
       <c r="S14">
-        <v>0.298051522927981</v>
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>0.3857950825619834</v>
       </c>
     </row>
     <row r="15">
@@ -1330,7 +1374,10 @@
         <v>0.1189272518667831</v>
       </c>
       <c r="S15">
-        <v>0.3095558292734193</v>
+        <v>0.5991571254558291</v>
+      </c>
+      <c r="T15">
+        <v>0.3457559912962205</v>
       </c>
     </row>
     <row r="16">
@@ -1393,7 +1440,10 @@
         <v>0.2433418210541713</v>
       </c>
       <c r="S16">
-        <v>0.375977908180847</v>
+        <v>0.615833348345295</v>
+      </c>
+      <c r="T16">
+        <v>0.405959838201403</v>
       </c>
     </row>
     <row r="17">
@@ -1456,7 +1506,10 @@
         <v>0.1278675422350279</v>
       </c>
       <c r="S17">
-        <v>0.1183432708789298</v>
+        <v>0.682795362548585</v>
+      </c>
+      <c r="T17">
+        <v>0.1888997823376367</v>
       </c>
     </row>
     <row r="18">
@@ -1519,7 +1572,10 @@
         <v>0.3653087018938461</v>
       </c>
       <c r="S18">
-        <v>0.4120185846105838</v>
+        <v>0.5691113227775285</v>
+      </c>
+      <c r="T18">
+        <v>0.4316551768814519</v>
       </c>
     </row>
     <row r="19">
@@ -1582,7 +1638,10 @@
         <v>0.6147991208738268</v>
       </c>
       <c r="S19">
-        <v>0.5782873719661964</v>
+        <v>0.4762697184401813</v>
+      </c>
+      <c r="T19">
+        <v>0.5655351652754445</v>
       </c>
     </row>
     <row r="20">
@@ -1645,7 +1704,10 @@
         <v>0.1830304771246527</v>
       </c>
       <c r="S20">
-        <v>0.3895929896831656</v>
+        <v>0.6169762430128304</v>
+      </c>
+      <c r="T20">
+        <v>0.4180158963493737</v>
       </c>
     </row>
     <row r="21">
@@ -1702,7 +1764,10 @@
         <v>0.8143839706609451</v>
       </c>
       <c r="S21">
-        <v>0.6309851173440358</v>
+        <v>0.5893605834780353</v>
+      </c>
+      <c r="T21">
+        <v>0.6250387553631787</v>
       </c>
     </row>
     <row r="22">
@@ -1765,7 +1830,10 @@
         <v>0.8229340500243738</v>
       </c>
       <c r="S22">
-        <v>0.4736896553045229</v>
+        <v>0.6145812357572692</v>
+      </c>
+      <c r="T22">
+        <v>0.4913011028611162</v>
       </c>
     </row>
     <row r="23">
@@ -1822,7 +1890,10 @@
         <v>0.1568873000010577</v>
       </c>
       <c r="S23">
-        <v>0.4483794930373389</v>
+        <v>0.5996922527986955</v>
+      </c>
+      <c r="T23">
+        <v>0.4699956015746756</v>
       </c>
     </row>
     <row r="24">
@@ -1879,7 +1950,10 @@
         <v>0.8162800998680531</v>
       </c>
       <c r="S24">
-        <v>0.5722136263462111</v>
+        <v>0.5801183710685277</v>
+      </c>
+      <c r="T24">
+        <v>0.5733428755922564</v>
       </c>
     </row>
     <row r="25">
@@ -1942,7 +2016,10 @@
         <v>0.08751634375215032</v>
       </c>
       <c r="S25">
-        <v>0.1760775769717749</v>
+        <v>0.6829831089609784</v>
+      </c>
+      <c r="T25">
+        <v>0.2394407684704253</v>
       </c>
     </row>
     <row r="26">
@@ -1999,7 +2076,10 @@
         <v>0.04932251807502108</v>
       </c>
       <c r="S26">
-        <v>0.3217579071990413</v>
+        <v>0.6188409714365701</v>
+      </c>
+      <c r="T26">
+        <v>0.3641983449472598</v>
       </c>
     </row>
     <row r="27">
@@ -2062,7 +2142,10 @@
         <v>0.3079124135096388</v>
       </c>
       <c r="S27">
-        <v>0.3690674449274484</v>
+        <v>0.594763872245282</v>
+      </c>
+      <c r="T27">
+        <v>0.3972794983421776</v>
       </c>
     </row>
     <row r="28">
@@ -2125,7 +2208,10 @@
         <v>0.09284481701469087</v>
       </c>
       <c r="S28">
-        <v>0.2894265316858725</v>
+        <v>0.6533281703868384</v>
+      </c>
+      <c r="T28">
+        <v>0.3349142365234932</v>
       </c>
     </row>
     <row r="29">
@@ -2188,7 +2274,10 @@
         <v>0.1793228053399155</v>
       </c>
       <c r="S29">
-        <v>0.3485964784999393</v>
+        <v>0.5774938934128605</v>
+      </c>
+      <c r="T29">
+        <v>0.3772086553640545</v>
       </c>
     </row>
     <row r="30">
@@ -2251,7 +2340,10 @@
         <v>0.4399859346834002</v>
       </c>
       <c r="S30">
-        <v>0.5371555782105024</v>
+        <v>0.5989790510914346</v>
+      </c>
+      <c r="T30">
+        <v>0.5448835123206189</v>
       </c>
     </row>
     <row r="31">
@@ -2314,7 +2406,10 @@
         <v>0.4377780342244889</v>
       </c>
       <c r="S31">
-        <v>0.3895586931085155</v>
+        <v>0.6415004625970644</v>
+      </c>
+      <c r="T31">
+        <v>0.4210514142945841</v>
       </c>
     </row>
     <row r="32">
@@ -2377,7 +2472,10 @@
         <v>0.2110482135820394</v>
       </c>
       <c r="S32">
-        <v>0.2687839258169726</v>
+        <v>0.5975978979229554</v>
+      </c>
+      <c r="T32">
+        <v>0.3098856723302205</v>
       </c>
     </row>
     <row r="33">
@@ -2440,7 +2538,10 @@
         <v>0.3361594147792935</v>
       </c>
       <c r="S33">
-        <v>0.4281838905949807</v>
+        <v>0.6409674193251149</v>
+      </c>
+      <c r="T33">
+        <v>0.4547818316862475</v>
       </c>
     </row>
     <row r="34">
@@ -2503,7 +2604,10 @@
         <v>0.02281253493604877</v>
       </c>
       <c r="S34">
-        <v>0.2616042244028842</v>
+        <v>0.3878842490321296</v>
+      </c>
+      <c r="T34">
+        <v>0.2773892274815399</v>
       </c>
     </row>
     <row r="35">
@@ -2566,7 +2670,10 @@
         <v>0.4403286329702006</v>
       </c>
       <c r="S35">
-        <v>0.4006417470947832</v>
+        <v>0.6126968147045188</v>
+      </c>
+      <c r="T35">
+        <v>0.4271486305460002</v>
       </c>
     </row>
     <row r="36">
@@ -2629,7 +2736,10 @@
         <v>0.2038430837769933</v>
       </c>
       <c r="S36">
-        <v>0.4486538802880188</v>
+        <v>0.6403530622123499</v>
+      </c>
+      <c r="T36">
+        <v>0.4726162780285602</v>
       </c>
     </row>
     <row r="37">
@@ -2692,7 +2802,10 @@
         <v>0.3251364505456744</v>
       </c>
       <c r="S37">
-        <v>0.4099779743254381</v>
+        <v>0.478776788243877</v>
+      </c>
+      <c r="T37">
+        <v>0.418577826065243</v>
       </c>
     </row>
     <row r="38">
@@ -2755,7 +2868,10 @@
         <v>0.2229649301928028</v>
       </c>
       <c r="S38">
-        <v>0.3488303025754664</v>
+        <v>0.661139318763453</v>
+      </c>
+      <c r="T38">
+        <v>0.3878689295989648</v>
       </c>
     </row>
     <row r="39">
@@ -2818,7 +2934,10 @@
         <v>0.1701929791078292</v>
       </c>
       <c r="S39">
-        <v>0.3341591780469724</v>
+        <v>0.6305161911917418</v>
+      </c>
+      <c r="T39">
+        <v>0.3712038046900686</v>
       </c>
     </row>
     <row r="40">
@@ -2881,7 +3000,10 @@
         <v>0.5211469907343621</v>
       </c>
       <c r="S40">
-        <v>0.5250723730321312</v>
+        <v>0.596078955458171</v>
+      </c>
+      <c r="T40">
+        <v>0.5339481958353862</v>
       </c>
     </row>
     <row r="41">
@@ -2944,7 +3066,10 @@
         <v>0.2964707187646027</v>
       </c>
       <c r="S41">
-        <v>0.5061434004910446</v>
+        <v>0.5826263751744765</v>
+      </c>
+      <c r="T41">
+        <v>0.5157037723264736</v>
       </c>
     </row>
     <row r="42">
@@ -3007,7 +3132,10 @@
         <v>0.4002046585006649</v>
       </c>
       <c r="S42">
-        <v>0.3443488695797177</v>
+        <v>0.566614599603148</v>
+      </c>
+      <c r="T42">
+        <v>0.3721320858326465</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3198,10 @@
         <v>0.05414792544086373</v>
       </c>
       <c r="S43">
-        <v>0.2303245849802084</v>
+        <v>0.6222562924529285</v>
+      </c>
+      <c r="T43">
+        <v>0.2793160484142984</v>
       </c>
     </row>
     <row r="44">
@@ -3133,7 +3264,10 @@
         <v>0.07146602998081229</v>
       </c>
       <c r="S44">
-        <v>0.3760480913452198</v>
+        <v>0.6336020089526978</v>
+      </c>
+      <c r="T44">
+        <v>0.4082423310461546</v>
       </c>
     </row>
     <row r="45">
@@ -3190,7 +3324,10 @@
         <v>0.3260096735872604</v>
       </c>
       <c r="S45">
-        <v>0.3705408723423639</v>
+        <v>0.6118374938834623</v>
+      </c>
+      <c r="T45">
+        <v>0.4050118182768065</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3390,10 @@
         <v>0.4464741142412194</v>
       </c>
       <c r="S46">
-        <v>0.4589732600294871</v>
+        <v>0.6743730996497096</v>
+      </c>
+      <c r="T46">
+        <v>0.4858982399820149</v>
       </c>
     </row>
     <row r="47">
@@ -3310,7 +3450,10 @@
         <v>0.2936587098507883</v>
       </c>
       <c r="S47">
-        <v>0.5314320335060397</v>
+        <v>0.6555409651319281</v>
+      </c>
+      <c r="T47">
+        <v>0.5491618808811666</v>
       </c>
     </row>
     <row r="48">
@@ -3373,7 +3516,10 @@
         <v>0.2983419634079955</v>
       </c>
       <c r="S48">
-        <v>0.4882217154607995</v>
+        <v>0.6109316377023839</v>
+      </c>
+      <c r="T48">
+        <v>0.5035604557409975</v>
       </c>
     </row>
     <row r="49">
@@ -3430,7 +3576,10 @@
         <v>0.1059915160799036</v>
       </c>
       <c r="S49">
-        <v>0.2971963109313115</v>
+        <v>0.6792937300270564</v>
+      </c>
+      <c r="T49">
+        <v>0.351781656516418</v>
       </c>
     </row>
     <row r="50">
@@ -3487,7 +3636,10 @@
         <v>0.6656169545741584</v>
       </c>
       <c r="S50">
-        <v>0.5903891368118868</v>
+        <v>0.6287366970060058</v>
+      </c>
+      <c r="T50">
+        <v>0.595867359696761</v>
       </c>
     </row>
     <row r="51">
@@ -3550,7 +3702,10 @@
         <v>0.690163433373723</v>
       </c>
       <c r="S51">
-        <v>0.4604887646886099</v>
+        <v>0.5714534258359116</v>
+      </c>
+      <c r="T51">
+        <v>0.4743593473320226</v>
       </c>
     </row>
     <row r="52">
@@ -3613,7 +3768,10 @@
         <v>0.1540676232248591</v>
       </c>
       <c r="S52">
-        <v>0.2696339425374459</v>
+        <v>0.5255938339302993</v>
+      </c>
+      <c r="T52">
+        <v>0.3016289289615526</v>
       </c>
     </row>
     <row r="53">
@@ -3670,7 +3828,10 @@
         <v>0.6434225384172394</v>
       </c>
       <c r="S53">
-        <v>0.5690446641386727</v>
+        <v>0.3947380546202585</v>
+      </c>
+      <c r="T53">
+        <v>0.5441437199217565</v>
       </c>
     </row>
     <row r="54">
@@ -3727,7 +3888,10 @@
         <v>0.495773586390557</v>
       </c>
       <c r="S54">
-        <v>0.4943371508542211</v>
+        <v>0.598697904392959</v>
+      </c>
+      <c r="T54">
+        <v>0.5092458299311837</v>
       </c>
     </row>
     <row r="55">
@@ -3790,7 +3954,10 @@
         <v>0.2936246343398432</v>
       </c>
       <c r="S55">
-        <v>0.4136318817346372</v>
+        <v>0.545484559726672</v>
+      </c>
+      <c r="T55">
+        <v>0.4301134664836416</v>
       </c>
     </row>
     <row r="56">
@@ -3853,7 +4020,10 @@
         <v>0.09733272948584863</v>
       </c>
       <c r="S56">
-        <v>0.2912757831257158</v>
+        <v>0.5998123870918999</v>
+      </c>
+      <c r="T56">
+        <v>0.3298428586214888</v>
       </c>
     </row>
     <row r="57">
@@ -3916,7 +4086,10 @@
         <v>0.2836291020695697</v>
       </c>
       <c r="S57">
-        <v>0.250132694118225</v>
+        <v>0.6128921960031078</v>
+      </c>
+      <c r="T57">
+        <v>0.2954776318538354</v>
       </c>
     </row>
     <row r="58">
@@ -3979,7 +4152,10 @@
         <v>0.4160821201627792</v>
       </c>
       <c r="S58">
-        <v>0.5495716014176817</v>
+        <v>0.6645498719476663</v>
+      </c>
+      <c r="T58">
+        <v>0.5639438852339298</v>
       </c>
     </row>
     <row r="59">
@@ -4042,7 +4218,10 @@
         <v>0.06049882961512109</v>
       </c>
       <c r="S59">
-        <v>0.3909021074196335</v>
+        <v>0.625978082019108</v>
+      </c>
+      <c r="T59">
+        <v>0.4202866042445678</v>
       </c>
     </row>
     <row r="60">
@@ -4105,7 +4284,10 @@
         <v>0.5635426354289883</v>
       </c>
       <c r="S60">
-        <v>0.6028309104919017</v>
+        <v>0.5562774968814153</v>
+      </c>
+      <c r="T60">
+        <v>0.5970117337905909</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4350,10 @@
         <v>0.1598195053246524</v>
       </c>
       <c r="S61">
-        <v>0.423692693565195</v>
+        <v>0.5618809113988922</v>
+      </c>
+      <c r="T61">
+        <v>0.4409662207944071</v>
       </c>
     </row>
     <row r="62">
@@ -4231,7 +4416,10 @@
         <v>0.5816221229475144</v>
       </c>
       <c r="S62">
-        <v>0.5466770863613633</v>
+        <v>0.5497647114252703</v>
+      </c>
+      <c r="T62">
+        <v>0.5470630394943516</v>
       </c>
     </row>
     <row r="63">
@@ -4288,7 +4476,10 @@
         <v>0.4896295946592574</v>
       </c>
       <c r="S63">
-        <v>0.5932109701638562</v>
+        <v>0.4656345146707593</v>
+      </c>
+      <c r="T63">
+        <v>0.5749857622362708</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4542,10 @@
         <v>0.6941109648268283</v>
       </c>
       <c r="S64">
-        <v>0.5011083458958873</v>
+        <v>0.5021810721168496</v>
+      </c>
+      <c r="T64">
+        <v>0.5012424366735075</v>
       </c>
     </row>
     <row r="65">
@@ -4414,7 +4608,10 @@
         <v>0.5053769041564342</v>
       </c>
       <c r="S65">
-        <v>0.4154792834622566</v>
+        <v>0.5352477992027502</v>
+      </c>
+      <c r="T65">
+        <v>0.4304503479298183</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4674,10 @@
         <v>0.3830767989130323</v>
       </c>
       <c r="S66">
-        <v>0.4351165398866201</v>
+        <v>0.583878886681464</v>
+      </c>
+      <c r="T66">
+        <v>0.4537118332359756</v>
       </c>
     </row>
     <row r="67">
@@ -4540,7 +4740,10 @@
         <v>0.1210445942521303</v>
       </c>
       <c r="S67">
-        <v>0.3611456243383549</v>
+        <v>0.5620731682909529</v>
+      </c>
+      <c r="T67">
+        <v>0.3862615673324296</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4806,10 @@
         <v>0.4048218374954839</v>
       </c>
       <c r="S68">
-        <v>0.361910066019606</v>
+        <v>0.5000679002635895</v>
+      </c>
+      <c r="T68">
+        <v>0.3791797953001039</v>
       </c>
     </row>
     <row r="69">
@@ -4666,7 +4872,10 @@
         <v>0.05017995772283684</v>
       </c>
       <c r="S69">
-        <v>0.4279376025771444</v>
+        <v>0.6452137412134239</v>
+      </c>
+      <c r="T69">
+        <v>0.4550971199066793</v>
       </c>
     </row>
     <row r="70">
@@ -4729,7 +4938,10 @@
         <v>0.4835470190802443</v>
       </c>
       <c r="S70">
-        <v>0.5474455346895999</v>
+        <v>0.6808911868735297</v>
+      </c>
+      <c r="T70">
+        <v>0.5641262412125911</v>
       </c>
     </row>
     <row r="71">
@@ -4792,7 +5004,10 @@
         <v>0.2792188433975049</v>
       </c>
       <c r="S71">
-        <v>0.4071934273761299</v>
+        <v>0.5868142752565406</v>
+      </c>
+      <c r="T71">
+        <v>0.4296460333611812</v>
       </c>
     </row>
     <row r="72">
@@ -4849,7 +5064,10 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>0.2447186930282441</v>
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0.2097588797384949</v>
       </c>
     </row>
     <row r="73">
@@ -4912,7 +5130,10 @@
         <v>0.03528014153309827</v>
       </c>
       <c r="S73">
-        <v>0.2743556905863575</v>
+        <v>0.6119871397440688</v>
+      </c>
+      <c r="T73">
+        <v>0.3165596217310714</v>
       </c>
     </row>
     <row r="74">
@@ -4975,7 +5196,10 @@
         <v>0.1057631609809458</v>
       </c>
       <c r="S74">
-        <v>0.321398270689901</v>
+        <v>0.5759859014309127</v>
+      </c>
+      <c r="T74">
+        <v>0.3532217245325274</v>
       </c>
     </row>
     <row r="75">
@@ -5038,7 +5262,10 @@
         <v>0.03251143917425656</v>
       </c>
       <c r="S75">
-        <v>0.2460411610386382</v>
+        <v>0.6060350084993592</v>
+      </c>
+      <c r="T75">
+        <v>0.2910403919712284</v>
       </c>
     </row>
     <row r="76">
@@ -5101,7 +5328,10 @@
         <v>0.3807606773129513</v>
       </c>
       <c r="S76">
-        <v>0.3704074563216646</v>
+        <v>0.5628408309384075</v>
+      </c>
+      <c r="T76">
+        <v>0.3944616281487575</v>
       </c>
     </row>
     <row r="77">
@@ -5164,7 +5394,10 @@
         <v>0.1525607253602217</v>
       </c>
       <c r="S77">
-        <v>0.408133780926715</v>
+        <v>0.6431040127003597</v>
+      </c>
+      <c r="T77">
+        <v>0.4375050598984205</v>
       </c>
     </row>
     <row r="78">
@@ -5227,7 +5460,10 @@
         <v>0.1928977467183089</v>
       </c>
       <c r="S78">
-        <v>0.4904316159997165</v>
+        <v>0.797701059445899</v>
+      </c>
+      <c r="T78">
+        <v>0.5288402964304894</v>
       </c>
     </row>
     <row r="79">
@@ -5290,7 +5526,10 @@
         <v>0.672291736389361</v>
       </c>
       <c r="S79">
-        <v>0.5686189190583649</v>
+        <v>0.5671346776639313</v>
+      </c>
+      <c r="T79">
+        <v>0.5684333888840607</v>
       </c>
     </row>
     <row r="80">
@@ -5353,7 +5592,10 @@
         <v>0.6078099058219762</v>
       </c>
       <c r="S80">
-        <v>0.3412325529016962</v>
+        <v>0.5816529148067182</v>
+      </c>
+      <c r="T80">
+        <v>0.3712850981398239</v>
       </c>
     </row>
     <row r="81">
@@ -5416,7 +5658,10 @@
         <v>1</v>
       </c>
       <c r="S81">
-        <v>0.5529223800651355</v>
+        <v>0.6414502173738073</v>
+      </c>
+      <c r="T81">
+        <v>0.5639883597287194</v>
       </c>
     </row>
     <row r="82">
@@ -5448,7 +5693,7 @@
       <c r="J82">
         <v>1</v>
       </c>
-      <c r="S82">
+      <c r="T82">
         <v>1</v>
       </c>
     </row>
@@ -5475,7 +5720,7 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="S83">
+      <c r="T83">
         <v>0.4914507303232135</v>
       </c>
     </row>
@@ -5502,7 +5747,7 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="S84">
+      <c r="T84">
         <v>0.238842983134942</v>
       </c>
     </row>

--- a/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
@@ -481,7 +481,7 @@
         <v>0.4502033243127747</v>
       </c>
       <c r="H2">
-        <v>11.83333333333333</v>
+        <v>11.55555555555556</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -516,10 +516,10 @@
         <v>0.3095837336681162</v>
       </c>
       <c r="S2">
-        <v>0.5329067273494283</v>
+        <v>0.257956957205875</v>
       </c>
       <c r="T2">
-        <v>0.4354594019648118</v>
+        <v>0.4010906806968677</v>
       </c>
     </row>
     <row r="3">
@@ -547,7 +547,7 @@
         <v>0.7413296543555572</v>
       </c>
       <c r="H3">
-        <v>5.728813559322034</v>
+        <v>5.685185185185185</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>0.4538193710537792</v>
       </c>
       <c r="S3">
-        <v>0.5349234617545326</v>
+        <v>0.2532498541851478</v>
       </c>
       <c r="T3">
-        <v>0.4702986596207985</v>
+        <v>0.4350894586746254</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         <v>0.1057957474868344</v>
       </c>
       <c r="H4">
-        <v>6.186440677966102</v>
+        <v>6.092592592592593</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -648,10 +648,10 @@
         <v>0.1763512235540355</v>
       </c>
       <c r="S4">
-        <v>0.3687207077501685</v>
+        <v>0.1702297501409914</v>
       </c>
       <c r="T4">
-        <v>0.3710736973455367</v>
+        <v>0.3462623276443896</v>
       </c>
     </row>
     <row r="5">
@@ -679,7 +679,7 @@
         <v>0.1938414998515946</v>
       </c>
       <c r="H5">
-        <v>3.35</v>
+        <v>3.296296296296296</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         <v>0.2901661958320036</v>
       </c>
       <c r="S5">
-        <v>0.9078847592894224</v>
+        <v>0.160709535150152</v>
       </c>
       <c r="T5">
-        <v>0.4810166675031289</v>
+        <v>0.3876197644857202</v>
       </c>
     </row>
     <row r="6">
@@ -745,7 +745,7 @@
         <v>0.05339131064146539</v>
       </c>
       <c r="H6">
-        <v>1.864406779661017</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         <v>0.08272192028282797</v>
       </c>
       <c r="S6">
-        <v>0.8102154638078963</v>
+        <v>0.1353865041854264</v>
       </c>
       <c r="T6">
-        <v>0.3808092436285181</v>
+        <v>0.2964556236757094</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +811,7 @@
         <v>0.2646275340176196</v>
       </c>
       <c r="H7">
-        <v>12.89830508474576</v>
+        <v>12.85185185185185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         <v>0.6061769173633896</v>
       </c>
       <c r="S7">
-        <v>0.6360493681792212</v>
+        <v>0.2621910960408731</v>
       </c>
       <c r="T7">
-        <v>0.5159078168911051</v>
+        <v>0.4691755328738116</v>
       </c>
     </row>
     <row r="8">
@@ -912,10 +912,10 @@
         <v>0.1482407307513151</v>
       </c>
       <c r="S8">
-        <v>0.577888345759738</v>
+        <v>0.1548245950020741</v>
       </c>
       <c r="T8">
-        <v>0.3774295605730006</v>
+        <v>0.3245465917282926</v>
       </c>
     </row>
     <row r="9">
@@ -978,10 +978,10 @@
         <v>0.3666128102901184</v>
       </c>
       <c r="S9">
-        <v>0.5269623043811215</v>
+        <v>0.1746890842429457</v>
       </c>
       <c r="T9">
-        <v>0.3302573739392751</v>
+        <v>0.2862232214220031</v>
       </c>
     </row>
     <row r="10">
@@ -1009,7 +1009,7 @@
         <v>0.2722728254797649</v>
       </c>
       <c r="H10">
-        <v>11.03333333333333</v>
+        <v>10.7962962962963</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         <v>0.6466931295555873</v>
       </c>
       <c r="S10">
-        <v>0.6286899729640903</v>
+        <v>0.2518041922392355</v>
       </c>
       <c r="T10">
-        <v>0.5189681427645747</v>
+        <v>0.4718574201739679</v>
       </c>
     </row>
     <row r="11">
@@ -1075,7 +1075,7 @@
         <v>0.1794372105771712</v>
       </c>
       <c r="H11">
-        <v>5.3</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
         <v>0.3387981378390733</v>
       </c>
       <c r="S11">
-        <v>0.5786033147410633</v>
+        <v>0.1605393662912078</v>
       </c>
       <c r="T11">
-        <v>0.4302901473936399</v>
+        <v>0.378032153837408</v>
       </c>
     </row>
     <row r="12">
@@ -1141,7 +1141,7 @@
         <v>0.1725654861486792</v>
       </c>
       <c r="H12">
-        <v>3.2</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         <v>0.3231240314170564</v>
       </c>
       <c r="S12">
-        <v>0.5881104701166693</v>
+        <v>0.1334079099935809</v>
       </c>
       <c r="T12">
-        <v>0.4199177691254978</v>
+        <v>0.3630799491101118</v>
       </c>
     </row>
     <row r="13">
@@ -1207,7 +1207,7 @@
         <v>0.4328120986234676</v>
       </c>
       <c r="H13">
-        <v>6.559322033898305</v>
+        <v>6.555555555555555</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1242,10 +1242,10 @@
         <v>0.3613628349666473</v>
       </c>
       <c r="S13">
-        <v>0.3967074045852518</v>
+        <v>0.2016718471293336</v>
       </c>
       <c r="T13">
-        <v>0.529439030243426</v>
+        <v>0.5050595855614363</v>
       </c>
     </row>
     <row r="14">
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.95</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>0.002517386384649483</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>0.1161380623010923</v>
       </c>
       <c r="T14">
-        <v>0.3857950825619834</v>
+        <v>0.2753123403496199</v>
       </c>
     </row>
     <row r="15">
@@ -1339,7 +1339,7 @@
         <v>0.2462012202106107</v>
       </c>
       <c r="H15">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
         <v>0.1189272518667831</v>
       </c>
       <c r="S15">
-        <v>0.5991571254558291</v>
+        <v>0.1900188806640827</v>
       </c>
       <c r="T15">
-        <v>0.3457559912962205</v>
+        <v>0.2946137106972522</v>
       </c>
     </row>
     <row r="16">
@@ -1440,10 +1440,10 @@
         <v>0.2433418210541713</v>
       </c>
       <c r="S16">
-        <v>0.615833348345295</v>
+        <v>0.1642039281024077</v>
       </c>
       <c r="T16">
-        <v>0.405959838201403</v>
+        <v>0.3495061606710421</v>
       </c>
     </row>
     <row r="17">
@@ -1506,10 +1506,10 @@
         <v>0.1278675422350279</v>
       </c>
       <c r="S17">
-        <v>0.682795362548585</v>
+        <v>0.1678917168888577</v>
       </c>
       <c r="T17">
-        <v>0.1888997823376367</v>
+        <v>0.1245368266301708</v>
       </c>
     </row>
     <row r="18">
@@ -1537,7 +1537,7 @@
         <v>0.5553722770017252</v>
       </c>
       <c r="H18">
-        <v>3.559322033898305</v>
+        <v>3.648148148148148</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
         <v>0.3653087018938461</v>
       </c>
       <c r="S18">
-        <v>0.5691113227775285</v>
+        <v>0.1821903962478089</v>
       </c>
       <c r="T18">
-        <v>0.4316551768814519</v>
+        <v>0.3832900610652369</v>
       </c>
     </row>
     <row r="19">
@@ -1603,7 +1603,7 @@
         <v>0.3432851485283125</v>
       </c>
       <c r="H19">
-        <v>12.15254237288136</v>
+        <v>11.92592592592593</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         <v>0.6147991208738268</v>
       </c>
       <c r="S19">
-        <v>0.4762697184401813</v>
+        <v>0.2392937685081673</v>
       </c>
       <c r="T19">
-        <v>0.5655351652754445</v>
+        <v>0.5359131715339427</v>
       </c>
     </row>
     <row r="20">
@@ -1669,7 +1669,7 @@
         <v>0.345635695996907</v>
       </c>
       <c r="H20">
-        <v>3.694915254237288</v>
+        <v>3.759259259259259</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>0.1830304771246527</v>
       </c>
       <c r="S20">
-        <v>0.6169762430128304</v>
+        <v>0.1735674814922469</v>
       </c>
       <c r="T20">
-        <v>0.4180158963493737</v>
+        <v>0.3625898011593008</v>
       </c>
     </row>
     <row r="21">
@@ -1735,7 +1735,7 @@
         <v>0.4034716741671714</v>
       </c>
       <c r="H21">
-        <v>33.2280701754386</v>
+        <v>32.85185185185185</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         <v>0.8143839706609451</v>
       </c>
       <c r="S21">
-        <v>0.5893605834780353</v>
+        <v>0.2777982644896537</v>
       </c>
       <c r="T21">
-        <v>0.6250387553631787</v>
+        <v>0.5805298526505527</v>
       </c>
     </row>
     <row r="22">
@@ -1795,7 +1795,7 @@
         <v>0.2635702634115568</v>
       </c>
       <c r="H22">
-        <v>3.6</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         <v>0.8229340500243738</v>
       </c>
       <c r="S22">
-        <v>0.6145812357572692</v>
+        <v>0.2544337843007431</v>
       </c>
       <c r="T22">
-        <v>0.4913011028611162</v>
+        <v>0.4462826714290504</v>
       </c>
     </row>
     <row r="23">
@@ -1861,7 +1861,7 @@
         <v>0.5406677202976605</v>
       </c>
       <c r="H23">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>0.1568873000010577</v>
       </c>
       <c r="S23">
-        <v>0.5996922527986955</v>
+        <v>0.2269023679670693</v>
       </c>
       <c r="T23">
-        <v>0.4699956015746756</v>
+        <v>0.4167399037415861</v>
       </c>
     </row>
     <row r="24">
@@ -1921,7 +1921,7 @@
         <v>0.5871287378423848</v>
       </c>
       <c r="H24">
-        <v>33.47457627118644</v>
+        <v>34.27777777777778</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         <v>0.8162800998680531</v>
       </c>
       <c r="S24">
-        <v>0.5801183710685277</v>
+        <v>0.2625608208348425</v>
       </c>
       <c r="T24">
-        <v>0.5733428755922564</v>
+        <v>0.5279775112731585</v>
       </c>
     </row>
     <row r="25">
@@ -2016,10 +2016,10 @@
         <v>0.08751634375215032</v>
       </c>
       <c r="S25">
-        <v>0.6829831089609784</v>
+        <v>0.06739172595307573</v>
       </c>
       <c r="T25">
-        <v>0.2394407684704253</v>
+        <v>0.1624918455944375</v>
       </c>
     </row>
     <row r="26">
@@ -2047,7 +2047,7 @@
         <v>0.1356334172128486</v>
       </c>
       <c r="H26">
-        <v>0.9833333333333333</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
         <v>0.04932251807502108</v>
       </c>
       <c r="S26">
-        <v>0.6188409714365701</v>
+        <v>0.156364379748628</v>
       </c>
       <c r="T26">
-        <v>0.3641983449472598</v>
+        <v>0.2981302604204109</v>
       </c>
     </row>
     <row r="27">
@@ -2107,7 +2107,7 @@
         <v>0.1929276683770822</v>
       </c>
       <c r="H27">
-        <v>3.677966101694915</v>
+        <v>3.685185185185185</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0.3079124135096388</v>
       </c>
       <c r="S27">
-        <v>0.594763872245282</v>
+        <v>0.2291827418108969</v>
       </c>
       <c r="T27">
-        <v>0.3972794983421776</v>
+        <v>0.3515818570378795</v>
       </c>
     </row>
     <row r="28">
@@ -2173,7 +2173,7 @@
         <v>0.2578755484434986</v>
       </c>
       <c r="H28">
-        <v>1.627118644067797</v>
+        <v>1.62962962962963</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         <v>0.09284481701469087</v>
       </c>
       <c r="S28">
-        <v>0.6533281703868384</v>
+        <v>0.1853852287088332</v>
       </c>
       <c r="T28">
-        <v>0.3349142365234932</v>
+        <v>0.2764213688137425</v>
       </c>
     </row>
     <row r="29">
@@ -2239,7 +2239,7 @@
         <v>0.2123270849778836</v>
       </c>
       <c r="H29">
-        <v>3.933333333333333</v>
+        <v>3.925925925925926</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>0.1793228053399155</v>
       </c>
       <c r="S29">
-        <v>0.5774938934128605</v>
+        <v>0.2516616844716736</v>
       </c>
       <c r="T29">
-        <v>0.3772086553640545</v>
+        <v>0.3364796292464061</v>
       </c>
     </row>
     <row r="30">
@@ -2305,7 +2305,7 @@
         <v>0.8385757809677933</v>
       </c>
       <c r="H30">
-        <v>12.86440677966102</v>
+        <v>12.72222222222222</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         <v>0.4399859346834002</v>
       </c>
       <c r="S30">
-        <v>0.5989790510914346</v>
+        <v>0.2752522366203629</v>
       </c>
       <c r="T30">
-        <v>0.5448835123206189</v>
+        <v>0.504417660511735</v>
       </c>
     </row>
     <row r="31">
@@ -2371,7 +2371,7 @@
         <v>0.3816370183502008</v>
       </c>
       <c r="H31">
-        <v>6.135593220338983</v>
+        <v>6.074074074074074</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
         <v>0.4377780342244889</v>
       </c>
       <c r="S31">
-        <v>0.6415004625970644</v>
+        <v>0.2632556384061693</v>
       </c>
       <c r="T31">
-        <v>0.4210514142945841</v>
+        <v>0.3737708112707222</v>
       </c>
     </row>
     <row r="32">
@@ -2472,10 +2472,10 @@
         <v>0.2110482135820394</v>
       </c>
       <c r="S32">
-        <v>0.5975978979229554</v>
+        <v>0.2320791337767583</v>
       </c>
       <c r="T32">
-        <v>0.3098856723302205</v>
+        <v>0.2641958268119458</v>
       </c>
     </row>
     <row r="33">
@@ -2503,7 +2503,7 @@
         <v>0.1794125704875191</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>6.037037037037037</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
         <v>0.3361594147792935</v>
       </c>
       <c r="S33">
-        <v>0.6409674193251149</v>
+        <v>0.2348699485863942</v>
       </c>
       <c r="T33">
-        <v>0.4547818316862475</v>
+        <v>0.4040196478439074</v>
       </c>
     </row>
     <row r="34">
@@ -2569,7 +2569,7 @@
         <v>0.02586534117939243</v>
       </c>
       <c r="H34">
-        <v>0.7333333333333333</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2604,10 +2604,10 @@
         <v>0.02281253493604877</v>
       </c>
       <c r="S34">
-        <v>0.3878842490321296</v>
+        <v>0.9745408842539789</v>
       </c>
       <c r="T34">
-        <v>0.2773892274815399</v>
+        <v>0.3507213068842711</v>
       </c>
     </row>
     <row r="35">
@@ -2635,7 +2635,7 @@
         <v>0.4252783256106065</v>
       </c>
       <c r="H35">
-        <v>3.610169491525424</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         <v>0.4403286329702006</v>
       </c>
       <c r="S35">
-        <v>0.6126968147045188</v>
+        <v>0.2447513819859251</v>
       </c>
       <c r="T35">
-        <v>0.4271486305460002</v>
+        <v>0.381155451456176</v>
       </c>
     </row>
     <row r="36">
@@ -2701,7 +2701,7 @@
         <v>0.3192961681722459</v>
       </c>
       <c r="H36">
-        <v>6.220338983050848</v>
+        <v>6.25925925925926</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>0.2038430837769933</v>
       </c>
       <c r="S36">
-        <v>0.6403530622123499</v>
+        <v>0.2232025060676819</v>
       </c>
       <c r="T36">
-        <v>0.4726162780285602</v>
+        <v>0.4204724585104767</v>
       </c>
     </row>
     <row r="37">
@@ -2767,7 +2767,7 @@
         <v>0.4289753967967581</v>
       </c>
       <c r="H37">
-        <v>11.2</v>
+        <v>11.22222222222222</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
         <v>0.3251364505456744</v>
       </c>
       <c r="S37">
-        <v>0.478776788243877</v>
+        <v>0.2245429766960785</v>
       </c>
       <c r="T37">
-        <v>0.418577826065243</v>
+        <v>0.3867985996217682</v>
       </c>
     </row>
     <row r="38">
@@ -2868,10 +2868,10 @@
         <v>0.2229649301928028</v>
       </c>
       <c r="S38">
-        <v>0.661139318763453</v>
+        <v>0.1930623898842926</v>
       </c>
       <c r="T38">
-        <v>0.3878689295989648</v>
+        <v>0.3293593134890697</v>
       </c>
     </row>
     <row r="39">
@@ -2899,7 +2899,7 @@
         <v>0.3274098028289681</v>
       </c>
       <c r="H39">
-        <v>1.88135593220339</v>
+        <v>1.87037037037037</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         <v>0.1701929791078292</v>
       </c>
       <c r="S39">
-        <v>0.6305161911917418</v>
+        <v>0.230276263816248</v>
       </c>
       <c r="T39">
-        <v>0.3712038046900686</v>
+        <v>0.3211738137681319</v>
       </c>
     </row>
     <row r="40">
@@ -2965,7 +2965,7 @@
         <v>0.3101001438235678</v>
       </c>
       <c r="H40">
-        <v>6.915254237288136</v>
+        <v>6.87037037037037</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         <v>0.5211469907343621</v>
       </c>
       <c r="S40">
-        <v>0.596078955458171</v>
+        <v>0.2749147008311783</v>
       </c>
       <c r="T40">
-        <v>0.5339481958353862</v>
+        <v>0.4938026640070121</v>
       </c>
     </row>
     <row r="41">
@@ -3031,7 +3031,7 @@
         <v>0.4360570801765042</v>
       </c>
       <c r="H41">
-        <v>11.22033898305085</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>0.2964707187646027</v>
       </c>
       <c r="S41">
-        <v>0.5826263751744765</v>
+        <v>0.2671520248835246</v>
       </c>
       <c r="T41">
-        <v>0.5157037723264736</v>
+        <v>0.4762694785401046</v>
       </c>
     </row>
     <row r="42">
@@ -3132,10 +3132,10 @@
         <v>0.4002046585006649</v>
       </c>
       <c r="S42">
-        <v>0.566614599603148</v>
+        <v>0.1459900740925717</v>
       </c>
       <c r="T42">
-        <v>0.3721320858326465</v>
+        <v>0.3195540201438244</v>
       </c>
     </row>
     <row r="43">
@@ -3163,7 +3163,7 @@
         <v>0.06292274041894994</v>
       </c>
       <c r="H43">
-        <v>1.932203389830508</v>
+        <v>1.925925925925926</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>0.05414792544086373</v>
       </c>
       <c r="S43">
-        <v>0.6222562924529285</v>
+        <v>0.1492307420428639</v>
       </c>
       <c r="T43">
-        <v>0.2793160484142984</v>
+        <v>0.2201878546130404</v>
       </c>
     </row>
     <row r="44">
@@ -3229,7 +3229,7 @@
         <v>0.1842351684165962</v>
       </c>
       <c r="H44">
-        <v>3.491525423728814</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
         <v>0.07146602998081229</v>
       </c>
       <c r="S44">
-        <v>0.6336020089526978</v>
+        <v>0.1486362155202371</v>
       </c>
       <c r="T44">
-        <v>0.4082423310461546</v>
+        <v>0.347621606867097</v>
       </c>
     </row>
     <row r="45">
@@ -3295,7 +3295,7 @@
         <v>0.4207276517137379</v>
       </c>
       <c r="H45">
-        <v>6.35593220338983</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
         <v>0.3260096735872604</v>
       </c>
       <c r="S45">
-        <v>0.6118374938834623</v>
+        <v>0.2100108886364534</v>
       </c>
       <c r="T45">
-        <v>0.4050118182768065</v>
+        <v>0.3476080175272339</v>
       </c>
     </row>
     <row r="46">
@@ -3355,7 +3355,7 @@
         <v>0.3016562708528405</v>
       </c>
       <c r="H46">
-        <v>5.491525423728813</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         <v>0.4464741142412194</v>
       </c>
       <c r="S46">
-        <v>0.6743730996497096</v>
+        <v>0.2478859201476175</v>
       </c>
       <c r="T46">
-        <v>0.4858982399820149</v>
+        <v>0.4325873425442534</v>
       </c>
     </row>
     <row r="47">
@@ -3450,10 +3450,10 @@
         <v>0.2936587098507883</v>
       </c>
       <c r="S47">
-        <v>0.6555409651319281</v>
+        <v>0.1859714351434707</v>
       </c>
       <c r="T47">
-        <v>0.5491618808811666</v>
+        <v>0.4820805194542441</v>
       </c>
     </row>
     <row r="48">
@@ -3481,7 +3481,7 @@
         <v>0.2649479515603004</v>
       </c>
       <c r="H48">
-        <v>6.203389830508475</v>
+        <v>6.074074074074074</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         <v>0.2983419634079955</v>
       </c>
       <c r="S48">
-        <v>0.6109316377023839</v>
+        <v>0.2463241435986678</v>
       </c>
       <c r="T48">
-        <v>0.5035604557409975</v>
+        <v>0.457984518978033</v>
       </c>
     </row>
     <row r="49">
@@ -3547,7 +3547,7 @@
         <v>0.1082340763151742</v>
       </c>
       <c r="H49">
-        <v>1.864406779661017</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         <v>0.1059915160799036</v>
       </c>
       <c r="S49">
-        <v>0.6792937300270564</v>
+        <v>0.08767184358108708</v>
       </c>
       <c r="T49">
-        <v>0.351781656516418</v>
+        <v>0.2672642441669938</v>
       </c>
     </row>
     <row r="50">
@@ -3607,7 +3607,7 @@
         <v>0.6784837014667312</v>
       </c>
       <c r="H50">
-        <v>11.5</v>
+        <v>11.37037037037037</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         <v>0.6656169545741584</v>
       </c>
       <c r="S50">
-        <v>0.6287366970060058</v>
+        <v>0.2783918632235105</v>
       </c>
       <c r="T50">
-        <v>0.595867359696761</v>
+        <v>0.5458180977278331</v>
       </c>
     </row>
     <row r="51">
@@ -3667,7 +3667,7 @@
         <v>0.889289216945143</v>
       </c>
       <c r="H51">
-        <v>3.254237288135593</v>
+        <v>3.185185185185185</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3702,10 +3702,10 @@
         <v>0.690163433373723</v>
       </c>
       <c r="S51">
-        <v>0.5714534258359116</v>
+        <v>0.2972274781089727</v>
       </c>
       <c r="T51">
-        <v>0.4743593473320226</v>
+        <v>0.4400811038661552</v>
       </c>
     </row>
     <row r="52">
@@ -3768,10 +3768,10 @@
         <v>0.1540676232248591</v>
       </c>
       <c r="S52">
-        <v>0.5255938339302993</v>
+        <v>0.2179525028826017</v>
       </c>
       <c r="T52">
-        <v>0.3016289289615526</v>
+        <v>0.2631737625805904</v>
       </c>
     </row>
     <row r="53">
@@ -3799,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="H53">
-        <v>3.033898305084746</v>
+        <v>3.018518518518519</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         <v>0.6434225384172394</v>
       </c>
       <c r="S53">
-        <v>0.3947380546202585</v>
+        <v>1</v>
       </c>
       <c r="T53">
-        <v>0.5441437199217565</v>
+        <v>0.6306097121188623</v>
       </c>
     </row>
     <row r="54">
@@ -3859,7 +3859,7 @@
         <v>0.4313278728958421</v>
       </c>
       <c r="H54">
-        <v>33.78947368421053</v>
+        <v>33.22222222222222</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>0.495773586390557</v>
       </c>
       <c r="S54">
-        <v>0.598697904392959</v>
+        <v>0.2572970892523003</v>
       </c>
       <c r="T54">
-        <v>0.5092458299311837</v>
+        <v>0.4604742849110896</v>
       </c>
     </row>
     <row r="55">
@@ -3919,7 +3919,7 @@
         <v>0.2550097067168988</v>
       </c>
       <c r="H55">
-        <v>10.33898305084746</v>
+        <v>10.38888888888889</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>0.2936246343398432</v>
       </c>
       <c r="S55">
-        <v>0.545484559726672</v>
+        <v>0.1889170238053269</v>
       </c>
       <c r="T55">
-        <v>0.4301134664836416</v>
+        <v>0.3855425244934734</v>
       </c>
     </row>
     <row r="56">
@@ -4020,10 +4020,10 @@
         <v>0.09733272948584863</v>
       </c>
       <c r="S56">
-        <v>0.5998123870918999</v>
+        <v>0.08300196495180187</v>
       </c>
       <c r="T56">
-        <v>0.3298428586214888</v>
+        <v>0.2652415558539766</v>
       </c>
     </row>
     <row r="57">
@@ -4051,7 +4051,7 @@
         <v>0.09813978288016498</v>
       </c>
       <c r="H57">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         <v>0.2836291020695697</v>
       </c>
       <c r="S57">
-        <v>0.6128921960031078</v>
+        <v>0.1979732350129783</v>
       </c>
       <c r="T57">
-        <v>0.2954776318538354</v>
+        <v>0.2436127617300692</v>
       </c>
     </row>
     <row r="58">
@@ -4117,7 +4117,7 @@
         <v>0.261327564612032</v>
       </c>
       <c r="H58">
-        <v>5.186440677966102</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4152,10 +4152,10 @@
         <v>0.4160821201627792</v>
       </c>
       <c r="S58">
-        <v>0.6645498719476663</v>
+        <v>0.2232137599698851</v>
       </c>
       <c r="T58">
-        <v>0.5639438852339298</v>
+        <v>0.5087768712367071</v>
       </c>
     </row>
     <row r="59">
@@ -4183,7 +4183,7 @@
         <v>0.111842042117239</v>
       </c>
       <c r="H59">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4218,10 +4218,10 @@
         <v>0.06049882961512109</v>
       </c>
       <c r="S59">
-        <v>0.625978082019108</v>
+        <v>0.1626101452000377</v>
       </c>
       <c r="T59">
-        <v>0.4202866042445678</v>
+        <v>0.362365612142184</v>
       </c>
     </row>
     <row r="60">
@@ -4249,7 +4249,7 @@
         <v>0.5793940482055104</v>
       </c>
       <c r="H60">
-        <v>12.3</v>
+        <v>12.18518518518519</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         <v>0.5635426354289883</v>
       </c>
       <c r="S60">
-        <v>0.5562774968814153</v>
+        <v>0.2786914248453622</v>
       </c>
       <c r="T60">
-        <v>0.5970117337905909</v>
+        <v>0.5623134747860843</v>
       </c>
     </row>
     <row r="61">
@@ -4315,7 +4315,7 @@
         <v>0.1177123840965592</v>
       </c>
       <c r="H61">
-        <v>3.416666666666667</v>
+        <v>3.425925925925926</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4350,10 +4350,10 @@
         <v>0.1598195053246524</v>
       </c>
       <c r="S61">
-        <v>0.5618809113988922</v>
+        <v>0.2751526068373289</v>
       </c>
       <c r="T61">
-        <v>0.4409662207944071</v>
+        <v>0.4051251827242117</v>
       </c>
     </row>
     <row r="62">
@@ -4381,7 +4381,7 @@
         <v>0.3442607960650296</v>
       </c>
       <c r="H62">
-        <v>11.28813559322034</v>
+        <v>11.14814814814815</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
         <v>0.5816221229475144</v>
       </c>
       <c r="S62">
-        <v>0.5497647114252703</v>
+        <v>0.2881704189419155</v>
       </c>
       <c r="T62">
-        <v>0.5470630394943516</v>
+        <v>0.5143637529339323</v>
       </c>
     </row>
     <row r="63">
@@ -4447,7 +4447,7 @@
         <v>0.7109402100562092</v>
       </c>
       <c r="H63">
-        <v>34.94915254237288</v>
+        <v>34.55555555555556</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
         <v>0.4896295946592574</v>
       </c>
       <c r="S63">
-        <v>0.4656345146707593</v>
+        <v>0.3537062882326431</v>
       </c>
       <c r="T63">
-        <v>0.5749857622362708</v>
+        <v>0.5589960156022543</v>
       </c>
     </row>
     <row r="64">
@@ -4507,7 +4507,7 @@
         <v>0.4338478696343794</v>
       </c>
       <c r="H64">
-        <v>13</v>
+        <v>13.09259259259259</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4542,10 +4542,10 @@
         <v>0.6941109648268283</v>
       </c>
       <c r="S64">
-        <v>0.5021810721168496</v>
+        <v>0.2926364621243586</v>
       </c>
       <c r="T64">
-        <v>0.5012424366735075</v>
+        <v>0.4750493604244461</v>
       </c>
     </row>
     <row r="65">
@@ -4573,7 +4573,7 @@
         <v>0.3022380138894571</v>
       </c>
       <c r="H65">
-        <v>2.95</v>
+        <v>2.851851851851852</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         <v>0.5053769041564342</v>
       </c>
       <c r="S65">
-        <v>0.5352477992027502</v>
+        <v>0.2500738063642959</v>
       </c>
       <c r="T65">
-        <v>0.4304503479298183</v>
+        <v>0.3948035988250115</v>
       </c>
     </row>
     <row r="66">
@@ -4639,7 +4639,7 @@
         <v>0.7225171888737136</v>
       </c>
       <c r="H66">
-        <v>7.689655172413793</v>
+        <v>7.69811320754717</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4674,10 +4674,10 @@
         <v>0.3830767989130323</v>
       </c>
       <c r="S66">
-        <v>0.583878886681464</v>
+        <v>0.2433711358906481</v>
       </c>
       <c r="T66">
-        <v>0.4537118332359756</v>
+        <v>0.4111483643871237</v>
       </c>
     </row>
     <row r="67">
@@ -4705,7 +4705,7 @@
         <v>0.1092083653444846</v>
       </c>
       <c r="H67">
-        <v>2.694915254237288</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>0.1210445942521303</v>
       </c>
       <c r="S67">
-        <v>0.5620731682909529</v>
+        <v>0.1483421034153823</v>
       </c>
       <c r="T67">
-        <v>0.3862615673324296</v>
+        <v>0.3345451842229833</v>
       </c>
     </row>
     <row r="68">
@@ -4771,7 +4771,7 @@
         <v>0.3888193395575589</v>
       </c>
       <c r="H68">
-        <v>6.677966101694915</v>
+        <v>6.685185185185185</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
         <v>0.4048218374954839</v>
       </c>
       <c r="S68">
-        <v>0.5000679002635895</v>
+        <v>0.2312243203600459</v>
       </c>
       <c r="T68">
-        <v>0.3791797953001039</v>
+        <v>0.345574347812161</v>
       </c>
     </row>
     <row r="69">
@@ -4872,10 +4872,10 @@
         <v>0.05017995772283684</v>
       </c>
       <c r="S69">
-        <v>0.6452137412134239</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>0.4550971199066793</v>
+        <v>0.3744454022550013</v>
       </c>
     </row>
     <row r="70">
@@ -4903,7 +4903,7 @@
         <v>0.8648964270282454</v>
       </c>
       <c r="H70">
-        <v>6.610169491525424</v>
+        <v>6.592592592592593</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4938,10 +4938,10 @@
         <v>0.4835470190802443</v>
       </c>
       <c r="S70">
-        <v>0.6808911868735297</v>
+        <v>0.2645072720608249</v>
       </c>
       <c r="T70">
-        <v>0.5641262412125911</v>
+        <v>0.512078251861003</v>
       </c>
     </row>
     <row r="71">
@@ -4969,7 +4969,7 @@
         <v>0.07749743659883106</v>
       </c>
       <c r="H71">
-        <v>3.779661016949153</v>
+        <v>3.759259259259259</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0.2792188433975049</v>
       </c>
       <c r="S71">
-        <v>0.5868142752565406</v>
+        <v>0.1815784376029904</v>
       </c>
       <c r="T71">
-        <v>0.4296460333611812</v>
+        <v>0.3789915536544874</v>
       </c>
     </row>
     <row r="72">
@@ -5035,7 +5035,7 @@
         <v>0.1292990040239251</v>
       </c>
       <c r="H72">
-        <v>0.9833333333333333</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>0.131644287510149</v>
       </c>
       <c r="T72">
-        <v>0.2097588797384949</v>
+        <v>0.2285652065256591</v>
       </c>
     </row>
     <row r="73">
@@ -5095,7 +5095,7 @@
         <v>0.02187888998215423</v>
       </c>
       <c r="H73">
-        <v>0.9833333333333333</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
         <v>0.03528014153309827</v>
       </c>
       <c r="S73">
-        <v>0.6119871397440688</v>
+        <v>0.04338224772508872</v>
       </c>
       <c r="T73">
-        <v>0.3165596217310714</v>
+        <v>0.2454840102286989</v>
       </c>
     </row>
     <row r="74">
@@ -5196,10 +5196,10 @@
         <v>0.1057631609809458</v>
       </c>
       <c r="S74">
-        <v>0.5759859014309127</v>
+        <v>0.1833784408786485</v>
       </c>
       <c r="T74">
-        <v>0.3532217245325274</v>
+        <v>0.3041457919634944</v>
       </c>
     </row>
     <row r="75">
@@ -5227,7 +5227,7 @@
         <v>0.02237366954390341</v>
       </c>
       <c r="H75">
-        <v>1.9</v>
+        <v>1.907407407407407</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5262,10 +5262,10 @@
         <v>0.03251143917425656</v>
       </c>
       <c r="S75">
-        <v>0.6060350084993592</v>
+        <v>0.1632758599237923</v>
       </c>
       <c r="T75">
-        <v>0.2910403919712284</v>
+        <v>0.2356954983992825</v>
       </c>
     </row>
     <row r="76">
@@ -5293,7 +5293,7 @@
         <v>0.3139710523042856</v>
       </c>
       <c r="H76">
-        <v>6.35593220338983</v>
+        <v>6.537037037037037</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>0.3807606773129513</v>
       </c>
       <c r="S76">
-        <v>0.5628408309384075</v>
+        <v>0.1565376364396137</v>
       </c>
       <c r="T76">
-        <v>0.3944616281487575</v>
+        <v>0.3436737288364082</v>
       </c>
     </row>
     <row r="77">
@@ -5394,10 +5394,10 @@
         <v>0.1525607253602217</v>
       </c>
       <c r="S77">
-        <v>0.6431040127003597</v>
+        <v>0.1064792360950618</v>
       </c>
       <c r="T77">
-        <v>0.4375050598984205</v>
+        <v>0.3704269628227583</v>
       </c>
     </row>
     <row r="78">
@@ -5425,7 +5425,7 @@
         <v>0.4561015823670683</v>
       </c>
       <c r="H78">
-        <v>10.48333333333333</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5460,10 +5460,10 @@
         <v>0.1928977467183089</v>
       </c>
       <c r="S78">
-        <v>0.797701059445899</v>
+        <v>0.1891495494652774</v>
       </c>
       <c r="T78">
-        <v>0.5288402964304894</v>
+        <v>0.4527713576829116</v>
       </c>
     </row>
     <row r="79">
@@ -5491,7 +5491,7 @@
         <v>0.6119830218729293</v>
       </c>
       <c r="H79">
-        <v>9.85</v>
+        <v>9.62962962962963</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5526,10 +5526,10 @@
         <v>0.672291736389361</v>
       </c>
       <c r="S79">
-        <v>0.5671346776639313</v>
+        <v>0.1312630330506945</v>
       </c>
       <c r="T79">
-        <v>0.5684333888840607</v>
+        <v>0.5139494333074062</v>
       </c>
     </row>
     <row r="80">
@@ -5557,7 +5557,7 @@
         <v>0.04579943656746183</v>
       </c>
       <c r="H80">
-        <v>1.9</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -5592,10 +5592,10 @@
         <v>0.6078099058219762</v>
       </c>
       <c r="S80">
-        <v>0.5816529148067182</v>
+        <v>0.09273992238029152</v>
       </c>
       <c r="T80">
-        <v>0.3712850981398239</v>
+        <v>0.3101709740865206</v>
       </c>
     </row>
     <row r="81">
@@ -5623,7 +5623,7 @@
         <v>0.2831754054086119</v>
       </c>
       <c r="H81">
-        <v>2.833333333333333</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>1</v>
       </c>
       <c r="S81">
-        <v>0.6414502173738073</v>
+        <v>0.1659300950003614</v>
       </c>
       <c r="T81">
-        <v>0.5639883597287194</v>
+        <v>0.5045483444320388</v>
       </c>
     </row>
     <row r="82">
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="H82">
-        <v>0.9523809523809523</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>

--- a/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -437,20 +437,15 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>biomass_stability</t>
+          <t>mean_WSA</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>biomass_stability_standardized</t>
+          <t>stand_WSA</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>aggregates_standardized</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>multifunctionality</t>
         </is>
@@ -463,25 +458,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>870.7120698129983</v>
+        <v>828.3773512579434</v>
       </c>
       <c r="C2">
-        <v>2.501219340892978</v>
+        <v>2.866126361212376</v>
       </c>
       <c r="D2">
-        <v>0.7409760260026874</v>
+        <v>0.6976528103196753</v>
       </c>
       <c r="E2">
-        <v>0.2031038447534122</v>
+        <v>0.6159109451427114</v>
       </c>
       <c r="F2">
-        <v>115.2180067008</v>
+        <v>152.379692735</v>
       </c>
       <c r="G2">
-        <v>0.4502033243127747</v>
+        <v>0.341094719692547</v>
       </c>
       <c r="H2">
-        <v>11.55555555555556</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -510,16 +505,13 @@
         <v>0.2216812478742441</v>
       </c>
       <c r="Q2">
-        <v>2.259870857882385</v>
+        <v>76.62873521908637</v>
       </c>
       <c r="R2">
-        <v>0.3095837336681162</v>
+        <v>0.6467060369329617</v>
       </c>
       <c r="S2">
-        <v>0.257956957205875</v>
-      </c>
-      <c r="T2">
-        <v>0.4010906806968677</v>
+        <v>0.5068951531028529</v>
       </c>
     </row>
     <row r="3">
@@ -529,25 +521,25 @@
         </is>
       </c>
       <c r="B3">
-        <v>673.5165133337398</v>
+        <v>655.9329685983965</v>
       </c>
       <c r="C3">
-        <v>2.210478914653579</v>
+        <v>2.472243181288298</v>
       </c>
       <c r="D3">
-        <v>0.6224479165285582</v>
+        <v>0.5403418864281665</v>
       </c>
       <c r="E3">
-        <v>0.1601965597224594</v>
+        <v>0.4765788354798875</v>
       </c>
       <c r="F3">
-        <v>173.367179246</v>
+        <v>275.3171712859375</v>
       </c>
       <c r="G3">
-        <v>0.7413296543555572</v>
+        <v>0.7967257165554308</v>
       </c>
       <c r="H3">
-        <v>5.685185185185185</v>
+        <v>5.728813559322034</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -576,16 +568,13 @@
         <v>0.2403557239196652</v>
       </c>
       <c r="Q3">
-        <v>3.037901513434422</v>
+        <v>82.09284007594343</v>
       </c>
       <c r="R3">
-        <v>0.4538193710537792</v>
+        <v>0.7533089956157759</v>
       </c>
       <c r="S3">
-        <v>0.2532498541851478</v>
-      </c>
-      <c r="T3">
-        <v>0.4350894586746254</v>
+        <v>0.5452325353758232</v>
       </c>
     </row>
     <row r="4">
@@ -595,25 +584,25 @@
         </is>
       </c>
       <c r="B4">
-        <v>792.8045437231686</v>
+        <v>776.4263094419364</v>
       </c>
       <c r="C4">
-        <v>2.286344724644616</v>
+        <v>2.584558235505043</v>
       </c>
       <c r="D4">
-        <v>0.6941482376584547</v>
+        <v>0.6502609135285969</v>
       </c>
       <c r="E4">
-        <v>0.1713927871459866</v>
+        <v>0.5163091267147911</v>
       </c>
       <c r="F4">
-        <v>46.4265112432</v>
+        <v>111.1061707528571</v>
       </c>
       <c r="G4">
-        <v>0.1057957474868344</v>
+        <v>0.1881267542972417</v>
       </c>
       <c r="H4">
-        <v>6.092592592592593</v>
+        <v>6.186440677966102</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -642,16 +631,13 @@
         <v>0.5374935235398688</v>
       </c>
       <c r="Q4">
-        <v>1.541192873274919</v>
+        <v>62.02883600242884</v>
       </c>
       <c r="R4">
-        <v>0.1763512235540355</v>
+        <v>0.3618666178992232</v>
       </c>
       <c r="S4">
-        <v>0.1702297501409914</v>
-      </c>
-      <c r="T4">
-        <v>0.3462623276443896</v>
+        <v>0.4526777553726667</v>
       </c>
     </row>
     <row r="5">
@@ -661,25 +647,25 @@
         </is>
       </c>
       <c r="B5">
-        <v>689.4003266994483</v>
+        <v>701.0418942996629</v>
       </c>
       <c r="C5">
-        <v>1.947248635589016</v>
+        <v>2.261728394637732</v>
       </c>
       <c r="D5">
-        <v>0.6319951822128911</v>
+        <v>0.5814921208885685</v>
       </c>
       <c r="E5">
-        <v>0.1213492045104929</v>
+        <v>0.4021114024077352</v>
       </c>
       <c r="F5">
-        <v>64.0126486612</v>
+        <v>95.08300676656251</v>
       </c>
       <c r="G5">
-        <v>0.1938414998515946</v>
+        <v>0.1287416890915327</v>
       </c>
       <c r="H5">
-        <v>3.296296296296296</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -708,16 +694,13 @@
         <v>0.4611487805902014</v>
       </c>
       <c r="Q5">
-        <v>2.155129477973325</v>
+        <v>53.8427432568273</v>
       </c>
       <c r="R5">
-        <v>0.2901661958320036</v>
+        <v>0.2021585358630746</v>
       </c>
       <c r="S5">
-        <v>0.160709535150152</v>
-      </c>
-      <c r="T5">
-        <v>0.3876197644857202</v>
+        <v>0.4310571780827911</v>
       </c>
     </row>
     <row r="6">
@@ -727,25 +710,25 @@
         </is>
       </c>
       <c r="B6">
-        <v>464.5123518702242</v>
+        <v>480.0111760454392</v>
       </c>
       <c r="C6">
-        <v>1.432234262794714</v>
+        <v>1.84865571757305</v>
       </c>
       <c r="D6">
-        <v>0.496822022249841</v>
+        <v>0.3798587248873637</v>
       </c>
       <c r="E6">
-        <v>0.045343714753362</v>
+        <v>0.2559912061846156</v>
       </c>
       <c r="F6">
-        <v>35.9593211412</v>
+        <v>104.9201081617857</v>
       </c>
       <c r="G6">
-        <v>0.05339131064146539</v>
+        <v>0.1651999633930487</v>
       </c>
       <c r="H6">
-        <v>1.851851851851852</v>
+        <v>1.864406779661017</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -774,16 +757,13 @@
         <v>0.2147429000968968</v>
       </c>
       <c r="Q6">
-        <v>1.036141073848968</v>
+        <v>58.9614365055913</v>
       </c>
       <c r="R6">
-        <v>0.08272192028282797</v>
+        <v>0.3020226232484428</v>
       </c>
       <c r="S6">
-        <v>0.1353865041854264</v>
-      </c>
-      <c r="T6">
-        <v>0.2964556236757094</v>
+        <v>0.3801502907151748</v>
       </c>
     </row>
     <row r="7">
@@ -793,25 +773,25 @@
         </is>
       </c>
       <c r="B7">
-        <v>876.9293567024525</v>
+        <v>834.7057465626099</v>
       </c>
       <c r="C7">
-        <v>2.708056805399216</v>
+        <v>3.054211065243965</v>
       </c>
       <c r="D7">
-        <v>0.7447130435816957</v>
+        <v>0.7034258352032589</v>
       </c>
       <c r="E7">
-        <v>0.2336287846781446</v>
+        <v>0.6824439679874053</v>
       </c>
       <c r="F7">
-        <v>78.1513537172</v>
+        <v>190.1838700915625</v>
       </c>
       <c r="G7">
-        <v>0.2646275340176196</v>
+        <v>0.4812045968234252</v>
       </c>
       <c r="H7">
-        <v>12.85185185185185</v>
+        <v>12.89830508474576</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,16 +820,13 @@
         <v>0.6243504756959108</v>
       </c>
       <c r="Q7">
-        <v>3.859743076186436</v>
+        <v>79.74070770421616</v>
       </c>
       <c r="R7">
-        <v>0.6061769173633896</v>
+        <v>0.7074196364968555</v>
       </c>
       <c r="S7">
-        <v>0.2621910960408731</v>
-      </c>
-      <c r="T7">
-        <v>0.4691755328738116</v>
+        <v>0.6023658462599593</v>
       </c>
     </row>
     <row r="8">
@@ -859,22 +836,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>657.0426526658875</v>
+        <v>692.6924213740515</v>
       </c>
       <c r="C8">
-        <v>1.945600343904767</v>
+        <v>2.262530900179275</v>
       </c>
       <c r="D8">
-        <v>0.6125459917815566</v>
+        <v>0.5738753851058309</v>
       </c>
       <c r="E8">
-        <v>0.1211059506843051</v>
+        <v>0.4023952804604635</v>
       </c>
       <c r="F8">
-        <v>41.2355401532</v>
+        <v>116.0377657446875</v>
       </c>
       <c r="G8">
-        <v>0.07980692775573352</v>
+        <v>0.2064042362233141</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -906,16 +883,13 @@
         <v>0.5217929277201457</v>
       </c>
       <c r="Q8">
-        <v>1.389560270267715</v>
+        <v>57.51093874987679</v>
       </c>
       <c r="R8">
-        <v>0.1482407307513151</v>
+        <v>0.2737238705025282</v>
       </c>
       <c r="S8">
-        <v>0.1548245950020741</v>
-      </c>
-      <c r="T8">
-        <v>0.3245465917282926</v>
+        <v>0.4194639014490705</v>
       </c>
     </row>
     <row r="9">
@@ -925,22 +899,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>576.1427017766376</v>
+        <v>604.6068150246119</v>
       </c>
       <c r="C9">
-        <v>1.785966977601064</v>
+        <v>2.077015005533984</v>
       </c>
       <c r="D9">
-        <v>0.5639195500571393</v>
+        <v>0.4935200386302585</v>
       </c>
       <c r="E9">
-        <v>0.09754736119938923</v>
+        <v>0.3367709474237064</v>
       </c>
       <c r="F9">
-        <v>40.0482818796</v>
+        <v>98.8683452184375</v>
       </c>
       <c r="G9">
-        <v>0.07386286821236809</v>
+        <v>0.1427709139676277</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -972,16 +946,13 @@
         <v>0.1312653782063204</v>
       </c>
       <c r="Q9">
-        <v>2.567495039214939</v>
+        <v>62.40776578939912</v>
       </c>
       <c r="R9">
-        <v>0.3666128102901184</v>
+        <v>0.3692594182722592</v>
       </c>
       <c r="S9">
-        <v>0.1746890842429457</v>
-      </c>
-      <c r="T9">
-        <v>0.2862232214220031</v>
+        <v>0.3364964879525594</v>
       </c>
     </row>
     <row r="10">
@@ -991,25 +962,25 @@
         </is>
       </c>
       <c r="B10">
-        <v>950.9130416145175</v>
+        <v>912.9959398422051</v>
       </c>
       <c r="C10">
-        <v>2.6233511580021</v>
+        <v>2.774944281334617</v>
       </c>
       <c r="D10">
-        <v>0.7891823331596233</v>
+        <v>0.7748453992766966</v>
       </c>
       <c r="E10">
-        <v>0.2211279797381161</v>
+        <v>0.5836562254685655</v>
       </c>
       <c r="F10">
-        <v>79.6784137132</v>
+        <v>119.3581357134375</v>
       </c>
       <c r="G10">
-        <v>0.2722728254797649</v>
+        <v>0.2187101944766251</v>
       </c>
       <c r="H10">
-        <v>10.7962962962963</v>
+        <v>11.03333333333333</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1038,16 +1009,13 @@
         <v>0.2902390589132616</v>
       </c>
       <c r="Q10">
-        <v>4.078294161783221</v>
+        <v>82.012073006596</v>
       </c>
       <c r="R10">
-        <v>0.6466931295555873</v>
+        <v>0.7517332556213703</v>
       </c>
       <c r="S10">
-        <v>0.2518041922392355</v>
-      </c>
-      <c r="T10">
-        <v>0.4718574201739679</v>
+        <v>0.5603891394375248</v>
       </c>
     </row>
     <row r="11">
@@ -1057,25 +1025,25 @@
         </is>
       </c>
       <c r="B11">
-        <v>659.8557433919196</v>
+        <v>705.031891045062</v>
       </c>
       <c r="C11">
-        <v>2.233130154891505</v>
+        <v>2.407601046433697</v>
       </c>
       <c r="D11">
-        <v>0.6142368530336501</v>
+        <v>0.58513196154132</v>
       </c>
       <c r="E11">
-        <v>0.1635394151821023</v>
+        <v>0.4537123474411335</v>
       </c>
       <c r="F11">
-        <v>61.1355557432</v>
+        <v>120.089965424375</v>
       </c>
       <c r="G11">
-        <v>0.1794372105771712</v>
+        <v>0.2214225024290789</v>
       </c>
       <c r="H11">
-        <v>5.166666666666667</v>
+        <v>5.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,16 +1072,13 @@
         <v>0.3213345229889077</v>
       </c>
       <c r="Q11">
-        <v>2.417458139643524</v>
+        <v>66.71843961892247</v>
       </c>
       <c r="R11">
-        <v>0.3387981378390733</v>
+        <v>0.4533593021840931</v>
       </c>
       <c r="S11">
-        <v>0.1605393662912078</v>
-      </c>
-      <c r="T11">
-        <v>0.378032153837408</v>
+        <v>0.4687617659102406</v>
       </c>
     </row>
     <row r="12">
@@ -1123,25 +1088,25 @@
         </is>
       </c>
       <c r="B12">
-        <v>583.109034912637</v>
+        <v>633.0952679188338</v>
       </c>
       <c r="C12">
-        <v>1.697644652531016</v>
+        <v>2.054620898268954</v>
       </c>
       <c r="D12">
-        <v>0.5681067960139915</v>
+        <v>0.5195083878934385</v>
       </c>
       <c r="E12">
-        <v>0.08451280929549751</v>
+        <v>0.3288492631064082</v>
       </c>
       <c r="F12">
-        <v>59.763006962</v>
+        <v>99.45453668906251</v>
       </c>
       <c r="G12">
-        <v>0.1725654861486792</v>
+        <v>0.1449434573389538</v>
       </c>
       <c r="H12">
-        <v>3.111111111111111</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1170,16 +1135,13 @@
         <v>0.2271825491538669</v>
       </c>
       <c r="Q12">
-        <v>2.332909442000188</v>
+        <v>66.44681236399113</v>
       </c>
       <c r="R12">
-        <v>0.3231240314170564</v>
+        <v>0.4480599402953412</v>
       </c>
       <c r="S12">
-        <v>0.1334079099935809</v>
-      </c>
-      <c r="T12">
-        <v>0.3630799491101118</v>
+        <v>0.4377548012351757</v>
       </c>
     </row>
     <row r="13">
@@ -1189,25 +1151,25 @@
         </is>
       </c>
       <c r="B13">
-        <v>841.413155045985</v>
+        <v>814.3056057503242</v>
       </c>
       <c r="C13">
-        <v>2.680548594249792</v>
+        <v>2.903930960374873</v>
       </c>
       <c r="D13">
-        <v>0.7233653605344572</v>
+        <v>0.6848159799606366</v>
       </c>
       <c r="E13">
-        <v>0.2295691405765428</v>
+        <v>0.6292839319183426</v>
       </c>
       <c r="F13">
-        <v>111.7443072136</v>
+        <v>192.928677510625</v>
       </c>
       <c r="G13">
-        <v>0.4328120986234676</v>
+        <v>0.4913774046220325</v>
       </c>
       <c r="H13">
-        <v>6.555555555555555</v>
+        <v>6.559322033898305</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1236,16 +1198,13 @@
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>2.539175812312433</v>
+        <v>79.9970448625028</v>
       </c>
       <c r="R13">
-        <v>0.3613628349666473</v>
+        <v>0.7124206934329075</v>
       </c>
       <c r="S13">
-        <v>0.2016718471293336</v>
-      </c>
-      <c r="T13">
-        <v>0.5050595855614363</v>
+        <v>0.658513344656423</v>
       </c>
     </row>
     <row r="14">
@@ -1255,25 +1214,25 @@
         </is>
       </c>
       <c r="B14">
-        <v>601.8196013282181</v>
+        <v>662.3028872476706</v>
       </c>
       <c r="C14">
-        <v>1.799419929991905</v>
+        <v>2.123226916759468</v>
       </c>
       <c r="D14">
-        <v>0.5793531349479127</v>
+        <v>0.5461527906303022</v>
       </c>
       <c r="E14">
-        <v>0.09953273925708785</v>
+        <v>0.3531179340704553</v>
       </c>
       <c r="F14">
-        <v>25.2950142252</v>
+        <v>67.78081792354838</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.02755429151588618</v>
       </c>
       <c r="H14">
-        <v>0.9444444444444444</v>
+        <v>0.95</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1302,16 +1261,13 @@
         <v>0.7911186628975807</v>
       </c>
       <c r="Q14">
-        <v>0.6035046795562488</v>
+        <v>59.53439274016294</v>
       </c>
       <c r="R14">
-        <v>0.002517386384649483</v>
+        <v>0.3132008182870046</v>
       </c>
       <c r="S14">
-        <v>0.1161380623010923</v>
-      </c>
-      <c r="T14">
-        <v>0.2753123403496199</v>
+        <v>0.3778547477728379</v>
       </c>
     </row>
     <row r="15">
@@ -1321,25 +1277,25 @@
         </is>
       </c>
       <c r="B15">
-        <v>682.3257811817598</v>
+        <v>745.9491221775057</v>
       </c>
       <c r="C15">
-        <v>2.064475816133158</v>
+        <v>2.427065160490093</v>
       </c>
       <c r="D15">
-        <v>0.6277428931625112</v>
+        <v>0.622458358222127</v>
       </c>
       <c r="E15">
-        <v>0.138649516386767</v>
+        <v>0.4605975769010921</v>
       </c>
       <c r="F15">
-        <v>74.47090715375001</v>
+        <v>126.9768313448387</v>
       </c>
       <c r="G15">
-        <v>0.2462012202106107</v>
+        <v>0.2469466112817081</v>
       </c>
       <c r="H15">
-        <v>1.981481481481481</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1368,16 +1324,13 @@
         <v>0.3402736316214968</v>
       </c>
       <c r="Q15">
-        <v>1.231438563271949</v>
+        <v>79.09302956292436</v>
       </c>
       <c r="R15">
-        <v>0.1189272518667831</v>
+        <v>0.6947836406760127</v>
       </c>
       <c r="S15">
-        <v>0.1900188806640827</v>
-      </c>
-      <c r="T15">
-        <v>0.2946137106972522</v>
+        <v>0.437165158624029</v>
       </c>
     </row>
     <row r="16">
@@ -1387,22 +1340,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>689.6108122507695</v>
+        <v>714.1590786180997</v>
       </c>
       <c r="C16">
-        <v>2.479256042832511</v>
+        <v>2.624414273372065</v>
       </c>
       <c r="D16">
-        <v>0.6321216985244914</v>
+        <v>0.5934581609077576</v>
       </c>
       <c r="E16">
-        <v>0.1998625153576704</v>
+        <v>0.5304077887594206</v>
       </c>
       <c r="F16">
-        <v>97.4972370524</v>
+        <v>184.2882473682143</v>
       </c>
       <c r="G16">
-        <v>0.3614835299036266</v>
+        <v>0.4593542344259761</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -1434,16 +1387,13 @@
         <v>0.09713711073965478</v>
       </c>
       <c r="Q16">
-        <v>1.902551130038404</v>
+        <v>63.13664235242246</v>
       </c>
       <c r="R16">
-        <v>0.2433418210541713</v>
+        <v>0.3834795696361811</v>
       </c>
       <c r="S16">
-        <v>0.1642039281024077</v>
-      </c>
-      <c r="T16">
-        <v>0.3495061606710421</v>
+        <v>0.4516765065936149</v>
       </c>
     </row>
     <row r="17">
@@ -1453,22 +1403,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>-362.0518748214354</v>
+        <v>63.60968471467833</v>
       </c>
       <c r="C17">
-        <v>1.584181062135045</v>
+        <v>2.011711592971416</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.06776792563165331</v>
+        <v>0.313670539220751</v>
       </c>
       <c r="F17">
-        <v>46.580965416</v>
+        <v>85.71637923125</v>
       </c>
       <c r="G17">
-        <v>0.1065690289372644</v>
+        <v>0.09402708544534275</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1500,16 +1450,13 @@
         <v>0.06536386408450168</v>
       </c>
       <c r="Q17">
-        <v>1.279663954042972</v>
+        <v>62.34958801792048</v>
       </c>
       <c r="R17">
-        <v>0.1278675422350279</v>
+        <v>0.3681243883393301</v>
       </c>
       <c r="S17">
-        <v>0.1678917168888577</v>
-      </c>
-      <c r="T17">
-        <v>0.1245368266301708</v>
+        <v>0.1860029160505696</v>
       </c>
     </row>
     <row r="18">
@@ -1519,25 +1466,25 @@
         </is>
       </c>
       <c r="B18">
-        <v>797.1924656038281</v>
+        <v>799.4162616745616</v>
       </c>
       <c r="C18">
-        <v>2.642121951611116</v>
+        <v>2.781380475817904</v>
       </c>
       <c r="D18">
-        <v>0.6967856808864893</v>
+        <v>0.6712333022498698</v>
       </c>
       <c r="E18">
-        <v>0.2238981613810915</v>
+        <v>0.5859329628396042</v>
       </c>
       <c r="F18">
-        <v>136.2243085884</v>
+        <v>196.8196160846875</v>
       </c>
       <c r="G18">
-        <v>0.5553722770017252</v>
+        <v>0.5057980047687795</v>
       </c>
       <c r="H18">
-        <v>3.648148148148148</v>
+        <v>3.559322033898305</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1566,16 +1513,13 @@
         <v>0.3800503571189321</v>
       </c>
       <c r="Q18">
-        <v>2.560460464897154</v>
+        <v>75.00451243271422</v>
       </c>
       <c r="R18">
-        <v>0.3653087018938461</v>
+        <v>0.6150179637492951</v>
       </c>
       <c r="S18">
-        <v>0.1821903962478089</v>
-      </c>
-      <c r="T18">
-        <v>0.3832900610652369</v>
+        <v>0.4886782149597833</v>
       </c>
     </row>
     <row r="19">
@@ -1585,25 +1529,25 @@
         </is>
       </c>
       <c r="B19">
-        <v>927.2100813371653</v>
+        <v>917.5395358708413</v>
       </c>
       <c r="C19">
-        <v>2.482292313178938</v>
+        <v>2.73056528632354</v>
       </c>
       <c r="D19">
-        <v>0.7749352217095716</v>
+        <v>0.7789902561750838</v>
       </c>
       <c r="E19">
-        <v>0.2003106061817443</v>
+        <v>0.5679576140152887</v>
       </c>
       <c r="F19">
-        <v>93.86231739920001</v>
+        <v>123.234310468125</v>
       </c>
       <c r="G19">
-        <v>0.3432851485283125</v>
+        <v>0.233076076942331</v>
       </c>
       <c r="H19">
-        <v>11.92592592592593</v>
+        <v>12.15254237288136</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1632,16 +1576,13 @@
         <v>0.3886229581419586</v>
       </c>
       <c r="Q19">
-        <v>3.906252654340075</v>
+        <v>76.03843121720853</v>
       </c>
       <c r="R19">
-        <v>0.6147991208738268</v>
+        <v>0.6351893924374753</v>
       </c>
       <c r="S19">
-        <v>0.2392937685081673</v>
-      </c>
-      <c r="T19">
-        <v>0.5359131715339427</v>
+        <v>0.6185564065771568</v>
       </c>
     </row>
     <row r="20">
@@ -1651,25 +1592,25 @@
         </is>
       </c>
       <c r="B20">
-        <v>810.2287041847036</v>
+        <v>813.5264000739855</v>
       </c>
       <c r="C20">
-        <v>2.221810285043644</v>
+        <v>2.500077708360005</v>
       </c>
       <c r="D20">
-        <v>0.7046213580246169</v>
+        <v>0.6841051561984712</v>
       </c>
       <c r="E20">
-        <v>0.1618688360735901</v>
+        <v>0.4864250121536806</v>
       </c>
       <c r="F20">
-        <v>94.331812516</v>
+        <v>140.165478528125</v>
       </c>
       <c r="G20">
-        <v>0.345635695996907</v>
+        <v>0.2958263876869464</v>
       </c>
       <c r="H20">
-        <v>3.759259259259259</v>
+        <v>3.694915254237288</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1698,104 +1639,104 @@
         <v>0.2034185793155251</v>
       </c>
       <c r="Q20">
-        <v>1.577221861175118</v>
+        <v>71.16260398610156</v>
       </c>
       <c r="R20">
-        <v>0.1830304771246527</v>
+        <v>0.5400635442923848</v>
       </c>
       <c r="S20">
-        <v>0.1735674814922469</v>
-      </c>
-      <c r="T20">
-        <v>0.3625898011593008</v>
+        <v>0.4769163801276965</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B1A22</t>
+          <t>B2A01</t>
         </is>
       </c>
       <c r="B21">
-        <v>982.779108216858</v>
+        <v>790.0249197554833</v>
       </c>
       <c r="C21">
-        <v>2.839018103463625</v>
+        <v>2.375324300110834</v>
       </c>
       <c r="D21">
-        <v>0.8083360336698544</v>
+        <v>0.6626661303241366</v>
       </c>
       <c r="E21">
-        <v>0.2529559687810056</v>
+        <v>0.4422947815550168</v>
       </c>
       <c r="F21">
-        <v>105.8838912079167</v>
+        <v>112.8774740863333</v>
       </c>
       <c r="G21">
-        <v>0.4034716741671714</v>
+        <v>0.1946915603522473</v>
       </c>
       <c r="H21">
-        <v>32.85185185185185</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="J21">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>6.333333333333333</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="L21">
-        <v>0.7916666666666666</v>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="M21">
+        <v>-1.33318693909328</v>
+      </c>
+      <c r="N21">
+        <v>0.5519544837795801</v>
       </c>
       <c r="O21">
-        <v>0.5947681296885415</v>
+        <v>0.2280327668409885</v>
       </c>
       <c r="P21">
-        <v>0.7150963901185717</v>
+        <v>0.2170662973172846</v>
       </c>
       <c r="Q21">
-        <v>4.98284602843752</v>
+        <v>80.38763960534897</v>
       </c>
       <c r="R21">
-        <v>0.8143839706609451</v>
+        <v>0.7200410734080649</v>
       </c>
       <c r="S21">
-        <v>0.2777982644896537</v>
-      </c>
-      <c r="T21">
-        <v>0.5805298526505527</v>
+        <v>0.4817210942956662</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B2A01</t>
+          <t>B2A02</t>
         </is>
       </c>
       <c r="B22">
-        <v>827.5179842743217</v>
+        <v>873.7027658075027</v>
       </c>
       <c r="C22">
-        <v>2.222399237288418</v>
+        <v>3.219755117538084</v>
       </c>
       <c r="D22">
-        <v>0.7150134059986122</v>
+        <v>0.7390005348937705</v>
       </c>
       <c r="E22">
-        <v>0.1619557532669196</v>
+        <v>0.7410034679201478</v>
       </c>
       <c r="F22">
-        <v>77.94017594125</v>
+        <v>195.54534427125</v>
       </c>
       <c r="G22">
-        <v>0.2635702634115568</v>
+        <v>0.5010752973936624</v>
       </c>
       <c r="H22">
-        <v>3.555555555555555</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1803,65 +1744,56 @@
         </is>
       </c>
       <c r="J22">
-        <v>4</v>
-      </c>
-      <c r="K22">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="L22">
-        <v>0.5833333333333334</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>-1.33318693909328</v>
+        <v>-0.511202244335448</v>
       </c>
       <c r="N22">
-        <v>0.5519544837795801</v>
+        <v>0.9181636175828851</v>
       </c>
       <c r="O22">
-        <v>0.2280327668409885</v>
+        <v>0.08608989262336765</v>
       </c>
       <c r="P22">
-        <v>0.2170662973172846</v>
+        <v>0.02430653106461261</v>
       </c>
       <c r="Q22">
-        <v>5.028966557127412</v>
+        <v>77.71981399095652</v>
       </c>
       <c r="R22">
-        <v>0.8229340500243738</v>
+        <v>0.6679926389079232</v>
       </c>
       <c r="S22">
-        <v>0.2544337843007431</v>
-      </c>
-      <c r="T22">
-        <v>0.4462826714290504</v>
+        <v>0.5985903479605003</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B2A02</t>
+          <t>B2A04</t>
         </is>
       </c>
       <c r="B23">
-        <v>914.8376385850046</v>
+        <v>548.7226506533721</v>
       </c>
       <c r="C23">
-        <v>3.040924993516866</v>
+        <v>1.92094178688546</v>
       </c>
       <c r="D23">
-        <v>0.7674985315773335</v>
+        <v>0.4425401841835008</v>
       </c>
       <c r="E23">
-        <v>0.2827532577004839</v>
+        <v>0.2815616571454121</v>
       </c>
       <c r="F23">
-        <v>133.2872406672</v>
+        <v>119.3736232370968</v>
       </c>
       <c r="G23">
-        <v>0.5406677202976605</v>
+        <v>0.2187675943511546</v>
       </c>
       <c r="H23">
-        <v>1.981481481481481</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1869,59 +1801,62 @@
         </is>
       </c>
       <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
         <v>2</v>
       </c>
+      <c r="L23">
+        <v>0.25</v>
+      </c>
       <c r="M23">
-        <v>-0.511202244335448</v>
+        <v>-2.57209142287238</v>
       </c>
       <c r="N23">
-        <v>0.9181636175828851</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>0.08608989262336765</v>
+        <v>0.2169251495462083</v>
       </c>
       <c r="P23">
-        <v>0.02430653106461261</v>
+        <v>0.2019820479305677</v>
       </c>
       <c r="Q23">
-        <v>1.436201281210562</v>
+        <v>50.11073792661856</v>
       </c>
       <c r="R23">
-        <v>0.1568873000010577</v>
+        <v>0.129348291469426</v>
       </c>
       <c r="S23">
-        <v>0.2269023679670693</v>
-      </c>
-      <c r="T23">
-        <v>0.4167399037415861</v>
+        <v>0.2177428250114373</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B2A03</t>
+          <t>B2A05</t>
         </is>
       </c>
       <c r="B24">
-        <v>1145.358663001164</v>
+        <v>648.7983906320918</v>
       </c>
       <c r="C24">
-        <v>3.544633181031509</v>
+        <v>2.035724943587848</v>
       </c>
       <c r="D24">
-        <v>0.9060575422666076</v>
+        <v>0.533833428256634</v>
       </c>
       <c r="E24">
-        <v>0.3570901879088728</v>
+        <v>0.322165014161533</v>
       </c>
       <c r="F24">
-        <v>142.5673003768</v>
+        <v>80.2080049490625</v>
       </c>
       <c r="G24">
-        <v>0.5871287378423848</v>
+        <v>0.07361194357916995</v>
       </c>
       <c r="H24">
-        <v>34.27777777777778</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1929,59 +1864,56 @@
         </is>
       </c>
       <c r="J24">
-        <v>60</v>
-      </c>
-      <c r="K24">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="L24">
-        <v>0.5833333333333334</v>
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>-1.102399389618816</v>
+      </c>
+      <c r="N24">
+        <v>0.6547745352046623</v>
       </c>
       <c r="O24">
-        <v>0.2032358553309727</v>
+        <v>0.3374767695716056</v>
       </c>
       <c r="P24">
-        <v>0.1833918568580152</v>
+        <v>0.3656922885859016</v>
       </c>
       <c r="Q24">
-        <v>4.993074059988925</v>
+        <v>62.67410392395845</v>
       </c>
       <c r="R24">
-        <v>0.8162800998680531</v>
+        <v>0.374455591094319</v>
       </c>
       <c r="S24">
-        <v>0.2625608208348425</v>
-      </c>
-      <c r="T24">
-        <v>0.5279775112731585</v>
+        <v>0.38742213348037</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B2A04</t>
+          <t>B2A06</t>
         </is>
       </c>
       <c r="B25">
-        <v>518.2429384907324</v>
+        <v>953.7906142421343</v>
       </c>
       <c r="C25">
-        <v>1.587541858605282</v>
+        <v>2.598086318190543</v>
       </c>
       <c r="D25">
-        <v>0.5291178050086915</v>
+        <v>0.8120599946188712</v>
       </c>
       <c r="E25">
-        <v>0.06826390981226653</v>
+        <v>0.5210945463425779</v>
       </c>
       <c r="F25">
-        <v>44.40259668125</v>
+        <v>123.441344703125</v>
       </c>
       <c r="G25">
-        <v>0.09566293229874817</v>
+        <v>0.2338433874158308</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>3.677966101694915</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1989,65 +1921,62 @@
         </is>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L25">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M25">
-        <v>-2.57209142287238</v>
+        <v>-1.090517443382615</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>0.6600681583910872</v>
       </c>
       <c r="O25">
-        <v>0.2169251495462083</v>
+        <v>0.2869006174457089</v>
       </c>
       <c r="P25">
-        <v>0.2019820479305677</v>
+        <v>0.2970093954467886</v>
       </c>
       <c r="Q25">
-        <v>1.062002979425445</v>
+        <v>72.39616613418542</v>
       </c>
       <c r="R25">
-        <v>0.08751634375215032</v>
+        <v>0.5641299519016463</v>
       </c>
       <c r="S25">
-        <v>0.06739172595307573</v>
-      </c>
-      <c r="T25">
-        <v>0.1624918455944375</v>
+        <v>0.4649817286833527</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B2A05</t>
+          <t>B2A08</t>
         </is>
       </c>
       <c r="B26">
-        <v>638.6032790314146</v>
+        <v>857.7172489851876</v>
       </c>
       <c r="C26">
-        <v>1.962920347908493</v>
+        <v>2.350635469275505</v>
       </c>
       <c r="D26">
-        <v>0.6014626583849895</v>
+        <v>0.7244178829023376</v>
       </c>
       <c r="E26">
-        <v>0.1236620257308251</v>
+        <v>0.4335613624583748</v>
       </c>
       <c r="F26">
-        <v>52.3862463348</v>
+        <v>177.1940864143333</v>
       </c>
       <c r="G26">
-        <v>0.1356334172128486</v>
+        <v>0.4330618485285115</v>
       </c>
       <c r="H26">
-        <v>0.9814814814814815</v>
+        <v>1.627118644067797</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2055,59 +1984,62 @@
         </is>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="L26">
+        <v>0.3333333333333333</v>
       </c>
       <c r="M26">
-        <v>-1.102399389618816</v>
+        <v>-1.598882708023645</v>
       </c>
       <c r="N26">
-        <v>0.6547745352046623</v>
+        <v>0.4335821855899429</v>
       </c>
       <c r="O26">
-        <v>0.3374767695716056</v>
+        <v>0.0827885435279237</v>
       </c>
       <c r="P26">
-        <v>0.3656922885859016</v>
+        <v>0.01982326775559581</v>
       </c>
       <c r="Q26">
-        <v>0.8559792271251629</v>
+        <v>59.67827330488004</v>
       </c>
       <c r="R26">
-        <v>0.04932251807502108</v>
+        <v>0.3160078826273875</v>
       </c>
       <c r="S26">
-        <v>0.156364379748628</v>
-      </c>
-      <c r="T26">
-        <v>0.2981302604204109</v>
+        <v>0.3848268233136405</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B2A06</t>
+          <t>B2A09</t>
         </is>
       </c>
       <c r="B27">
-        <v>956.6004474053108</v>
+        <v>1010.778519775807</v>
       </c>
       <c r="C27">
-        <v>2.251747536584524</v>
+        <v>2.521925385274342</v>
       </c>
       <c r="D27">
-        <v>0.7926008557076495</v>
+        <v>0.8640467275694197</v>
       </c>
       <c r="E27">
-        <v>0.166286956393226</v>
+        <v>0.4941534023740833</v>
       </c>
       <c r="F27">
-        <v>63.83012122</v>
+        <v>168.7766671846875</v>
       </c>
       <c r="G27">
-        <v>0.1929276683770822</v>
+        <v>0.4018652015838838</v>
       </c>
       <c r="H27">
-        <v>3.685185185185185</v>
+        <v>3.933333333333333</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2118,62 +2050,59 @@
         <v>4</v>
       </c>
       <c r="K27">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>-1.090517443382615</v>
+        <v>-1.518151748796495</v>
       </c>
       <c r="N27">
-        <v>0.6600681583910872</v>
+        <v>0.4695492964598048</v>
       </c>
       <c r="O27">
-        <v>0.2869006174457089</v>
+        <v>0.472248451133825</v>
       </c>
       <c r="P27">
-        <v>0.2970093954467886</v>
+        <v>0.5487135073586293</v>
       </c>
       <c r="Q27">
-        <v>2.25085548316566</v>
+        <v>72.11785885738277</v>
       </c>
       <c r="R27">
-        <v>0.3079124135096388</v>
+        <v>0.5587002648975824</v>
       </c>
       <c r="S27">
-        <v>0.2291827418108969</v>
-      </c>
-      <c r="T27">
-        <v>0.3515818570378795</v>
+        <v>0.4767183428919147</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B2A08</t>
+          <t>B2A10</t>
         </is>
       </c>
       <c r="B28">
-        <v>858.5921718212161</v>
+        <v>1107.679249668098</v>
       </c>
       <c r="C28">
-        <v>2.174151864269008</v>
+        <v>3.62140707432442</v>
       </c>
       <c r="D28">
-        <v>0.7336911326631342</v>
+        <v>0.9524435956495637</v>
       </c>
       <c r="E28">
-        <v>0.1548354370009114</v>
+        <v>0.8830837022171001</v>
       </c>
       <c r="F28">
-        <v>76.80272141</v>
+        <v>232.0746173662963</v>
       </c>
       <c r="G28">
-        <v>0.2578755484434986</v>
+        <v>0.6364601231697685</v>
       </c>
       <c r="H28">
-        <v>1.62962962962963</v>
+        <v>12.86440677966102</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2181,65 +2110,62 @@
         </is>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K28">
-        <v>2.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="L28">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="M28">
-        <v>-1.598882708023645</v>
+        <v>-1.122665910493637</v>
       </c>
       <c r="N28">
-        <v>0.4335821855899429</v>
+        <v>0.6457454314973707</v>
       </c>
       <c r="O28">
-        <v>0.0827885435279237</v>
+        <v>0.1755318038826786</v>
       </c>
       <c r="P28">
-        <v>0.01982326775559581</v>
+        <v>0.1457694928551716</v>
       </c>
       <c r="Q28">
-        <v>1.090745637070177</v>
+        <v>88.456374931675</v>
       </c>
       <c r="R28">
-        <v>0.09284481701469087</v>
+        <v>0.8774595492880565</v>
       </c>
       <c r="S28">
-        <v>0.1853852287088332</v>
-      </c>
-      <c r="T28">
-        <v>0.2764213688137425</v>
+        <v>0.6451374135252902</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B2A09</t>
+          <t>B2A12</t>
         </is>
       </c>
       <c r="B29">
-        <v>1029.288345796775</v>
+        <v>845.6928104684499</v>
       </c>
       <c r="C29">
-        <v>2.439337530630742</v>
+        <v>2.759213488094072</v>
       </c>
       <c r="D29">
-        <v>0.8362912883513184</v>
+        <v>0.7134486909624694</v>
       </c>
       <c r="E29">
-        <v>0.1939713670120237</v>
+        <v>0.5780916197159226</v>
       </c>
       <c r="F29">
-        <v>67.7049339964</v>
+        <v>164.713646173125</v>
       </c>
       <c r="G29">
-        <v>0.2123270849778836</v>
+        <v>0.3868068293479019</v>
       </c>
       <c r="H29">
-        <v>3.925925925925926</v>
+        <v>6.135593220338983</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2247,65 +2173,62 @@
         </is>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="M29">
-        <v>-1.518151748796495</v>
+        <v>-1.468379965955051</v>
       </c>
       <c r="N29">
-        <v>0.4695492964598048</v>
+        <v>0.4917235310878367</v>
       </c>
       <c r="O29">
-        <v>0.472248451133825</v>
+        <v>0.1496236035425811</v>
       </c>
       <c r="P29">
-        <v>0.5487135073586293</v>
+        <v>0.1105859116496234</v>
       </c>
       <c r="Q29">
-        <v>1.557222072208001</v>
+        <v>76.94415348095713</v>
       </c>
       <c r="R29">
-        <v>0.1793228053399155</v>
+        <v>0.6528597475257988</v>
       </c>
       <c r="S29">
-        <v>0.2516616844716736</v>
-      </c>
-      <c r="T29">
-        <v>0.3364796292464061</v>
+        <v>0.4726451900413647</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B2A10</t>
+          <t>B2A13</t>
         </is>
       </c>
       <c r="B30">
-        <v>1228.302213247796</v>
+        <v>797.0526848735647</v>
       </c>
       <c r="C30">
-        <v>3.558252237712686</v>
+        <v>2.48792606317468</v>
       </c>
       <c r="D30">
-        <v>0.9559123279389198</v>
+        <v>0.6690771493818031</v>
       </c>
       <c r="E30">
-        <v>0.3591000795308614</v>
+        <v>0.4821264930854841</v>
       </c>
       <c r="F30">
-        <v>192.7909867556</v>
+        <v>93.236065658125</v>
       </c>
       <c r="G30">
-        <v>0.8385757809677933</v>
+        <v>0.1218965542449143</v>
       </c>
       <c r="H30">
-        <v>12.72222222222222</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2313,65 +2236,62 @@
         </is>
       </c>
       <c r="J30">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="L30">
-        <v>0.375</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="M30">
-        <v>-1.122665910493637</v>
+        <v>-2.47887339261411</v>
       </c>
       <c r="N30">
-        <v>0.6457454314973707</v>
+        <v>0.04153032815992834</v>
       </c>
       <c r="O30">
-        <v>0.1755318038826786</v>
+        <v>0.2687833024585698</v>
       </c>
       <c r="P30">
-        <v>0.1457694928551716</v>
+        <v>0.2724059102680065</v>
       </c>
       <c r="Q30">
-        <v>2.963281691573024</v>
+        <v>74.87135259237039</v>
       </c>
       <c r="R30">
-        <v>0.4399859346834002</v>
+        <v>0.6124200573528666</v>
       </c>
       <c r="S30">
-        <v>0.2752522366203629</v>
-      </c>
-      <c r="T30">
-        <v>0.504417660511735</v>
+        <v>0.3439699751180481</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B2A12</t>
+          <t>B2A14</t>
         </is>
       </c>
       <c r="B31">
-        <v>857.0664466363648</v>
+        <v>1004.951093615742</v>
       </c>
       <c r="C31">
-        <v>2.462653275859922</v>
+        <v>3.163390120458246</v>
       </c>
       <c r="D31">
-        <v>0.7327740667567505</v>
+        <v>0.8587307075343737</v>
       </c>
       <c r="E31">
-        <v>0.1974122896907081</v>
+        <v>0.7210649319415701</v>
       </c>
       <c r="F31">
-        <v>101.5226671016</v>
+        <v>144.923307941875</v>
       </c>
       <c r="G31">
-        <v>0.3816370183502008</v>
+        <v>0.313459859466606</v>
       </c>
       <c r="H31">
-        <v>6.074074074074074</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2382,62 +2302,59 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="L31">
-        <v>0.375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="M31">
-        <v>-1.468379965955051</v>
+        <v>-1.785782758889025</v>
       </c>
       <c r="N31">
-        <v>0.4917235310878367</v>
+        <v>0.350314813129475</v>
       </c>
       <c r="O31">
-        <v>0.1496236035425811</v>
+        <v>0.1870355989054326</v>
       </c>
       <c r="P31">
-        <v>0.1105859116496234</v>
+        <v>0.1613917553451152</v>
       </c>
       <c r="Q31">
-        <v>2.951371914817594</v>
+        <v>76.28621821905159</v>
       </c>
       <c r="R31">
-        <v>0.4377780342244889</v>
+        <v>0.6400236385238157</v>
       </c>
       <c r="S31">
-        <v>0.2632556384061693</v>
-      </c>
-      <c r="T31">
-        <v>0.3737708112707222</v>
+        <v>0.5361884341820413</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B2A13</t>
+          <t>B2A15</t>
         </is>
       </c>
       <c r="B32">
-        <v>855.92110160506</v>
+        <v>736.0154404505465</v>
       </c>
       <c r="C32">
-        <v>2.592476867396955</v>
+        <v>2.332496835604216</v>
       </c>
       <c r="D32">
-        <v>0.7320856355178325</v>
+        <v>0.6133964414115498</v>
       </c>
       <c r="E32">
-        <v>0.2165715717963027</v>
+        <v>0.4271450080044754</v>
       </c>
       <c r="F32">
-        <v>65.1453640424</v>
+        <v>67.318532718125</v>
       </c>
       <c r="G32">
-        <v>0.1995124880613656</v>
+        <v>0.02584096965940489</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2448,62 +2365,59 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>1.666666666666667</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="L32">
-        <v>0.2083333333333333</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="M32">
-        <v>-2.47887339261411</v>
+        <v>-2.447393696741595</v>
       </c>
       <c r="N32">
-        <v>0.04153032815992834</v>
+        <v>0.05555510530162636</v>
       </c>
       <c r="O32">
-        <v>0.2687833024585698</v>
+        <v>0.3451972616050876</v>
       </c>
       <c r="P32">
-        <v>0.2724059102680065</v>
+        <v>0.3761767898187565</v>
       </c>
       <c r="Q32">
-        <v>1.728354121261013</v>
+        <v>52.66464479745166</v>
       </c>
       <c r="R32">
-        <v>0.2110482135820394</v>
+        <v>0.1791742072897486</v>
       </c>
       <c r="S32">
-        <v>0.2320791337767583</v>
-      </c>
-      <c r="T32">
-        <v>0.2641958268119458</v>
+        <v>0.3169935983074612</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B2A14</t>
+          <t>B2A16</t>
         </is>
       </c>
       <c r="B33">
-        <v>1177.519511472431</v>
+        <v>877.0060330270752</v>
       </c>
       <c r="C33">
-        <v>3.403669917036881</v>
+        <v>2.576887445112982</v>
       </c>
       <c r="D33">
-        <v>0.9253884269804534</v>
+        <v>0.7420139123674653</v>
       </c>
       <c r="E33">
-        <v>0.3362869201096756</v>
+        <v>0.5135956637831848</v>
       </c>
       <c r="F33">
-        <v>61.1306341656</v>
+        <v>173.841501374375</v>
       </c>
       <c r="G33">
-        <v>0.1794125704875191</v>
+        <v>0.4206364947484525</v>
       </c>
       <c r="H33">
-        <v>6.037037037037037</v>
+        <v>3.610169491525424</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2511,7 +2425,7 @@
         </is>
       </c>
       <c r="J33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K33">
         <v>5.666666666666667</v>
@@ -2520,56 +2434,53 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="M33">
-        <v>-1.785782758889025</v>
+        <v>-2.044371416713645</v>
       </c>
       <c r="N33">
-        <v>0.350314813129475</v>
+        <v>0.2351088622191451</v>
       </c>
       <c r="O33">
-        <v>0.1870355989054326</v>
+        <v>0.1479047577539238</v>
       </c>
       <c r="P33">
-        <v>0.1613917553451152</v>
+        <v>0.1082517028048877</v>
       </c>
       <c r="Q33">
-        <v>2.4032244352052</v>
+        <v>68.13236753508144</v>
       </c>
       <c r="R33">
-        <v>0.3361594147792935</v>
+        <v>0.4809445889191414</v>
       </c>
       <c r="S33">
-        <v>0.2348699485863942</v>
-      </c>
-      <c r="T33">
-        <v>0.4040196478439074</v>
+        <v>0.4584120797393729</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B2A15</t>
+          <t>B2A17</t>
         </is>
       </c>
       <c r="B34">
-        <v>717.6041019280676</v>
+        <v>985.8426334202379</v>
       </c>
       <c r="C34">
-        <v>2.210539761878858</v>
+        <v>2.923565604627012</v>
       </c>
       <c r="D34">
-        <v>0.6489475934008841</v>
+        <v>0.8412991769670165</v>
       </c>
       <c r="E34">
-        <v>0.1602055395168147</v>
+        <v>0.6362294846750176</v>
       </c>
       <c r="F34">
-        <v>30.4613218792</v>
+        <v>124.1271808390625</v>
       </c>
       <c r="G34">
-        <v>0.02586534117939243</v>
+        <v>0.2363852339380231</v>
       </c>
       <c r="H34">
-        <v>0.7037037037037037</v>
+        <v>6.220338983050848</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2577,65 +2488,62 @@
         </is>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>4.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="L34">
-        <v>0.5416666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="M34">
-        <v>-2.447393696741595</v>
+        <v>-0.846345379850909</v>
       </c>
       <c r="N34">
-        <v>0.05555510530162636</v>
+        <v>0.7688512542992849</v>
       </c>
       <c r="O34">
-        <v>0.3451972616050876</v>
+        <v>0.486419836610353</v>
       </c>
       <c r="P34">
-        <v>0.3761767898187565</v>
+        <v>0.5679583829255702</v>
       </c>
       <c r="Q34">
-        <v>0.7129800354265221</v>
+        <v>75.21099306353558</v>
       </c>
       <c r="R34">
-        <v>0.02281253493604877</v>
+        <v>0.6190463355929701</v>
       </c>
       <c r="S34">
-        <v>0.9745408842539789</v>
-      </c>
-      <c r="T34">
-        <v>0.3507213068842711</v>
+        <v>0.5599671240568403</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B2A16</t>
+          <t>B2A18</t>
         </is>
       </c>
       <c r="B35">
-        <v>861.6532718160278</v>
+        <v>1091.19812954318</v>
       </c>
       <c r="C35">
-        <v>2.15263714219207</v>
+        <v>3.047672135596225</v>
       </c>
       <c r="D35">
-        <v>0.7355310645651214</v>
+        <v>0.9374088337533967</v>
       </c>
       <c r="E35">
-        <v>0.1516603081601881</v>
+        <v>0.6801308891122624</v>
       </c>
       <c r="F35">
-        <v>110.2395217592</v>
+        <v>175.416226305</v>
       </c>
       <c r="G35">
-        <v>0.4252783256106065</v>
+        <v>0.4264727417447518</v>
       </c>
       <c r="H35">
-        <v>3.611111111111111</v>
+        <v>11.2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2643,65 +2551,62 @@
         </is>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K35">
-        <v>5.666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L35">
-        <v>0.7083333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M35">
-        <v>-2.044371416713645</v>
+        <v>-1.54801040680585</v>
       </c>
       <c r="N35">
-        <v>0.2351088622191451</v>
+        <v>0.4562467211735867</v>
       </c>
       <c r="O35">
-        <v>0.1479047577539238</v>
+        <v>0.2793487897798765</v>
       </c>
       <c r="P35">
-        <v>0.1082517028048877</v>
+        <v>0.2867539420211062</v>
       </c>
       <c r="Q35">
-        <v>2.965130262270036</v>
+        <v>75.34812239283114</v>
       </c>
       <c r="R35">
-        <v>0.4403286329702006</v>
+        <v>0.6217216854641848</v>
       </c>
       <c r="S35">
-        <v>0.2447513819859251</v>
-      </c>
-      <c r="T35">
-        <v>0.381155451456176</v>
+        <v>0.5107716399908507</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B2A17</t>
+          <t>B2A19</t>
         </is>
       </c>
       <c r="B36">
-        <v>1007.797378137004</v>
+        <v>971.6103559477901</v>
       </c>
       <c r="C36">
-        <v>2.529344489221601</v>
+        <v>2.805361940402622</v>
       </c>
       <c r="D36">
-        <v>0.823373736795078</v>
+        <v>0.8283159026861067</v>
       </c>
       <c r="E36">
-        <v>0.2072545360469593</v>
+        <v>0.5944161584257603</v>
       </c>
       <c r="F36">
-        <v>89.070791474</v>
+        <v>161.3252078546875</v>
       </c>
       <c r="G36">
-        <v>0.3192961681722459</v>
+        <v>0.3742485961139383</v>
       </c>
       <c r="H36">
-        <v>6.25925925925926</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2709,7 +2614,7 @@
         </is>
       </c>
       <c r="J36">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K36">
         <v>2</v>
@@ -2718,56 +2623,53 @@
         <v>0.25</v>
       </c>
       <c r="M36">
-        <v>-0.846345379850909</v>
+        <v>-1.820442695176075</v>
       </c>
       <c r="N36">
-        <v>0.7688512542992849</v>
+        <v>0.3348731810330309</v>
       </c>
       <c r="O36">
-        <v>0.486419836610353</v>
+        <v>0.2218767116537631</v>
       </c>
       <c r="P36">
-        <v>0.5679583829255702</v>
+        <v>0.208706316124366</v>
       </c>
       <c r="Q36">
-        <v>1.689488470807592</v>
+        <v>67.48794969187188</v>
       </c>
       <c r="R36">
-        <v>0.2038430837769933</v>
+        <v>0.4683722004833799</v>
       </c>
       <c r="S36">
-        <v>0.2232025060676819</v>
-      </c>
-      <c r="T36">
-        <v>0.4204724585104767</v>
+        <v>0.4369903364095117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B2A18</t>
+          <t>B2A20</t>
         </is>
       </c>
       <c r="B37">
-        <v>1199.117536403405</v>
+        <v>962.3463114578503</v>
       </c>
       <c r="C37">
-        <v>2.938898922213582</v>
+        <v>2.61686311036833</v>
       </c>
       <c r="D37">
-        <v>0.9383703273292716</v>
+        <v>0.8198648567592489</v>
       </c>
       <c r="E37">
-        <v>0.2676963157450034</v>
+        <v>0.5277366427817703</v>
       </c>
       <c r="F37">
-        <v>110.9779696704</v>
+        <v>125.714529449375</v>
       </c>
       <c r="G37">
-        <v>0.4289753967967581</v>
+        <v>0.2422682668276714</v>
       </c>
       <c r="H37">
-        <v>11.22222222222222</v>
+        <v>1.88135593220339</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2775,65 +2677,62 @@
         </is>
       </c>
       <c r="J37">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>1.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L37">
-        <v>0.1666666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="M37">
-        <v>-1.54801040680585</v>
+        <v>-1.485043139252253</v>
       </c>
       <c r="N37">
-        <v>0.4562467211735867</v>
+        <v>0.4842997842729641</v>
       </c>
       <c r="O37">
-        <v>0.2793487897798765</v>
+        <v>0.2685142008552549</v>
       </c>
       <c r="P37">
-        <v>0.2867539420211062</v>
+        <v>0.2720404677444623</v>
       </c>
       <c r="Q37">
-        <v>2.343764760437876</v>
+        <v>67.71297343870387</v>
       </c>
       <c r="R37">
-        <v>0.3251364505456744</v>
+        <v>0.4727623426593815</v>
       </c>
       <c r="S37">
-        <v>0.2245429766960785</v>
-      </c>
-      <c r="T37">
-        <v>0.3867985996217682</v>
+        <v>0.408662718244595</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B2A19</t>
+          <t>B2A21</t>
         </is>
       </c>
       <c r="B38">
-        <v>1007.335780123657</v>
+        <v>1151.611594239395</v>
       </c>
       <c r="C38">
-        <v>2.652072847749746</v>
+        <v>3.091423669845631</v>
       </c>
       <c r="D38">
-        <v>0.823096284600739</v>
+        <v>0.9925205039642586</v>
       </c>
       <c r="E38">
-        <v>0.2253667082304452</v>
+        <v>0.6956075427970684</v>
       </c>
       <c r="F38">
-        <v>100.557466054</v>
+        <v>151.1668673634375</v>
       </c>
       <c r="G38">
-        <v>0.3768046978468813</v>
+        <v>0.3365997451772152</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>6.915254237288136</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2841,65 +2740,62 @@
         </is>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="L38">
-        <v>0.25</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="M38">
-        <v>-1.820442695176075</v>
+        <v>-1.057303568606605</v>
       </c>
       <c r="N38">
-        <v>0.3348731810330309</v>
+        <v>0.6748655437798236</v>
       </c>
       <c r="O38">
-        <v>0.2218767116537631</v>
+        <v>0.3533872806922469</v>
       </c>
       <c r="P38">
-        <v>0.208706316124366</v>
+        <v>0.3872989132331756</v>
       </c>
       <c r="Q38">
-        <v>1.792634842757805</v>
+        <v>80.03361241972343</v>
       </c>
       <c r="R38">
-        <v>0.2229649301928028</v>
+        <v>0.7131341149161409</v>
       </c>
       <c r="S38">
-        <v>0.1930623898842926</v>
-      </c>
-      <c r="T38">
-        <v>0.3293593134890697</v>
+        <v>0.6261942424572879</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B2A20</t>
+          <t>B2A22</t>
         </is>
       </c>
       <c r="B39">
-        <v>1001.743157216678</v>
+        <v>1159.810624825328</v>
       </c>
       <c r="C39">
-        <v>2.641252258387419</v>
+        <v>3.445955299958285</v>
       </c>
       <c r="D39">
-        <v>0.8197347330931846</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0.2237698126147321</v>
+        <v>0.8210194478581516</v>
       </c>
       <c r="F39">
-        <v>90.6913976952</v>
+        <v>181.2209807528125</v>
       </c>
       <c r="G39">
-        <v>0.3274098028289681</v>
+        <v>0.4479863280552536</v>
       </c>
       <c r="H39">
-        <v>1.87037037037037</v>
+        <v>11.22033898305085</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2907,197 +2803,188 @@
         </is>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K39">
-        <v>0.3333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="L39">
-        <v>0.04166666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="M39">
-        <v>-1.485043139252253</v>
+        <v>-0.731112442471976</v>
       </c>
       <c r="N39">
-        <v>0.4842997842729641</v>
+        <v>0.8201896240429966</v>
       </c>
       <c r="O39">
-        <v>0.2685142008552549</v>
+        <v>0.1799247235403907</v>
       </c>
       <c r="P39">
-        <v>0.2720404677444623</v>
+        <v>0.151735119316202</v>
       </c>
       <c r="Q39">
-        <v>1.507974293939214</v>
+        <v>78.15316550397495</v>
       </c>
       <c r="R39">
-        <v>0.1701929791078292</v>
+        <v>0.6764471899547364</v>
       </c>
       <c r="S39">
-        <v>0.230276263816248</v>
-      </c>
-      <c r="T39">
-        <v>0.3211738137681319</v>
+        <v>0.6370063394134295</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B2A21</t>
+          <t>B3A01</t>
         </is>
       </c>
       <c r="B40">
-        <v>1210.126021964464</v>
+        <v>769.90286227345</v>
       </c>
       <c r="C40">
-        <v>2.844564490838305</v>
+        <v>2.366237997369227</v>
       </c>
       <c r="D40">
-        <v>0.9449871852596519</v>
+        <v>0.6443099542383888</v>
       </c>
       <c r="E40">
-        <v>0.2537745010610041</v>
+        <v>0.4390805957391429</v>
       </c>
       <c r="F40">
-        <v>87.2339902252</v>
+        <v>133.0338306171875</v>
       </c>
       <c r="G40">
-        <v>0.3101001438235678</v>
+        <v>0.2693950675945206</v>
       </c>
       <c r="H40">
-        <v>6.87037037037037</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="J40">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>4.666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L40">
-        <v>0.5833333333333334</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M40">
-        <v>-1.057303568606605</v>
+        <v>-1.536001281277885</v>
       </c>
       <c r="N40">
-        <v>0.6748655437798236</v>
+        <v>0.4615970050479438</v>
       </c>
       <c r="O40">
-        <v>0.3533872806922469</v>
+        <v>0.4548407613285498</v>
       </c>
       <c r="P40">
-        <v>0.3872989132331756</v>
+        <v>0.5250736998913001</v>
       </c>
       <c r="Q40">
-        <v>3.401077723047435</v>
+        <v>69.09029773310604</v>
       </c>
       <c r="R40">
-        <v>0.5211469907343621</v>
+        <v>0.4996335043034948</v>
       </c>
       <c r="S40">
-        <v>0.2749147008311783</v>
-      </c>
-      <c r="T40">
-        <v>0.4938026640070121</v>
+        <v>0.4174890228783035</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B2A22</t>
+          <t>B3A02</t>
         </is>
       </c>
       <c r="B41">
-        <v>1234.640977423058</v>
+        <v>696.5614238650267</v>
       </c>
       <c r="C41">
-        <v>3.409601048929084</v>
+        <v>1.964231324205769</v>
       </c>
       <c r="D41">
-        <v>0.9597223617323291</v>
+        <v>0.5774048497773214</v>
       </c>
       <c r="E41">
-        <v>0.3371622327380108</v>
+        <v>0.2968748841847817</v>
       </c>
       <c r="F41">
-        <v>112.3924553636</v>
+        <v>108.986184225625</v>
       </c>
       <c r="G41">
-        <v>0.4360570801765042</v>
+        <v>0.1802696582666082</v>
       </c>
       <c r="H41">
-        <v>11.16666666666667</v>
+        <v>1.932203389830508</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="J41">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>4.333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L41">
-        <v>0.5416666666666666</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M41">
-        <v>-0.731112442471976</v>
+        <v>-1.186029765726801</v>
       </c>
       <c r="N41">
-        <v>0.8201896240429966</v>
+        <v>0.61751568137263</v>
       </c>
       <c r="O41">
-        <v>0.1799247235403907</v>
+        <v>0.1200298150105244</v>
       </c>
       <c r="P41">
-        <v>0.151735119316202</v>
+        <v>0.07039726680631563</v>
       </c>
       <c r="Q41">
-        <v>2.189137107426769</v>
+        <v>67.07931202238098</v>
       </c>
       <c r="R41">
-        <v>0.2964707187646027</v>
+        <v>0.4603998087123266</v>
       </c>
       <c r="S41">
-        <v>0.2671520248835246</v>
-      </c>
-      <c r="T41">
-        <v>0.4762694785401046</v>
+        <v>0.3265993546361881</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B3A01</t>
+          <t>B3A03</t>
         </is>
       </c>
       <c r="B42">
-        <v>738.9485760541409</v>
+        <v>890.8958090422312</v>
       </c>
       <c r="C42">
-        <v>1.990728391365028</v>
+        <v>2.573170232495415</v>
       </c>
       <c r="D42">
-        <v>0.6617770922549774</v>
+        <v>0.7546847426020699</v>
       </c>
       <c r="E42">
-        <v>0.1277659188913868</v>
+        <v>0.5122807381847606</v>
       </c>
       <c r="F42">
-        <v>55.39370319</v>
+        <v>119.8886665934375</v>
       </c>
       <c r="G42">
-        <v>0.150690379138417</v>
+        <v>0.2206764485154273</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>3.491525423728814</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3105,65 +2992,62 @@
         </is>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>0.6666666666666666</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="L42">
-        <v>0.08333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="M42">
-        <v>-1.536001281277885</v>
+        <v>-0.9956581805243985</v>
       </c>
       <c r="N42">
-        <v>0.4615970050479438</v>
+        <v>0.7023296855290859</v>
       </c>
       <c r="O42">
-        <v>0.4548407613285498</v>
+        <v>0.3940111154255836</v>
       </c>
       <c r="P42">
-        <v>0.5250736998913001</v>
+        <v>0.4424664651842483</v>
       </c>
       <c r="Q42">
-        <v>2.748694971202441</v>
+        <v>66.80099591164563</v>
       </c>
       <c r="R42">
-        <v>0.4002046585006649</v>
+        <v>0.4549699493610279</v>
       </c>
       <c r="S42">
-        <v>0.1459900740925717</v>
-      </c>
-      <c r="T42">
-        <v>0.3195540201438244</v>
+        <v>0.4827249565776124</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B3A02</t>
+          <t>B3A04</t>
         </is>
       </c>
       <c r="B43">
-        <v>677.2660150068546</v>
+        <v>772.0165795662651</v>
       </c>
       <c r="C43">
-        <v>1.797527951189686</v>
+        <v>2.672861675954276</v>
       </c>
       <c r="D43">
-        <v>0.6247016252465389</v>
+        <v>0.6462381748916222</v>
       </c>
       <c r="E43">
-        <v>0.09925352224282744</v>
+        <v>0.5475455574012923</v>
       </c>
       <c r="F43">
-        <v>37.8631158088</v>
+        <v>155.2948253259375</v>
       </c>
       <c r="G43">
-        <v>0.06292274041894994</v>
+        <v>0.3518987868009025</v>
       </c>
       <c r="H43">
-        <v>1.925925925925926</v>
+        <v>6.35593220338983</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3171,65 +3055,56 @@
         </is>
       </c>
       <c r="J43">
-        <v>2</v>
-      </c>
-      <c r="K43">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="L43">
-        <v>0.08333333333333333</v>
+        <v>8</v>
       </c>
       <c r="M43">
-        <v>-1.186029765726801</v>
+        <v>-1.719018652508012</v>
       </c>
       <c r="N43">
-        <v>0.61751568137263</v>
+        <v>0.3800594369927521</v>
       </c>
       <c r="O43">
-        <v>0.1200298150105244</v>
+        <v>0.2767194558216268</v>
       </c>
       <c r="P43">
-        <v>0.07039726680631563</v>
+        <v>0.2831832816270143</v>
       </c>
       <c r="Q43">
-        <v>0.8820082649149967</v>
+        <v>83.30550969256235</v>
       </c>
       <c r="R43">
-        <v>0.05414792544086373</v>
+        <v>0.7769677965397922</v>
       </c>
       <c r="S43">
-        <v>0.1492307420428639</v>
-      </c>
-      <c r="T43">
-        <v>0.2201878546130404</v>
+        <v>0.4976488390422292</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B3A03</t>
+          <t>B3A05</t>
         </is>
       </c>
       <c r="B44">
-        <v>924.1148284617932</v>
+        <v>972.281952784939</v>
       </c>
       <c r="C44">
-        <v>2.257242245942205</v>
+        <v>2.964106549473492</v>
       </c>
       <c r="D44">
-        <v>0.7730747615744021</v>
+        <v>0.8289285611984056</v>
       </c>
       <c r="E44">
-        <v>0.1670978620647274</v>
+        <v>0.6505704254947626</v>
       </c>
       <c r="F44">
-        <v>62.0938932396</v>
+        <v>112.6675989174194</v>
       </c>
       <c r="G44">
-        <v>0.1842351684165962</v>
+        <v>0.1939137208068444</v>
       </c>
       <c r="H44">
-        <v>3.444444444444445</v>
+        <v>5.491525423728813</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3237,65 +3112,62 @@
         </is>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>2.333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="L44">
-        <v>0.2916666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="M44">
-        <v>-0.9956581805243985</v>
+        <v>-0.6055895411415485</v>
       </c>
       <c r="N44">
-        <v>0.7023296855290859</v>
+        <v>0.876112359906389</v>
       </c>
       <c r="O44">
-        <v>0.3940111154255836</v>
+        <v>0.1704249607823244</v>
       </c>
       <c r="P44">
-        <v>0.4424664651842483</v>
+        <v>0.1388343516038813</v>
       </c>
       <c r="Q44">
-        <v>0.9754249577126826</v>
+        <v>80.03409263738827</v>
       </c>
       <c r="R44">
-        <v>0.07146602998081229</v>
+        <v>0.7131434838109965</v>
       </c>
       <c r="S44">
-        <v>0.1486362155202371</v>
-      </c>
-      <c r="T44">
-        <v>0.347621606867097</v>
+        <v>0.5514051765935161</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B3A04</t>
+          <t>B3A06</t>
         </is>
       </c>
       <c r="B45">
-        <v>735.5685782084339</v>
+        <v>884.1512260972701</v>
       </c>
       <c r="C45">
-        <v>2.165236473379724</v>
+        <v>2.829127670606511</v>
       </c>
       <c r="D45">
-        <v>0.6597454807834461</v>
+        <v>0.7485320540773909</v>
       </c>
       <c r="E45">
-        <v>0.1535197093499728</v>
+        <v>0.6028230402012745</v>
       </c>
       <c r="F45">
-        <v>109.3305764172</v>
+        <v>202.9518392865625</v>
       </c>
       <c r="G45">
-        <v>0.4207276517137379</v>
+        <v>0.5285252560788698</v>
       </c>
       <c r="H45">
-        <v>6.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3303,59 +3175,56 @@
         </is>
       </c>
       <c r="J45">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M45">
-        <v>-1.719018652508012</v>
+        <v>-0.390713495517238</v>
       </c>
       <c r="N45">
-        <v>0.3800594369927521</v>
+        <v>0.9718435469284799</v>
       </c>
       <c r="O45">
-        <v>0.2767194558216268</v>
+        <v>0.4640198872263714</v>
       </c>
       <c r="P45">
-        <v>0.2831832816270143</v>
+        <v>0.537539039713539</v>
       </c>
       <c r="Q45">
-        <v>2.348475068568395</v>
+        <v>71.55827950431745</v>
       </c>
       <c r="R45">
-        <v>0.3260096735872604</v>
+        <v>0.5477830485890927</v>
       </c>
       <c r="S45">
-        <v>0.2100108886364534</v>
-      </c>
-      <c r="T45">
-        <v>0.3476080175272339</v>
+        <v>0.6561743309314412</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B3A05</t>
+          <t>B3A07</t>
         </is>
       </c>
       <c r="B46">
-        <v>936.2348494130874</v>
+        <v>963.5470426919795</v>
       </c>
       <c r="C46">
-        <v>2.555012885459033</v>
+        <v>2.690502686665903</v>
       </c>
       <c r="D46">
-        <v>0.7803597288210897</v>
+        <v>0.8209602136324221</v>
       </c>
       <c r="E46">
-        <v>0.2110426614476562</v>
+        <v>0.5537858828691359</v>
       </c>
       <c r="F46">
-        <v>85.54742265759999</v>
+        <v>107.9302736590323</v>
       </c>
       <c r="G46">
-        <v>0.3016562708528405</v>
+        <v>0.1763562415467805</v>
       </c>
       <c r="H46">
-        <v>5.333333333333333</v>
+        <v>6.203389830508475</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3366,62 +3235,59 @@
         <v>8</v>
       </c>
       <c r="K46">
-        <v>3.666666666666667</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>0.4583333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="M46">
-        <v>-0.6055895411415485</v>
+        <v>-0.4288801960791515</v>
       </c>
       <c r="N46">
-        <v>0.876112359906389</v>
+        <v>0.9548395875578904</v>
       </c>
       <c r="O46">
-        <v>0.1704249607823244</v>
+        <v>0.199481621832267</v>
       </c>
       <c r="P46">
-        <v>0.1388343516038813</v>
+        <v>0.1782935722441714</v>
       </c>
       <c r="Q46">
-        <v>2.998279994948021</v>
+        <v>68.56408423780213</v>
       </c>
       <c r="R46">
-        <v>0.4464741142412194</v>
+        <v>0.4893672453337708</v>
       </c>
       <c r="S46">
-        <v>0.2478859201476175</v>
-      </c>
-      <c r="T46">
-        <v>0.4325873425442534</v>
+        <v>0.5605146775977388</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B3A06</t>
+          <t>B3A08</t>
         </is>
       </c>
       <c r="B47">
-        <v>943.991013777351</v>
+        <v>800.328067796833</v>
       </c>
       <c r="C47">
-        <v>2.955095779901564</v>
+        <v>2.308053410886439</v>
       </c>
       <c r="D47">
-        <v>0.7850217177384895</v>
+        <v>0.6720650896429542</v>
       </c>
       <c r="E47">
-        <v>0.2700866375809209</v>
+        <v>0.4184983987891018</v>
       </c>
       <c r="F47">
-        <v>91.29715428679999</v>
+        <v>115.11182788125</v>
       </c>
       <c r="G47">
-        <v>0.3304425492240205</v>
+        <v>0.2029725244562933</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>1.864406779661017</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3429,59 +3295,56 @@
         </is>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47">
-        <v>-0.390713495517238</v>
+        <v>-0.951522905393257</v>
       </c>
       <c r="N47">
-        <v>0.9718435469284799</v>
+        <v>0.7219927534414485</v>
       </c>
       <c r="O47">
-        <v>0.4640198872263714</v>
+        <v>0.09279550814808123</v>
       </c>
       <c r="P47">
-        <v>0.537539039713539</v>
+        <v>0.03341282039578649</v>
       </c>
       <c r="Q47">
-        <v>2.173968670705522</v>
+        <v>61.49383346542474</v>
       </c>
       <c r="R47">
-        <v>0.2936587098507883</v>
+        <v>0.3514288875039369</v>
       </c>
       <c r="S47">
-        <v>0.1859714351434707</v>
-      </c>
-      <c r="T47">
-        <v>0.4820805194542441</v>
+        <v>0.4000617457049202</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B3A07</t>
+          <t>B3A09</t>
         </is>
       </c>
       <c r="B48">
-        <v>972.8863491148774</v>
+        <v>922.4330881276862</v>
       </c>
       <c r="C48">
-        <v>2.268363497938214</v>
+        <v>3.070241885028659</v>
       </c>
       <c r="D48">
-        <v>0.8023898041767772</v>
+        <v>0.7834543576712484</v>
       </c>
       <c r="E48">
-        <v>0.1687391292784614</v>
+        <v>0.6881147050334921</v>
       </c>
       <c r="F48">
-        <v>78.21535347625</v>
+        <v>254.4268867953125</v>
       </c>
       <c r="G48">
-        <v>0.2649479515603004</v>
+        <v>0.7193021248289343</v>
       </c>
       <c r="H48">
-        <v>6.074074074074074</v>
+        <v>11.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3489,65 +3352,56 @@
         </is>
       </c>
       <c r="J48">
-        <v>8</v>
-      </c>
-      <c r="K48">
-        <v>6</v>
-      </c>
-      <c r="L48">
-        <v>0.75</v>
+        <v>16</v>
       </c>
       <c r="M48">
-        <v>-0.4288801960791515</v>
+        <v>-0.6142770080829645</v>
       </c>
       <c r="N48">
-        <v>0.9548395875578904</v>
+        <v>0.8722419353548734</v>
       </c>
       <c r="O48">
-        <v>0.199481621832267</v>
+        <v>0.2823229594857957</v>
       </c>
       <c r="P48">
-        <v>0.1782935722441714</v>
+        <v>0.290792892623373</v>
       </c>
       <c r="Q48">
-        <v>2.19923090756511</v>
+        <v>88.97166044345161</v>
       </c>
       <c r="R48">
-        <v>0.2983419634079955</v>
+        <v>0.8875126067532404</v>
       </c>
       <c r="S48">
-        <v>0.2463241435986678</v>
-      </c>
-      <c r="T48">
-        <v>0.457984518978033</v>
+        <v>0.7069031037108603</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B3A08</t>
+          <t>B3A11</t>
         </is>
       </c>
       <c r="B49">
-        <v>788.4386873146162</v>
+        <v>874.7313058615135</v>
       </c>
       <c r="C49">
-        <v>1.951811858806947</v>
+        <v>2.721435365830919</v>
       </c>
       <c r="D49">
-        <v>0.6915240572987129</v>
+        <v>0.7399388118249205</v>
       </c>
       <c r="E49">
-        <v>0.1220226420568437</v>
+        <v>0.5647279988701689</v>
       </c>
       <c r="F49">
-        <v>46.913539688</v>
+        <v>231.912202086875</v>
       </c>
       <c r="G49">
-        <v>0.1082340763151742</v>
+        <v>0.635858179510758</v>
       </c>
       <c r="H49">
-        <v>1.851851851851852</v>
+        <v>3.254237288135593</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3555,59 +3409,62 @@
         </is>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>-0.951522905393257</v>
+        <v>-1.384072060386383</v>
       </c>
       <c r="N49">
-        <v>0.7219927534414485</v>
+        <v>0.5292842366191833</v>
       </c>
       <c r="O49">
-        <v>0.09279550814808123</v>
+        <v>0.2174399877180209</v>
       </c>
       <c r="P49">
-        <v>0.03341282039578649</v>
+        <v>0.202681203039294</v>
       </c>
       <c r="Q49">
-        <v>1.161661085411861</v>
+        <v>93.73392303334973</v>
       </c>
       <c r="R49">
-        <v>0.1059915160799036</v>
+        <v>0.9804228446434465</v>
       </c>
       <c r="S49">
-        <v>0.08767184358108708</v>
-      </c>
-      <c r="T49">
-        <v>0.2672642441669938</v>
+        <v>0.5218447535011101</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B3A09</t>
+          <t>B3A12</t>
         </is>
       </c>
       <c r="B50">
-        <v>942.626970427123</v>
+        <v>771.2549657006074</v>
       </c>
       <c r="C50">
-        <v>2.82574750977417</v>
+        <v>2.128997105629884</v>
       </c>
       <c r="D50">
-        <v>0.7842018337490636</v>
+        <v>0.645543399109382</v>
       </c>
       <c r="E50">
-        <v>0.250997503103121</v>
+        <v>0.3551590788297286</v>
       </c>
       <c r="F50">
-        <v>160.814415098</v>
+        <v>115.4052684690625</v>
       </c>
       <c r="G50">
-        <v>0.6784837014667312</v>
+        <v>0.2040600742346113</v>
       </c>
       <c r="H50">
-        <v>11.37037037037037</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3615,59 +3472,62 @@
         </is>
       </c>
       <c r="J50">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L50">
+        <v>0.08333333333333333</v>
       </c>
       <c r="M50">
-        <v>-0.6142770080829645</v>
+        <v>-1.67486576535385</v>
       </c>
       <c r="N50">
-        <v>0.8722419353548734</v>
+        <v>0.3997303513817413</v>
       </c>
       <c r="O50">
-        <v>0.2823229594857957</v>
+        <v>0.389249727780955</v>
       </c>
       <c r="P50">
-        <v>0.290792892623373</v>
+        <v>0.4360004557105367</v>
       </c>
       <c r="Q50">
-        <v>4.180372373878496</v>
+        <v>67.68422725167903</v>
       </c>
       <c r="R50">
-        <v>0.6656169545741584</v>
+        <v>0.4722015136365176</v>
       </c>
       <c r="S50">
-        <v>0.2783918632235105</v>
-      </c>
-      <c r="T50">
-        <v>0.5458180977278331</v>
+        <v>0.3708611723194072</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B3A11</t>
+          <t>B3A13</t>
         </is>
       </c>
       <c r="B51">
-        <v>833.5776464733858</v>
+        <v>870.8383767477686</v>
       </c>
       <c r="C51">
-        <v>2.435110757541504</v>
+        <v>2.965250120862364</v>
       </c>
       <c r="D51">
-        <v>0.7186556802837452</v>
+        <v>0.7363875202949643</v>
       </c>
       <c r="E51">
-        <v>0.1933475825591806</v>
+        <v>0.6509749520708715</v>
       </c>
       <c r="F51">
-        <v>202.9204186712</v>
+        <v>268.7253422890625</v>
       </c>
       <c r="G51">
-        <v>0.889289216945143</v>
+        <v>0.7722950738222517</v>
       </c>
       <c r="H51">
-        <v>3.185185185185185</v>
+        <v>3.033898305084746</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3677,63 +3537,54 @@
       <c r="J51">
         <v>4</v>
       </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
       <c r="M51">
-        <v>-1.384072060386383</v>
+        <v>-1.086829674307075</v>
       </c>
       <c r="N51">
-        <v>0.5292842366191833</v>
+        <v>0.6617111265964968</v>
       </c>
       <c r="O51">
-        <v>0.2174399877180209</v>
+        <v>0.1895459894682848</v>
       </c>
       <c r="P51">
-        <v>0.202681203039294</v>
+        <v>0.1648008894828135</v>
       </c>
       <c r="Q51">
-        <v>4.312780101525268</v>
+        <v>87.879173087021</v>
       </c>
       <c r="R51">
-        <v>0.690163433373723</v>
+        <v>0.8661985237387249</v>
       </c>
       <c r="S51">
-        <v>0.2972274781089727</v>
-      </c>
-      <c r="T51">
-        <v>0.4400811038661552</v>
+        <v>0.6420613476676871</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B3A12</t>
+          <t>B3A16</t>
         </is>
       </c>
       <c r="B52">
-        <v>713.8205147827568</v>
+        <v>941.7955308036528</v>
       </c>
       <c r="C52">
-        <v>1.846643069246183</v>
+        <v>2.753839423059208</v>
       </c>
       <c r="D52">
-        <v>0.6466733969667903</v>
+        <v>0.8011175815998943</v>
       </c>
       <c r="E52">
-        <v>0.1065018997630688</v>
+        <v>0.5761905996751149</v>
       </c>
       <c r="F52">
-        <v>37.5051436404</v>
+        <v>102.683986036875</v>
       </c>
       <c r="G52">
-        <v>0.06113053738179166</v>
+        <v>0.1569124455027409</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>10.33898305084746</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3741,125 +3592,125 @@
         </is>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K52">
-        <v>0.6666666666666666</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="L52">
-        <v>0.08333333333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="M52">
-        <v>-1.67486576535385</v>
+        <v>-0.9276073003238816</v>
       </c>
       <c r="N52">
-        <v>0.3997303513817413</v>
+        <v>0.7326475905359738</v>
       </c>
       <c r="O52">
-        <v>0.389249727780955</v>
+        <v>0.1669130100930245</v>
       </c>
       <c r="P52">
-        <v>0.4360004557105367</v>
+        <v>0.1340650893376933</v>
       </c>
       <c r="Q52">
-        <v>1.420991482783528</v>
+        <v>77.01895281663913</v>
       </c>
       <c r="R52">
-        <v>0.1540676232248591</v>
+        <v>0.6543190589226516</v>
       </c>
       <c r="S52">
-        <v>0.2179525028826017</v>
-      </c>
-      <c r="T52">
-        <v>0.2631737625805904</v>
+        <v>0.5019408141296289</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B3A13</t>
+          <t>B3A17</t>
         </is>
       </c>
       <c r="B53">
-        <v>841.6262690872577</v>
+        <v>803.6205597323058</v>
       </c>
       <c r="C53">
-        <v>2.621399623865686</v>
+        <v>2.029796058820261</v>
       </c>
       <c r="D53">
-        <v>0.7234934567495312</v>
+        <v>0.6750686374552197</v>
       </c>
       <c r="E53">
-        <v>0.2208399735859556</v>
+        <v>0.3200677323665221</v>
       </c>
       <c r="F53">
-        <v>225.03363813</v>
+        <v>89.29260579419355</v>
       </c>
       <c r="G53">
+        <v>0.107281299645013</v>
+      </c>
+      <c r="H53">
         <v>1</v>
       </c>
-      <c r="H53">
-        <v>3.018518518518519</v>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>0.125</v>
       </c>
       <c r="M53">
-        <v>-1.086829674307075</v>
+        <v>-0.5462452308386635</v>
       </c>
       <c r="N53">
-        <v>0.6617111265964968</v>
+        <v>0.9025513296472754</v>
       </c>
       <c r="O53">
-        <v>0.1895459894682848</v>
+        <v>0.0762124666863655</v>
       </c>
       <c r="P53">
-        <v>0.1648008894828135</v>
+        <v>0.01089289318184347</v>
       </c>
       <c r="Q53">
-        <v>4.060652057421678</v>
+        <v>55.27091702878026</v>
       </c>
       <c r="R53">
-        <v>0.6434225384172394</v>
+        <v>0.2300217547418851</v>
       </c>
       <c r="S53">
-        <v>1</v>
-      </c>
-      <c r="T53">
-        <v>0.6306097121188623</v>
+        <v>0.338697663862537</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B3A14</t>
+          <t>B3A19</t>
         </is>
       </c>
       <c r="B54">
-        <v>979.6777570703656</v>
+        <v>838.7181694002497</v>
       </c>
       <c r="C54">
-        <v>2.616260508286441</v>
+        <v>2.367598667232508</v>
       </c>
       <c r="D54">
-        <v>0.8064719080537793</v>
+        <v>0.7070861338682416</v>
       </c>
       <c r="E54">
-        <v>0.2200815462154731</v>
+        <v>0.4395619186599191</v>
       </c>
       <c r="F54">
-        <v>111.4478500092</v>
+        <v>118.3972807875</v>
       </c>
       <c r="G54">
-        <v>0.4313278728958421</v>
+        <v>0.2151490730602286</v>
       </c>
       <c r="H54">
-        <v>33.22222222222222</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3867,59 +3718,62 @@
         </is>
       </c>
       <c r="J54">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>5.666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L54">
-        <v>0.7083333333333334</v>
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="M54">
+        <v>-1.385944877613435</v>
+      </c>
+      <c r="N54">
+        <v>0.5284498624771043</v>
       </c>
       <c r="O54">
-        <v>0.2920738235139098</v>
+        <v>0.06819124629979556</v>
       </c>
       <c r="P54">
-        <v>0.3040346582363419</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.264209423554901</v>
+        <v>77.05132113137303</v>
       </c>
       <c r="R54">
-        <v>0.495773586390557</v>
+        <v>0.6549505545122504</v>
       </c>
       <c r="S54">
-        <v>0.2572970892523003</v>
-      </c>
-      <c r="T54">
-        <v>0.4604742849110896</v>
+        <v>0.3695520298920587</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B3A16</t>
+          <t>B3A20</t>
         </is>
       </c>
       <c r="B55">
-        <v>958.4918656362097</v>
+        <v>917.4690102689739</v>
       </c>
       <c r="C55">
-        <v>2.669950560400654</v>
+        <v>2.654039794401924</v>
       </c>
       <c r="D55">
-        <v>0.7937377283184526</v>
+        <v>0.7789259197935986</v>
       </c>
       <c r="E55">
-        <v>0.2280050895602654</v>
+        <v>0.5408875110612112</v>
       </c>
       <c r="F55">
-        <v>76.23030212720001</v>
+        <v>151.9766271153571</v>
       </c>
       <c r="G55">
-        <v>0.2550097067168988</v>
+        <v>0.3396008775197312</v>
       </c>
       <c r="H55">
-        <v>10.38888888888889</v>
+        <v>5.186440677966102</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3927,65 +3781,62 @@
         </is>
       </c>
       <c r="J55">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K55">
-        <v>3.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="L55">
-        <v>0.4583333333333333</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>-0.9276073003238816</v>
+        <v>-0.716170377852074</v>
       </c>
       <c r="N55">
-        <v>0.7326475905359738</v>
+        <v>0.8268465856343549</v>
       </c>
       <c r="O55">
-        <v>0.1669130100930245</v>
+        <v>0.3532388874340821</v>
       </c>
       <c r="P55">
-        <v>0.1340650893376933</v>
+        <v>0.3870973937844891</v>
       </c>
       <c r="Q55">
-        <v>2.173784861817515</v>
+        <v>74.36607320035223</v>
       </c>
       <c r="R55">
-        <v>0.2936246343398432</v>
+        <v>0.6025622161214722</v>
       </c>
       <c r="S55">
-        <v>0.1889170238053269</v>
-      </c>
-      <c r="T55">
-        <v>0.3855425244934734</v>
+        <v>0.6394172148449796</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B3A17</t>
+          <t>B3A21</t>
         </is>
       </c>
       <c r="B56">
-        <v>744.7720380074095</v>
+        <v>863.5299298005199</v>
       </c>
       <c r="C56">
-        <v>1.734933104705882</v>
+        <v>2.677901633048614</v>
       </c>
       <c r="D56">
-        <v>0.6652773939262682</v>
+        <v>0.7297204516218514</v>
       </c>
       <c r="E56">
-        <v>0.09001581507465463</v>
+        <v>0.5493283902064392</v>
       </c>
       <c r="F56">
-        <v>54.8284311848</v>
+        <v>143.5188982909375</v>
       </c>
       <c r="G56">
-        <v>0.1478603205641204</v>
+        <v>0.3082548351176205</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3993,65 +3844,62 @@
         </is>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56">
-        <v>1</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="L56">
-        <v>0.125</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="M56">
-        <v>-0.5462452308386635</v>
+        <v>-0.6166659216415455</v>
       </c>
       <c r="N56">
-        <v>0.9025513296472754</v>
+        <v>0.8711776309090629</v>
       </c>
       <c r="O56">
-        <v>0.0762124666863655</v>
+        <v>0.3341450838158363</v>
       </c>
       <c r="P56">
-        <v>0.01089289318184347</v>
+        <v>0.3611678278051172</v>
       </c>
       <c r="Q56">
-        <v>1.114954172112448</v>
+        <v>67.47438294184587</v>
       </c>
       <c r="R56">
-        <v>0.09733272948584863</v>
+        <v>0.4681075174785018</v>
       </c>
       <c r="S56">
-        <v>0.08300196495180187</v>
-      </c>
-      <c r="T56">
-        <v>0.2652415558539766</v>
+        <v>0.5292033314007514</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B3A19</t>
+          <t>B3A22</t>
         </is>
       </c>
       <c r="B57">
-        <v>794.3731951185905</v>
+        <v>1111.033140487697</v>
       </c>
       <c r="C57">
-        <v>1.829367209925923</v>
+        <v>3.307029389479954</v>
       </c>
       <c r="D57">
-        <v>0.6950911051735392</v>
+        <v>0.9555031540725488</v>
       </c>
       <c r="E57">
-        <v>0.1039523395605303</v>
+        <v>0.7718758408691314</v>
       </c>
       <c r="F57">
-        <v>44.897319408</v>
+        <v>183.8040500878125</v>
       </c>
       <c r="G57">
-        <v>0.09813978288016498</v>
+        <v>0.4575597020169162</v>
       </c>
       <c r="H57">
-        <v>1.981481481481481</v>
+        <v>12.3</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4059,65 +3907,62 @@
         </is>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K57">
-        <v>0.3333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="L57">
-        <v>0.04166666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M57">
-        <v>-1.385944877613435</v>
+        <v>-0.8743934316383419</v>
       </c>
       <c r="N57">
-        <v>0.5284498624771043</v>
+        <v>0.7563553370207129</v>
       </c>
       <c r="O57">
-        <v>0.06819124629979556</v>
+        <v>0.3971980876573364</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>0.4467944036301372</v>
       </c>
       <c r="Q57">
-        <v>2.119867323365915</v>
+        <v>94.73738138937408</v>
       </c>
       <c r="R57">
-        <v>0.2836291020695697</v>
+        <v>1</v>
       </c>
       <c r="S57">
-        <v>0.1979732350129783</v>
-      </c>
-      <c r="T57">
-        <v>0.2436127617300692</v>
+        <v>0.7221078720394447</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B3A20</t>
+          <t>B3A23</t>
         </is>
       </c>
       <c r="B58">
-        <v>908.1890415674118</v>
+        <v>1050.074936152694</v>
       </c>
       <c r="C58">
-        <v>2.426963928839512</v>
+        <v>3.156049903851567</v>
       </c>
       <c r="D58">
-        <v>0.7635022669087962</v>
+        <v>0.8998945497514735</v>
       </c>
       <c r="E58">
-        <v>0.1921452788213204</v>
+        <v>0.7184684060747184</v>
       </c>
       <c r="F58">
-        <v>77.49222236919999</v>
+        <v>117.7899405009375</v>
       </c>
       <c r="G58">
-        <v>0.261327564612032</v>
+        <v>0.2128981479276881</v>
       </c>
       <c r="H58">
-        <v>5.166666666666667</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4125,65 +3970,62 @@
         </is>
       </c>
       <c r="J58">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K58">
-        <v>8</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="M58">
-        <v>-0.716170377852074</v>
+        <v>-0.5644465323086085</v>
       </c>
       <c r="N58">
-        <v>0.8268465856343549</v>
+        <v>0.8944423187521697</v>
       </c>
       <c r="O58">
-        <v>0.3532388874340821</v>
+        <v>0.1863967799717657</v>
       </c>
       <c r="P58">
-        <v>0.3870973937844891</v>
+        <v>0.1605242331886833</v>
       </c>
       <c r="Q58">
-        <v>2.834340600322842</v>
+        <v>80.35157914235437</v>
       </c>
       <c r="R58">
-        <v>0.4160821201627792</v>
+        <v>0.7193375451729008</v>
       </c>
       <c r="S58">
-        <v>0.2232137599698851</v>
-      </c>
-      <c r="T58">
-        <v>0.5087768712367071</v>
+        <v>0.592461695362043</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B3A21</t>
+          <t>B3A24</t>
         </is>
       </c>
       <c r="B59">
-        <v>818.8409120553962</v>
+        <v>961.8098517393934</v>
       </c>
       <c r="C59">
-        <v>2.515178081988641</v>
+        <v>2.79305649673674</v>
       </c>
       <c r="D59">
-        <v>0.7097978880415029</v>
+        <v>0.8193754759360552</v>
       </c>
       <c r="E59">
-        <v>0.2051638667827247</v>
+        <v>0.5900632347324082</v>
       </c>
       <c r="F59">
-        <v>47.6341898124</v>
+        <v>134.8362436684375</v>
       </c>
       <c r="G59">
-        <v>0.111842042117239</v>
+        <v>0.2760751725143514</v>
       </c>
       <c r="H59">
-        <v>1.981481481481481</v>
+        <v>11.28813559322034</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4191,69 +4033,66 @@
         </is>
       </c>
       <c r="J59">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K59">
-        <v>3.333333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="L59">
-        <v>0.4166666666666667</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="M59">
-        <v>-0.6166659216415455</v>
+        <v>-1.093688034025946</v>
       </c>
       <c r="N59">
-        <v>0.8711776309090629</v>
+        <v>0.6586556025849467</v>
       </c>
       <c r="O59">
-        <v>0.3341450838158363</v>
+        <v>0.7683568704970393</v>
       </c>
       <c r="P59">
-        <v>0.3611678278051172</v>
+        <v>0.9508315426352157</v>
       </c>
       <c r="Q59">
-        <v>0.9162660823837382</v>
+        <v>84.75672142841009</v>
       </c>
       <c r="R59">
-        <v>0.06049882961512109</v>
+        <v>0.8052804788124337</v>
       </c>
       <c r="S59">
-        <v>0.1626101452000377</v>
-      </c>
-      <c r="T59">
-        <v>0.362365612142184</v>
+        <v>0.6274211676974397</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B3A22</t>
+          <t>B4A02</t>
         </is>
       </c>
       <c r="B60">
-        <v>1155.612559516232</v>
+        <v>940.1657715297354</v>
       </c>
       <c r="C60">
-        <v>3.122841494967197</v>
+        <v>3.062506222892643</v>
       </c>
       <c r="D60">
-        <v>0.9122208402149681</v>
+        <v>0.7996308475402127</v>
       </c>
       <c r="E60">
-        <v>0.2948424422763286</v>
+        <v>0.6853782943919974</v>
       </c>
       <c r="F60">
-        <v>141.0223841124</v>
+        <v>200.0871802265625</v>
       </c>
       <c r="G60">
-        <v>0.5793940482055104</v>
+        <v>0.5179082540176206</v>
       </c>
       <c r="H60">
-        <v>12.18518518518519</v>
+        <v>13</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="J60">
@@ -4266,188 +4105,179 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="M60">
-        <v>-0.8743934316383419</v>
+        <v>-1.954007242935438</v>
       </c>
       <c r="N60">
-        <v>0.7563553370207129</v>
+        <v>0.275367745404212</v>
       </c>
       <c r="O60">
-        <v>0.3971980876573364</v>
+        <v>0.3618746321584899</v>
       </c>
       <c r="P60">
-        <v>0.4467944036301372</v>
+        <v>0.3988248168317528</v>
       </c>
       <c r="Q60">
-        <v>3.629766775435469</v>
+        <v>86.73634089097996</v>
       </c>
       <c r="R60">
-        <v>0.5635426354289883</v>
+        <v>0.8439022288162242</v>
       </c>
       <c r="S60">
-        <v>0.2786914248453622</v>
-      </c>
-      <c r="T60">
-        <v>0.5623134747860843</v>
+        <v>0.5982398362383838</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B3A23</t>
+          <t>B4A04</t>
         </is>
       </c>
       <c r="B61">
-        <v>1059.194416158953</v>
+        <v>931.0850222829723</v>
       </c>
       <c r="C61">
-        <v>2.733724799848018</v>
+        <v>3.951922152773463</v>
       </c>
       <c r="D61">
-        <v>0.8542668961444996</v>
+        <v>0.7913470111426208</v>
       </c>
       <c r="E61">
-        <v>0.237416850783134</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>48.8067238412</v>
+        <v>146.71501500875</v>
       </c>
       <c r="G61">
-        <v>0.1177123840965592</v>
+        <v>0.3201002858572309</v>
       </c>
       <c r="H61">
-        <v>3.425925925925926</v>
+        <v>2.95</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61">
-        <v>4.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L61">
-        <v>0.5416666666666666</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="M61">
-        <v>-0.5644465323086085</v>
+        <v>-1.132070635144987</v>
       </c>
       <c r="N61">
-        <v>0.8944423187521697</v>
+        <v>0.641555455588824</v>
       </c>
       <c r="O61">
-        <v>0.1863967799717657</v>
+        <v>0.1604913406406163</v>
       </c>
       <c r="P61">
-        <v>0.1605242331886833</v>
+        <v>0.1253444014594112</v>
       </c>
       <c r="Q61">
-        <v>1.45201807705575</v>
+        <v>74.2736138695964</v>
       </c>
       <c r="R61">
-        <v>0.1598195053246524</v>
+        <v>0.6007583638026363</v>
       </c>
       <c r="S61">
-        <v>0.2751526068373289</v>
-      </c>
-      <c r="T61">
-        <v>0.4051251827242117</v>
+        <v>0.5029674549310557</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B3A24</t>
+          <t>B4A06</t>
         </is>
       </c>
       <c r="B62">
-        <v>967.5596028930293</v>
+        <v>935.1347230762776</v>
       </c>
       <c r="C62">
-        <v>2.483676006578784</v>
+        <v>2.488230333792243</v>
       </c>
       <c r="D62">
-        <v>0.7991880628667972</v>
+        <v>0.7950413163061399</v>
       </c>
       <c r="E62">
-        <v>0.2005148107633725</v>
+        <v>0.4822341256760957</v>
       </c>
       <c r="F62">
-        <v>94.0571918956</v>
+        <v>190.33094006125</v>
       </c>
       <c r="G62">
-        <v>0.3442607960650296</v>
+        <v>0.4817496676812886</v>
       </c>
       <c r="H62">
-        <v>11.14814814814815</v>
+        <v>7.689655172413793</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="J62">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K62">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="L62">
-        <v>0.2916666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="M62">
-        <v>-1.093688034025946</v>
+        <v>-1.376599108941444</v>
       </c>
       <c r="N62">
-        <v>0.6586556025849467</v>
+        <v>0.5326135724244097</v>
       </c>
       <c r="O62">
-        <v>0.7683568704970393</v>
+        <v>0.1819735616857008</v>
       </c>
       <c r="P62">
-        <v>0.9508315426352157</v>
+        <v>0.1545174609036637</v>
       </c>
       <c r="Q62">
-        <v>3.727290492743089</v>
+        <v>77.19327688318194</v>
       </c>
       <c r="R62">
-        <v>0.5816221229475144</v>
+        <v>0.6577200663611824</v>
       </c>
       <c r="S62">
-        <v>0.2881704189419155</v>
-      </c>
-      <c r="T62">
-        <v>0.5143637529339323</v>
+        <v>0.4791251727646829</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B4A01</t>
+          <t>B4A07</t>
         </is>
       </c>
       <c r="B63">
-        <v>1110.854887684022</v>
+        <v>899.7614602872376</v>
       </c>
       <c r="C63">
-        <v>3.591608040777307</v>
+        <v>2.162868994009377</v>
       </c>
       <c r="D63">
-        <v>0.8853183971708553</v>
+        <v>0.7627723576739119</v>
       </c>
       <c r="E63">
-        <v>0.3640227074847447</v>
+        <v>0.3671409097550509</v>
       </c>
       <c r="F63">
-        <v>167.2972334604167</v>
+        <v>68.9591740921875</v>
       </c>
       <c r="G63">
-        <v>0.7109402100562092</v>
+        <v>0.03192151623942003</v>
       </c>
       <c r="H63">
-        <v>34.55555555555556</v>
+        <v>2.694915254237288</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4455,59 +4285,62 @@
         </is>
       </c>
       <c r="J63">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="K63">
-        <v>4.666666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="L63">
-        <v>0.5833333333333334</v>
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M63">
+        <v>-0.9066587597174209</v>
+      </c>
+      <c r="N63">
+        <v>0.7419805464399709</v>
       </c>
       <c r="O63">
-        <v>0.4555387523322594</v>
+        <v>0.2902623101548458</v>
       </c>
       <c r="P63">
-        <v>0.526021578278737</v>
+        <v>0.3015746059541723</v>
       </c>
       <c r="Q63">
-        <v>3.231067725698165</v>
+        <v>57.40860185120891</v>
       </c>
       <c r="R63">
-        <v>0.4896295946592574</v>
+        <v>0.271727309955794</v>
       </c>
       <c r="S63">
-        <v>0.3537062882326431</v>
-      </c>
-      <c r="T63">
-        <v>0.5589960156022543</v>
+        <v>0.413397701812141</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B4A02</t>
+          <t>B4A08</t>
         </is>
       </c>
       <c r="B64">
-        <v>964.0300716470809</v>
+        <v>825.6953914759764</v>
       </c>
       <c r="C64">
-        <v>2.763925064330018</v>
+        <v>2.814837724279613</v>
       </c>
       <c r="D64">
-        <v>0.7970665715239834</v>
+        <v>0.6952062152805429</v>
       </c>
       <c r="E64">
-        <v>0.2418737863833878</v>
+        <v>0.5977681191734737</v>
       </c>
       <c r="F64">
-        <v>111.95119069</v>
+        <v>154.55160473125</v>
       </c>
       <c r="G64">
-        <v>0.4338478696343794</v>
+        <v>0.3491442619445448</v>
       </c>
       <c r="H64">
-        <v>13.09259259259259</v>
+        <v>6.677966101694915</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4515,65 +4348,62 @@
         </is>
       </c>
       <c r="J64">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K64">
-        <v>5.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="M64">
-        <v>-1.954007242935438</v>
+        <v>-1.126452331932567</v>
       </c>
       <c r="N64">
-        <v>0.275367745404212</v>
+        <v>0.6440585118695387</v>
       </c>
       <c r="O64">
-        <v>0.3618746321584899</v>
+        <v>0.17317336636282</v>
       </c>
       <c r="P64">
-        <v>0.3988248168317528</v>
+        <v>0.1425667123876401</v>
       </c>
       <c r="Q64">
-        <v>4.334073732835398</v>
+        <v>73.11013280198483</v>
       </c>
       <c r="R64">
-        <v>0.6941109648268283</v>
+        <v>0.578059215922415</v>
       </c>
       <c r="S64">
-        <v>0.2926364621243586</v>
-      </c>
-      <c r="T64">
-        <v>0.4750493604244461</v>
+        <v>0.4295432909397365</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B4A04</t>
+          <t>B4A09</t>
         </is>
       </c>
       <c r="B65">
-        <v>970.6620158721365</v>
+        <v>844.2071193141553</v>
       </c>
       <c r="C65">
-        <v>4.452826108356576</v>
+        <v>2.641342805042894</v>
       </c>
       <c r="D65">
-        <v>0.8010528267173979</v>
+        <v>0.7120933818216612</v>
       </c>
       <c r="E65">
-        <v>0.4911207157576051</v>
+        <v>0.5363960821200183</v>
       </c>
       <c r="F65">
-        <v>85.6636192112</v>
+        <v>73.60762752531249</v>
       </c>
       <c r="G65">
-        <v>0.3022380138894571</v>
+        <v>0.04914961865838969</v>
       </c>
       <c r="H65">
-        <v>2.851851851851852</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4581,65 +4411,62 @@
         </is>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K65">
-        <v>0.3333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="L65">
-        <v>0.04166666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="M65">
-        <v>-1.132070635144987</v>
+        <v>-0.389471081015986</v>
       </c>
       <c r="N65">
-        <v>0.641555455588824</v>
+        <v>0.9723970651888925</v>
       </c>
       <c r="O65">
-        <v>0.1604913406406163</v>
+        <v>0.3781242293694638</v>
       </c>
       <c r="P65">
-        <v>0.1253444014594112</v>
+        <v>0.4208919235981351</v>
       </c>
       <c r="Q65">
-        <v>3.316011292720438</v>
+        <v>53.85854141825244</v>
       </c>
       <c r="R65">
-        <v>0.5053769041564342</v>
+        <v>0.2024667529990534</v>
       </c>
       <c r="S65">
-        <v>0.2500738063642959</v>
-      </c>
-      <c r="T65">
-        <v>0.3948035988250115</v>
+        <v>0.4907230701504024</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B4A06</t>
+          <t>B4A10</t>
         </is>
       </c>
       <c r="B66">
-        <v>1005.270956197545</v>
+        <v>954.6694808040943</v>
       </c>
       <c r="C66">
-        <v>2.353039606296398</v>
+        <v>3.324423197436492</v>
       </c>
       <c r="D66">
-        <v>0.8218551832253911</v>
+        <v>0.8128617331777446</v>
       </c>
       <c r="E66">
-        <v>0.1812355748661308</v>
+        <v>0.7780287209137213</v>
       </c>
       <c r="F66">
-        <v>169.6096032784</v>
+        <v>330.164247171875</v>
       </c>
       <c r="G66">
-        <v>0.7225171888737136</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>7.69811320754717</v>
+        <v>6.610169491525424</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4650,62 +4477,59 @@
         <v>8</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="M66">
-        <v>-1.376599108941444</v>
+        <v>-1.20366931536268</v>
       </c>
       <c r="N66">
-        <v>0.5326135724244097</v>
+        <v>0.6096569411381311</v>
       </c>
       <c r="O66">
-        <v>0.1819735616857008</v>
+        <v>0.3303346114367731</v>
       </c>
       <c r="P66">
-        <v>0.1545174609036637</v>
+        <v>0.355993170259615</v>
       </c>
       <c r="Q66">
-        <v>2.656304490841908</v>
+        <v>83.67070406500328</v>
       </c>
       <c r="R66">
-        <v>0.3830767989130323</v>
+        <v>0.7840926233168005</v>
       </c>
       <c r="S66">
-        <v>0.2433711358906481</v>
-      </c>
-      <c r="T66">
-        <v>0.4111483643871237</v>
+        <v>0.6736618841151446</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B4A07</t>
+          <t>B4A11</t>
         </is>
       </c>
       <c r="B67">
-        <v>864.1034109893671</v>
+        <v>817.2379250340023</v>
       </c>
       <c r="C67">
-        <v>1.806250733014492</v>
+        <v>2.393989412593131</v>
       </c>
       <c r="D67">
-        <v>0.7370037669390967</v>
+        <v>0.687490963329454</v>
       </c>
       <c r="E67">
-        <v>0.1005408247719626</v>
+        <v>0.4488973724545661</v>
       </c>
       <c r="F67">
-        <v>47.108142838</v>
+        <v>76.5980043496875</v>
       </c>
       <c r="G67">
-        <v>0.1092083653444846</v>
+        <v>0.06023255601439794</v>
       </c>
       <c r="H67">
-        <v>2.666666666666667</v>
+        <v>3.779661016949153</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4716,62 +4540,59 @@
         <v>4</v>
       </c>
       <c r="K67">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>0.4166666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="M67">
-        <v>-0.9066587597174209</v>
+        <v>-0.3275141611830821</v>
       </c>
       <c r="N67">
-        <v>0.7419805464399709</v>
+        <v>1</v>
       </c>
       <c r="O67">
-        <v>0.2902623101548458</v>
+        <v>0.2572213614690207</v>
       </c>
       <c r="P67">
-        <v>0.3015746059541723</v>
+        <v>0.2567046850049774</v>
       </c>
       <c r="Q67">
-        <v>1.242859854944097</v>
+        <v>63.62258017304175</v>
       </c>
       <c r="R67">
-        <v>0.1210445942521303</v>
+        <v>0.3929600629229978</v>
       </c>
       <c r="S67">
-        <v>0.1483421034153823</v>
-      </c>
-      <c r="T67">
-        <v>0.3345451842229833</v>
+        <v>0.4601836628180562</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B4A08</t>
+          <t>B4A12</t>
         </is>
       </c>
       <c r="B68">
-        <v>844.2846047425069</v>
+        <v>857.5264607957037</v>
       </c>
       <c r="C68">
-        <v>2.670002544093911</v>
+        <v>2.553084119794869</v>
       </c>
       <c r="D68">
-        <v>0.7250912995467522</v>
+        <v>0.724243837996424</v>
       </c>
       <c r="E68">
-        <v>0.228012761280268</v>
+        <v>0.5051754831240297</v>
       </c>
       <c r="F68">
-        <v>102.957254056</v>
+        <v>162.0354838759375</v>
       </c>
       <c r="G68">
-        <v>0.3888193395575589</v>
+        <v>0.3768810217617106</v>
       </c>
       <c r="H68">
-        <v>6.685185185185185</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4779,65 +4600,56 @@
         </is>
       </c>
       <c r="J68">
-        <v>8</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68">
-        <v>-1.126452331932567</v>
+        <v>-1.816154692047206</v>
       </c>
       <c r="N68">
-        <v>0.6440585118695387</v>
+        <v>0.3367835644277383</v>
       </c>
       <c r="O68">
-        <v>0.17317336636282</v>
+        <v>0.1378526305046144</v>
       </c>
       <c r="P68">
-        <v>0.1425667123876401</v>
+        <v>0.0946008188869794</v>
       </c>
       <c r="Q68">
-        <v>2.773600791048716</v>
+        <v>62.30164690035363</v>
       </c>
       <c r="R68">
-        <v>0.4048218374954839</v>
+        <v>0.3671890722886557</v>
       </c>
       <c r="S68">
-        <v>0.2312243203600459</v>
-      </c>
-      <c r="T68">
-        <v>0.345574347812161</v>
+        <v>0.4008122997475896</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B4A09</t>
+          <t>B4A13</t>
         </is>
       </c>
       <c r="B69">
-        <v>824.1377555140724</v>
+        <v>740.1297030877272</v>
       </c>
       <c r="C69">
-        <v>2.493586792433825</v>
+        <v>2.080240700410156</v>
       </c>
       <c r="D69">
-        <v>0.7129816557315387</v>
+        <v>0.617149642568963</v>
       </c>
       <c r="E69">
-        <v>0.2019774381628826</v>
+        <v>0.3379120036940255</v>
       </c>
       <c r="F69">
-        <v>44.3637632324</v>
+        <v>88.9824012521875</v>
       </c>
       <c r="G69">
-        <v>0.09546851096905824</v>
+        <v>0.1061316192841371</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4848,62 +4660,59 @@
         <v>1</v>
       </c>
       <c r="K69">
-        <v>4.333333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="L69">
-        <v>0.5416666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M69">
-        <v>-0.389471081015986</v>
+        <v>-0.714038504471876</v>
       </c>
       <c r="N69">
-        <v>0.9723970651888925</v>
+        <v>0.8277963740050138</v>
       </c>
       <c r="O69">
-        <v>0.3781242293694638</v>
+        <v>0.1538282593601269</v>
       </c>
       <c r="P69">
-        <v>0.4208919235981351</v>
+        <v>0.1162958740343532</v>
       </c>
       <c r="Q69">
-        <v>0.8606043970441799</v>
+        <v>43.4807847210309</v>
       </c>
       <c r="R69">
-        <v>0.05017995772283684</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0.3744454022550013</v>
+        <v>0.3102788828933085</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B4A10</t>
+          <t>B4A14</t>
         </is>
       </c>
       <c r="B70">
-        <v>1004.19269737696</v>
+        <v>899.4694821174611</v>
       </c>
       <c r="C70">
-        <v>3.305629035542037</v>
+        <v>2.765656411943148</v>
       </c>
       <c r="D70">
-        <v>0.8212070754190615</v>
+        <v>0.7625060030676597</v>
       </c>
       <c r="E70">
-        <v>0.3218181099019017</v>
+        <v>0.5803707375306559</v>
       </c>
       <c r="F70">
-        <v>198.04823638</v>
+        <v>102.4966450978125</v>
       </c>
       <c r="G70">
-        <v>0.8648964270282454</v>
+        <v>0.1562181223408834</v>
       </c>
       <c r="H70">
-        <v>6.592592592592593</v>
+        <v>2</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4911,65 +4720,62 @@
         </is>
       </c>
       <c r="J70">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L70">
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="M70">
-        <v>-1.20366931536268</v>
+        <v>-1.60020019793378</v>
       </c>
       <c r="N70">
-        <v>0.6096569411381311</v>
+        <v>0.4329952198692158</v>
       </c>
       <c r="O70">
-        <v>0.3303346114367731</v>
+        <v>0.3573260414299296</v>
       </c>
       <c r="P70">
-        <v>0.355993170259615</v>
+        <v>0.3926477875835491</v>
       </c>
       <c r="Q70">
-        <v>3.198257316627551</v>
+        <v>61.70609180193854</v>
       </c>
       <c r="R70">
-        <v>0.4835470190802443</v>
+        <v>0.3555699805594751</v>
       </c>
       <c r="S70">
-        <v>0.2645072720608249</v>
-      </c>
-      <c r="T70">
-        <v>0.512078251861003</v>
+        <v>0.4007582644216341</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B4A11</t>
+          <t>B4A15</t>
         </is>
       </c>
       <c r="B71">
-        <v>825.7249027478038</v>
+        <v>892.7724353911411</v>
       </c>
       <c r="C71">
-        <v>2.127817125808322</v>
+        <v>2.631552202183076</v>
       </c>
       <c r="D71">
-        <v>0.7139356405191779</v>
+        <v>0.7563966790548159</v>
       </c>
       <c r="E71">
-        <v>0.1479973861124179</v>
+        <v>0.53293275740635</v>
       </c>
       <c r="F71">
-        <v>40.7742455676</v>
+        <v>60.3461720246875</v>
       </c>
       <c r="G71">
-        <v>0.07749743659883106</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>3.759259259259259</v>
+        <v>1.9</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4977,7 +4783,7 @@
         </is>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K71">
         <v>3</v>
@@ -4986,56 +4792,53 @@
         <v>0.375</v>
       </c>
       <c r="M71">
-        <v>-0.3275141611830821</v>
+        <v>-1.851713085829956</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>0.3209416531735951</v>
       </c>
       <c r="O71">
-        <v>0.2572213614690207</v>
+        <v>0.07530113020270239</v>
       </c>
       <c r="P71">
-        <v>0.2567046850049774</v>
+        <v>0.009655289613952461</v>
       </c>
       <c r="Q71">
-        <v>2.096077665636558</v>
+        <v>59.83480433705234</v>
       </c>
       <c r="R71">
-        <v>0.2792188433975049</v>
+        <v>0.3190617535893077</v>
       </c>
       <c r="S71">
-        <v>0.1815784376029904</v>
-      </c>
-      <c r="T71">
-        <v>0.3789915536544874</v>
+        <v>0.3305697332625744</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B4A12</t>
+          <t>B4A16</t>
         </is>
       </c>
       <c r="B72">
-        <v>860.5820955838788</v>
+        <v>984.282715387383</v>
       </c>
       <c r="C72">
-        <v>2.295484009664331</v>
+        <v>2.832724909576293</v>
       </c>
       <c r="D72">
-        <v>0.7348872138821897</v>
+        <v>0.8398761549864866</v>
       </c>
       <c r="E72">
-        <v>0.1727415569486321</v>
+        <v>0.6040955263600328</v>
       </c>
       <c r="F72">
-        <v>51.1210193612</v>
+        <v>135.46246887375</v>
       </c>
       <c r="G72">
-        <v>0.1292990040239251</v>
+        <v>0.2783960889502532</v>
       </c>
       <c r="H72">
-        <v>0.9814814814814815</v>
+        <v>6.35593220338983</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5043,59 +4846,62 @@
         </is>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="K72">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="L72">
+        <v>0.1666666666666667</v>
       </c>
       <c r="M72">
-        <v>-1.816154692047206</v>
+        <v>-1.413333462589079</v>
       </c>
       <c r="N72">
-        <v>0.3367835644277383</v>
+        <v>0.5162477496591965</v>
       </c>
       <c r="O72">
-        <v>0.1378526305046144</v>
+        <v>0.1823399902473845</v>
       </c>
       <c r="P72">
-        <v>0.0946008188869794</v>
+        <v>0.1550150743575815</v>
       </c>
       <c r="Q72">
-        <v>0.5899254850199525</v>
+        <v>62.92368688532389</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>0.3793248757832806</v>
       </c>
       <c r="S72">
-        <v>0.131644287510149</v>
-      </c>
-      <c r="T72">
-        <v>0.2285652065256591</v>
+        <v>0.4199460195376425</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B4A13</t>
+          <t>B4A17</t>
         </is>
       </c>
       <c r="B73">
-        <v>706.1781152890081</v>
+        <v>706.9460658690535</v>
       </c>
       <c r="C73">
-        <v>1.8736807230348</v>
+        <v>2.220446207460934</v>
       </c>
       <c r="D73">
-        <v>0.6420797885710791</v>
+        <v>0.5868781512716429</v>
       </c>
       <c r="E73">
-        <v>0.1104920993121371</v>
+        <v>0.38750825476394</v>
       </c>
       <c r="F73">
-        <v>29.6650736028</v>
+        <v>104.8937559309375</v>
       </c>
       <c r="G73">
-        <v>0.02187888998215423</v>
+        <v>0.1651022967306731</v>
       </c>
       <c r="H73">
-        <v>0.9814814814814815</v>
+        <v>2</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5103,65 +4909,62 @@
         </is>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>1.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="L73">
-        <v>0.1666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="M73">
-        <v>-0.714038504471876</v>
+        <v>-0.6974744579940655</v>
       </c>
       <c r="N73">
-        <v>0.8277963740050138</v>
+        <v>0.8351759580186843</v>
       </c>
       <c r="O73">
-        <v>0.1538282593601269</v>
+        <v>0.2605866789926531</v>
       </c>
       <c r="P73">
-        <v>0.1162958740343532</v>
+        <v>0.2612748180447441</v>
       </c>
       <c r="Q73">
-        <v>0.7802323477516002</v>
+        <v>53.62515091401034</v>
       </c>
       <c r="R73">
-        <v>0.03528014153309827</v>
+        <v>0.197913378030515</v>
       </c>
       <c r="S73">
-        <v>0.04338224772508872</v>
-      </c>
-      <c r="T73">
-        <v>0.2454840102286989</v>
+        <v>0.436978979551457</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B4A14</t>
+          <t>B4A18</t>
         </is>
       </c>
       <c r="B74">
-        <v>955.1556805013</v>
+        <v>976.9563461971909</v>
       </c>
       <c r="C74">
-        <v>2.696138821543334</v>
+        <v>3.142902868993676</v>
       </c>
       <c r="D74">
-        <v>0.7917324513033079</v>
+        <v>0.8331927368994226</v>
       </c>
       <c r="E74">
-        <v>0.231869936289178</v>
+        <v>0.7138177781831853</v>
       </c>
       <c r="F74">
-        <v>59.2065057252</v>
+        <v>151.39790363125</v>
       </c>
       <c r="G74">
-        <v>0.16977933880311</v>
+        <v>0.337456012006954</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>10.48333333333333</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5169,65 +4972,62 @@
         </is>
       </c>
       <c r="J74">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>0.125</v>
+        <v>0.625</v>
       </c>
       <c r="M74">
-        <v>-1.60020019793378</v>
+        <v>-0.6333708939956759</v>
       </c>
       <c r="N74">
-        <v>0.4329952198692158</v>
+        <v>0.8637352618539839</v>
       </c>
       <c r="O74">
-        <v>0.3573260414299296</v>
+        <v>0.168616944640567</v>
       </c>
       <c r="P74">
-        <v>0.3926477875835491</v>
+        <v>0.1363790485759047</v>
       </c>
       <c r="Q74">
-        <v>1.160429300600832</v>
+        <v>70.64538134139848</v>
       </c>
       <c r="R74">
-        <v>0.1057631609809458</v>
+        <v>0.5299726939760873</v>
       </c>
       <c r="S74">
-        <v>0.1833784408786485</v>
-      </c>
-      <c r="T74">
-        <v>0.3041457919634944</v>
+        <v>0.5770790759279339</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B4A15</t>
+          <t>B4A20</t>
         </is>
       </c>
       <c r="B75">
-        <v>934.3217531772182</v>
+        <v>990.9597563929921</v>
       </c>
       <c r="C75">
-        <v>2.36225955882839</v>
+        <v>2.953631968905547</v>
       </c>
       <c r="D75">
-        <v>0.7792098262364263</v>
+        <v>0.8459672289504764</v>
       </c>
       <c r="E75">
-        <v>0.1825962495283338</v>
+        <v>0.6468651507261209</v>
       </c>
       <c r="F75">
-        <v>29.7639001916</v>
+        <v>152.0578600525</v>
       </c>
       <c r="G75">
-        <v>0.02237366954390341</v>
+        <v>0.3399019431066032</v>
       </c>
       <c r="H75">
-        <v>1.907407407407407</v>
+        <v>9.85</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5235,65 +5035,62 @@
         </is>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L75">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="M75">
-        <v>-1.851713085829956</v>
+        <v>-1.035834938222531</v>
       </c>
       <c r="N75">
-        <v>0.3209416531735951</v>
+        <v>0.6844302091404252</v>
       </c>
       <c r="O75">
-        <v>0.07530113020270239</v>
+        <v>0.3646367785288091</v>
       </c>
       <c r="P75">
-        <v>0.009655289613952461</v>
+        <v>0.4025758377381077</v>
       </c>
       <c r="Q75">
-        <v>0.7652975136819987</v>
+        <v>64.51055244793349</v>
       </c>
       <c r="R75">
-        <v>0.03251143917425656</v>
+        <v>0.410284121339076</v>
       </c>
       <c r="S75">
-        <v>0.1632758599237923</v>
-      </c>
-      <c r="T75">
-        <v>0.2356954983992825</v>
+        <v>0.5471463558572585</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B4A16</t>
+          <t>B4A21</t>
         </is>
       </c>
       <c r="B76">
-        <v>969.3120819520811</v>
+        <v>748.9641781174147</v>
       </c>
       <c r="C76">
-        <v>2.886406721124843</v>
+        <v>2.339591991004429</v>
       </c>
       <c r="D76">
-        <v>0.8002414234671629</v>
+        <v>0.6252088174030913</v>
       </c>
       <c r="E76">
-        <v>0.2599495504838077</v>
+        <v>0.4296548459987961</v>
       </c>
       <c r="F76">
-        <v>88.0071601584</v>
+        <v>61.79041457875</v>
       </c>
       <c r="G76">
-        <v>0.3139710523042856</v>
+        <v>0.005352653091438228</v>
       </c>
       <c r="H76">
-        <v>6.537037037037037</v>
+        <v>1.9</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5301,65 +5098,62 @@
         </is>
       </c>
       <c r="J76">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K76">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="L76">
-        <v>0.1666666666666667</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="M76">
-        <v>-1.413333462589079</v>
+        <v>-1.10875161355244</v>
       </c>
       <c r="N76">
-        <v>0.5162477496591965</v>
+        <v>0.6519445038922881</v>
       </c>
       <c r="O76">
-        <v>0.1823399902473845</v>
+        <v>0.1084997787626584</v>
       </c>
       <c r="P76">
-        <v>0.1550150743575815</v>
+        <v>0.05473936848437524</v>
       </c>
       <c r="Q76">
-        <v>2.643810951523113</v>
+        <v>44.98763421897511</v>
       </c>
       <c r="R76">
-        <v>0.3807606773129513</v>
+        <v>0.02939815742536144</v>
       </c>
       <c r="S76">
-        <v>0.1565376364396137</v>
-      </c>
-      <c r="T76">
-        <v>0.3436737288364082</v>
+        <v>0.2863759542326691</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B4A17</t>
+          <t>B4A22</t>
         </is>
       </c>
       <c r="B77">
-        <v>687.6515140523901</v>
+        <v>729.3911372457928</v>
       </c>
       <c r="C77">
-        <v>1.877251447170667</v>
+        <v>2.420880084084988</v>
       </c>
       <c r="D77">
-        <v>0.630944025378624</v>
+        <v>0.6073534770586047</v>
       </c>
       <c r="E77">
-        <v>0.1110190644825686</v>
+        <v>0.4584096699584418</v>
       </c>
       <c r="F77">
-        <v>73.4244075916</v>
+        <v>114.1203750196875</v>
       </c>
       <c r="G77">
-        <v>0.2409618752021621</v>
+        <v>0.1992980009425456</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5367,131 +5161,95 @@
         </is>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L77">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="M77">
-        <v>-0.6974744579940655</v>
+        <v>-1.26993673157125</v>
       </c>
       <c r="N77">
-        <v>0.8351759580186843</v>
+        <v>0.5801336017817053</v>
       </c>
       <c r="O77">
-        <v>0.2605866789926531</v>
+        <v>0.3612722184373502</v>
       </c>
       <c r="P77">
-        <v>0.2612748180447441</v>
+        <v>0.3980067332983994</v>
       </c>
       <c r="Q77">
-        <v>1.412863028854081</v>
+        <v>77.71137580179388</v>
       </c>
       <c r="R77">
-        <v>0.1525607253602217</v>
+        <v>0.6678280125044722</v>
       </c>
       <c r="S77">
-        <v>0.1064792360950618</v>
-      </c>
-      <c r="T77">
-        <v>0.3704269628227583</v>
+        <v>0.5230042136491669</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B4A18</t>
+          <t>B1A09</t>
         </is>
       </c>
       <c r="B78">
-        <v>1089.560605949949</v>
+        <v>676.5846424714285</v>
       </c>
       <c r="C78">
-        <v>3.065558163535105</v>
+        <v>3.16392122</v>
       </c>
       <c r="D78">
-        <v>0.8725190674008934</v>
+        <v>0.5591812005697393</v>
       </c>
       <c r="E78">
-        <v>0.2863886050818564</v>
+        <v>0.7212528029230316</v>
       </c>
       <c r="F78">
-        <v>116.396116648</v>
+        <v>214.3728571428572</v>
       </c>
       <c r="G78">
-        <v>0.4561015823670683</v>
+        <v>0.5708538430353383</v>
       </c>
       <c r="H78">
-        <v>10.33333333333333</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="J78">
-        <v>16</v>
-      </c>
-      <c r="K78">
-        <v>5</v>
-      </c>
-      <c r="L78">
-        <v>0.625</v>
-      </c>
-      <c r="M78">
-        <v>-0.6333708939956759</v>
-      </c>
-      <c r="N78">
-        <v>0.8637352618539839</v>
-      </c>
-      <c r="O78">
-        <v>0.168616944640567</v>
-      </c>
-      <c r="P78">
-        <v>0.1363790485759047</v>
-      </c>
-      <c r="Q78">
-        <v>1.630447529738109</v>
-      </c>
-      <c r="R78">
-        <v>0.1928977467183089</v>
+        <v>1</v>
       </c>
       <c r="S78">
-        <v>0.1891495494652774</v>
-      </c>
-      <c r="T78">
-        <v>0.4527713576829116</v>
+        <v>0.617095948842703</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B4A20</t>
+          <t>B4A03</t>
         </is>
       </c>
       <c r="B79">
-        <v>1065.292555952169</v>
+        <v>666.26620934</v>
       </c>
       <c r="C79">
-        <v>2.826573011754531</v>
+        <v>2.543287669</v>
       </c>
       <c r="D79">
-        <v>0.8579322981135081</v>
+        <v>0.5497682975572799</v>
       </c>
       <c r="E79">
-        <v>0.2511193301542233</v>
-      </c>
-      <c r="F79">
-        <v>147.5316608672</v>
-      </c>
-      <c r="G79">
-        <v>0.6119830218729293</v>
+        <v>0.5017100897636932</v>
       </c>
       <c r="H79">
-        <v>9.62962962962963</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5499,256 +5257,16 @@
         </is>
       </c>
       <c r="J79">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L79">
-        <v>0.5</v>
-      </c>
-      <c r="M79">
-        <v>-1.035834938222531</v>
-      </c>
-      <c r="N79">
-        <v>0.6844302091404252</v>
-      </c>
-      <c r="O79">
-        <v>0.3646367785288091</v>
-      </c>
-      <c r="P79">
-        <v>0.4025758377381077</v>
-      </c>
-      <c r="Q79">
-        <v>4.216377240397463</v>
-      </c>
-      <c r="R79">
-        <v>0.672291736389361</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="S79">
-        <v>0.1312630330506945</v>
-      </c>
-      <c r="T79">
-        <v>0.5139494333074062</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>B4A21</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>734.2236921921332</v>
-      </c>
-      <c r="C80">
-        <v>2.216358130007247</v>
-      </c>
-      <c r="D80">
-        <v>0.6589371116709957</v>
-      </c>
-      <c r="E80">
-        <v>0.1610642105414428</v>
-      </c>
-      <c r="F80">
-        <v>34.4429306608</v>
-      </c>
-      <c r="G80">
-        <v>0.04579943656746183</v>
-      </c>
-      <c r="H80">
-        <v>1.888888888888889</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="J80">
-        <v>2</v>
-      </c>
-      <c r="K80">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="L80">
-        <v>0.2083333333333333</v>
-      </c>
-      <c r="M80">
-        <v>-1.10875161355244</v>
-      </c>
-      <c r="N80">
-        <v>0.6519445038922881</v>
-      </c>
-      <c r="O80">
-        <v>0.1084997787626584</v>
-      </c>
-      <c r="P80">
-        <v>0.05473936848437524</v>
-      </c>
-      <c r="Q80">
-        <v>3.868551683434767</v>
-      </c>
-      <c r="R80">
-        <v>0.6078099058219762</v>
-      </c>
-      <c r="S80">
-        <v>0.09273992238029152</v>
-      </c>
-      <c r="T80">
-        <v>0.3101709740865206</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>B4A22</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>783.7945610874324</v>
-      </c>
-      <c r="C81">
-        <v>2.27967384047498</v>
-      </c>
-      <c r="D81">
-        <v>0.6887326176146994</v>
-      </c>
-      <c r="E81">
-        <v>0.1704083023525325</v>
-      </c>
-      <c r="F81">
-        <v>81.8560800252</v>
-      </c>
-      <c r="G81">
-        <v>0.2831754054086119</v>
-      </c>
-      <c r="H81">
-        <v>2.777777777777778</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="J81">
-        <v>4</v>
-      </c>
-      <c r="K81">
-        <v>6</v>
-      </c>
-      <c r="L81">
-        <v>0.75</v>
-      </c>
-      <c r="M81">
-        <v>-1.26993673157125</v>
-      </c>
-      <c r="N81">
-        <v>0.5801336017817053</v>
-      </c>
-      <c r="O81">
-        <v>0.3612722184373502</v>
-      </c>
-      <c r="P81">
-        <v>0.3980067332983994</v>
-      </c>
-      <c r="Q81">
-        <v>5.984089296781033</v>
-      </c>
-      <c r="R81">
-        <v>1</v>
-      </c>
-      <c r="S81">
-        <v>0.1659300950003614</v>
-      </c>
-      <c r="T81">
-        <v>0.5045483444320388</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>B1A09</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>1301.651</v>
-      </c>
-      <c r="C82">
-        <v>7.901</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
-        <v>1</v>
-      </c>
-      <c r="H82">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="J82">
-        <v>1</v>
-      </c>
-      <c r="T82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>B3A10</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>1162.64967222488</v>
-      </c>
-      <c r="C83">
-        <v>1.57525640908611</v>
-      </c>
-      <c r="D83">
-        <v>0.9164506295692739</v>
-      </c>
-      <c r="E83">
-        <v>0.06645083107715304</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="T83">
-        <v>0.4914507303232135</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>B3A15</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>432.675640523626</v>
-      </c>
-      <c r="C84">
-        <v>1.12498455111615</v>
-      </c>
-      <c r="D84">
-        <v>0.4776859662698841</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="T84">
-        <v>0.238842983134942</v>
+        <v>0.3643816846625466</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality_reduced.xlsx
@@ -470,10 +470,10 @@
         <v>0.6159109451427114</v>
       </c>
       <c r="F2">
-        <v>152.379692735</v>
+        <v>175.9036689618518</v>
       </c>
       <c r="G2">
-        <v>0.341094719692547</v>
+        <v>0.3393615933846007</v>
       </c>
       <c r="H2">
         <v>11.83333333333333</v>
@@ -511,7 +511,7 @@
         <v>0.6467060369329617</v>
       </c>
       <c r="S2">
-        <v>0.5068951531028529</v>
+        <v>0.5066475636302892</v>
       </c>
     </row>
     <row r="3">
@@ -533,10 +533,10 @@
         <v>0.4765788354798875</v>
       </c>
       <c r="F3">
-        <v>275.3171712859375</v>
+        <v>316.0996166033333</v>
       </c>
       <c r="G3">
-        <v>0.7967257165554308</v>
+        <v>0.7846491592479132</v>
       </c>
       <c r="H3">
         <v>5.728813559322034</v>
@@ -574,7 +574,7 @@
         <v>0.7533089956157759</v>
       </c>
       <c r="S3">
-        <v>0.5452325353758232</v>
+        <v>0.5435073129033207</v>
       </c>
     </row>
     <row r="4">
@@ -596,10 +596,10 @@
         <v>0.5163091267147911</v>
       </c>
       <c r="F4">
-        <v>111.1061707528571</v>
+        <v>132.1994830808696</v>
       </c>
       <c r="G4">
-        <v>0.1881267542972417</v>
+        <v>0.2005492319977569</v>
       </c>
       <c r="H4">
         <v>6.186440677966102</v>
@@ -637,7 +637,7 @@
         <v>0.3618666178992232</v>
       </c>
       <c r="S4">
-        <v>0.4526777553726667</v>
+        <v>0.4544523950441689</v>
       </c>
     </row>
     <row r="5">
@@ -659,10 +659,10 @@
         <v>0.4021114024077352</v>
       </c>
       <c r="F5">
-        <v>95.08300676656251</v>
+        <v>110.6795104085185</v>
       </c>
       <c r="G5">
-        <v>0.1287416890915327</v>
+        <v>0.1321979250596891</v>
       </c>
       <c r="H5">
         <v>3.35</v>
@@ -700,7 +700,7 @@
         <v>0.2021585358630746</v>
       </c>
       <c r="S5">
-        <v>0.4310571780827911</v>
+        <v>0.4315509260782421</v>
       </c>
     </row>
     <row r="6">
@@ -722,10 +722,10 @@
         <v>0.2559912061846156</v>
       </c>
       <c r="F6">
-        <v>104.9201081617857</v>
+        <v>123.4828555304348</v>
       </c>
       <c r="G6">
-        <v>0.1651999633930487</v>
+        <v>0.1728636538496925</v>
       </c>
       <c r="H6">
         <v>1.864406779661017</v>
@@ -763,7 +763,7 @@
         <v>0.3020226232484428</v>
       </c>
       <c r="S6">
-        <v>0.3801502907151748</v>
+        <v>0.3812451036375524</v>
       </c>
     </row>
     <row r="7">
@@ -785,10 +785,10 @@
         <v>0.6824439679874053</v>
       </c>
       <c r="F7">
-        <v>190.1838700915625</v>
+        <v>218.0827665203704</v>
       </c>
       <c r="G7">
-        <v>0.4812045968234252</v>
+        <v>0.4733299997337918</v>
       </c>
       <c r="H7">
         <v>12.89830508474576</v>
@@ -826,7 +826,7 @@
         <v>0.7074196364968555</v>
       </c>
       <c r="S7">
-        <v>0.6023658462599593</v>
+        <v>0.6012409038185831</v>
       </c>
     </row>
     <row r="8">
@@ -848,10 +848,10 @@
         <v>0.4023952804604635</v>
       </c>
       <c r="F8">
-        <v>116.0377657446875</v>
+        <v>133.3449700559259</v>
       </c>
       <c r="G8">
-        <v>0.2064042362233141</v>
+        <v>0.2041875048254093</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -889,7 +889,7 @@
         <v>0.2737238705025282</v>
       </c>
       <c r="S8">
-        <v>0.4194639014490705</v>
+        <v>0.419147225535084</v>
       </c>
     </row>
     <row r="9">
@@ -911,10 +911,10 @@
         <v>0.3367709474237064</v>
       </c>
       <c r="F9">
-        <v>98.8683452184375</v>
+        <v>111.0446189811111</v>
       </c>
       <c r="G9">
-        <v>0.1427709139676277</v>
+        <v>0.1333575756080868</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -952,7 +952,7 @@
         <v>0.3692594182722592</v>
       </c>
       <c r="S9">
-        <v>0.3364964879525594</v>
+        <v>0.3351517253297678</v>
       </c>
     </row>
     <row r="10">
@@ -974,10 +974,10 @@
         <v>0.5836562254685655</v>
       </c>
       <c r="F10">
-        <v>119.3581357134375</v>
+        <v>137.07819946</v>
       </c>
       <c r="G10">
-        <v>0.2187101944766251</v>
+        <v>0.2160449134175649</v>
       </c>
       <c r="H10">
         <v>11.03333333333333</v>
@@ -1015,7 +1015,7 @@
         <v>0.7517332556213703</v>
       </c>
       <c r="S10">
-        <v>0.5603891394375248</v>
+        <v>0.5600083850005162</v>
       </c>
     </row>
     <row r="11">
@@ -1037,10 +1037,10 @@
         <v>0.4537123474411335</v>
       </c>
       <c r="F11">
-        <v>120.089965424375</v>
+        <v>129.6514192474074</v>
       </c>
       <c r="G11">
-        <v>0.2214225024290789</v>
+        <v>0.1924561225951354</v>
       </c>
       <c r="H11">
         <v>5.3</v>
@@ -1078,7 +1078,7 @@
         <v>0.4533593021840931</v>
       </c>
       <c r="S11">
-        <v>0.4687617659102406</v>
+        <v>0.4646237116482487</v>
       </c>
     </row>
     <row r="12">
@@ -1100,10 +1100,10 @@
         <v>0.3288492631064082</v>
       </c>
       <c r="F12">
-        <v>99.45453668906251</v>
+        <v>115.78909633</v>
       </c>
       <c r="G12">
-        <v>0.1449434573389538</v>
+        <v>0.1484268897039762</v>
       </c>
       <c r="H12">
         <v>3.2</v>
@@ -1141,7 +1141,7 @@
         <v>0.4480599402953412</v>
       </c>
       <c r="S12">
-        <v>0.4377548012351757</v>
+        <v>0.438252434430179</v>
       </c>
     </row>
     <row r="13">
@@ -1163,10 +1163,10 @@
         <v>0.6292839319183426</v>
       </c>
       <c r="F13">
-        <v>192.928677510625</v>
+        <v>223.4902612148148</v>
       </c>
       <c r="G13">
-        <v>0.4913774046220325</v>
+        <v>0.4905051762664656</v>
       </c>
       <c r="H13">
         <v>6.559322033898305</v>
@@ -1204,7 +1204,7 @@
         <v>0.7124206934329075</v>
       </c>
       <c r="S13">
-        <v>0.658513344656423</v>
+        <v>0.6583887406056277</v>
       </c>
     </row>
     <row r="14">
@@ -1226,10 +1226,10 @@
         <v>0.3531179340704553</v>
       </c>
       <c r="F14">
-        <v>67.78081792354838</v>
+        <v>79.78627797423077</v>
       </c>
       <c r="G14">
-        <v>0.02755429151588618</v>
+        <v>0.03407545787189094</v>
       </c>
       <c r="H14">
         <v>0.95</v>
@@ -1267,7 +1267,7 @@
         <v>0.3132008182870046</v>
       </c>
       <c r="S14">
-        <v>0.3778547477728379</v>
+        <v>0.3787863429665529</v>
       </c>
     </row>
     <row r="15">
@@ -1289,10 +1289,10 @@
         <v>0.4605975769010921</v>
       </c>
       <c r="F15">
-        <v>126.9768313448387</v>
+        <v>147.3560944807692</v>
       </c>
       <c r="G15">
-        <v>0.2469466112817081</v>
+        <v>0.248689358089394</v>
       </c>
       <c r="H15">
         <v>1.983050847457627</v>
@@ -1330,7 +1330,7 @@
         <v>0.6947836406760127</v>
       </c>
       <c r="S15">
-        <v>0.437165158624029</v>
+        <v>0.4374141224536984</v>
       </c>
     </row>
     <row r="16">
@@ -1352,10 +1352,10 @@
         <v>0.5304077887594206</v>
       </c>
       <c r="F16">
-        <v>184.2882473682143</v>
+        <v>218.6172393317391</v>
       </c>
       <c r="G16">
-        <v>0.4593542344259761</v>
+        <v>0.4750275815911728</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -1393,7 +1393,7 @@
         <v>0.3834795696361811</v>
       </c>
       <c r="S16">
-        <v>0.4516765065936149</v>
+        <v>0.453915556188643</v>
       </c>
     </row>
     <row r="17">
@@ -1415,10 +1415,10 @@
         <v>0.313670539220751</v>
       </c>
       <c r="F17">
-        <v>85.71637923125</v>
+        <v>98.60168228703704</v>
       </c>
       <c r="G17">
-        <v>0.09402708544534275</v>
+        <v>0.09383656886069811</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1456,7 +1456,7 @@
         <v>0.3681243883393301</v>
       </c>
       <c r="S17">
-        <v>0.1860029160505696</v>
+        <v>0.1859756993956204</v>
       </c>
     </row>
     <row r="18">
@@ -1478,10 +1478,10 @@
         <v>0.5859329628396042</v>
       </c>
       <c r="F18">
-        <v>196.8196160846875</v>
+        <v>226.3424978181482</v>
       </c>
       <c r="G18">
-        <v>0.5057980047687795</v>
+        <v>0.4995643931392132</v>
       </c>
       <c r="H18">
         <v>3.559322033898305</v>
@@ -1519,7 +1519,7 @@
         <v>0.6150179637492951</v>
       </c>
       <c r="S18">
-        <v>0.4886782149597833</v>
+        <v>0.4877876990127024</v>
       </c>
     </row>
     <row r="19">
@@ -1541,10 +1541,10 @@
         <v>0.5679576140152887</v>
       </c>
       <c r="F19">
-        <v>123.234310468125</v>
+        <v>137.8385049933333</v>
       </c>
       <c r="G19">
-        <v>0.233076076942331</v>
+        <v>0.2184597806512183</v>
       </c>
       <c r="H19">
         <v>12.15254237288136</v>
@@ -1582,7 +1582,7 @@
         <v>0.6351893924374753</v>
       </c>
       <c r="S19">
-        <v>0.6185564065771568</v>
+        <v>0.6164683642498551</v>
       </c>
     </row>
     <row r="20">
@@ -1604,10 +1604,10 @@
         <v>0.4864250121536806</v>
       </c>
       <c r="F20">
-        <v>140.165478528125</v>
+        <v>152.6567249751852</v>
       </c>
       <c r="G20">
-        <v>0.2958263876869464</v>
+        <v>0.265525114686548</v>
       </c>
       <c r="H20">
         <v>3.694915254237288</v>
@@ -1645,7 +1645,7 @@
         <v>0.5400635442923848</v>
       </c>
       <c r="S20">
-        <v>0.4769163801276965</v>
+        <v>0.4725876268419253</v>
       </c>
     </row>
     <row r="21">
@@ -1667,10 +1667,10 @@
         <v>0.4422947815550168</v>
       </c>
       <c r="F21">
-        <v>112.8774740863333</v>
+        <v>128.430548844</v>
       </c>
       <c r="G21">
-        <v>0.1946915603522473</v>
+        <v>0.188578418429548</v>
       </c>
       <c r="H21">
         <v>3.6</v>
@@ -1708,7 +1708,7 @@
         <v>0.7200410734080649</v>
       </c>
       <c r="S21">
-        <v>0.4817210942956662</v>
+        <v>0.4808477883067092</v>
       </c>
     </row>
     <row r="22">
@@ -1730,10 +1730,10 @@
         <v>0.7410034679201478</v>
       </c>
       <c r="F22">
-        <v>195.54534427125</v>
+        <v>220.6409793874074</v>
       </c>
       <c r="G22">
-        <v>0.5010752973936624</v>
+        <v>0.481455344293937</v>
       </c>
       <c r="H22">
         <v>1.983050847457627</v>
@@ -1765,7 +1765,7 @@
         <v>0.6679926389079232</v>
       </c>
       <c r="S22">
-        <v>0.5985903479605003</v>
+        <v>0.5953203557772127</v>
       </c>
     </row>
     <row r="23">
@@ -1787,10 +1787,10 @@
         <v>0.2815616571454121</v>
       </c>
       <c r="F23">
-        <v>119.3736232370968</v>
+        <v>139.410289585</v>
       </c>
       <c r="G23">
-        <v>0.2187675943511546</v>
+        <v>0.2234520514454821</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         <v>0.129348291469426</v>
       </c>
       <c r="S23">
-        <v>0.2177428250114373</v>
+        <v>0.2184120331677698</v>
       </c>
     </row>
     <row r="24">
@@ -1850,10 +1850,10 @@
         <v>0.322165014161533</v>
       </c>
       <c r="F24">
-        <v>80.2080049490625</v>
+        <v>93.11473346</v>
       </c>
       <c r="G24">
-        <v>0.07361194357916995</v>
+        <v>0.07640903170066567</v>
       </c>
       <c r="H24">
         <v>0.9833333333333333</v>
@@ -1885,7 +1885,7 @@
         <v>0.374455591094319</v>
       </c>
       <c r="S24">
-        <v>0.38742213348037</v>
+        <v>0.3878883148339526</v>
       </c>
     </row>
     <row r="25">
@@ -1907,10 +1907,10 @@
         <v>0.5210945463425779</v>
       </c>
       <c r="F25">
-        <v>123.441344703125</v>
+        <v>142.6759671048148</v>
       </c>
       <c r="G25">
-        <v>0.2338433874158308</v>
+        <v>0.233824431090945</v>
       </c>
       <c r="H25">
         <v>3.677966101694915</v>
@@ -1948,7 +1948,7 @@
         <v>0.5641299519016463</v>
       </c>
       <c r="S25">
-        <v>0.4649817286833527</v>
+        <v>0.4649790206369404</v>
       </c>
     </row>
     <row r="26">
@@ -1970,10 +1970,10 @@
         <v>0.4335613624583748</v>
       </c>
       <c r="F26">
-        <v>177.1940864143333</v>
+        <v>207.2343066116</v>
       </c>
       <c r="G26">
-        <v>0.4330618485285115</v>
+        <v>0.438873338272396</v>
       </c>
       <c r="H26">
         <v>1.627118644067797</v>
@@ -2011,7 +2011,7 @@
         <v>0.3160078826273875</v>
       </c>
       <c r="S26">
-        <v>0.3848268233136405</v>
+        <v>0.3856570361341954</v>
       </c>
     </row>
     <row r="27">
@@ -2033,10 +2033,10 @@
         <v>0.4941534023740833</v>
       </c>
       <c r="F27">
-        <v>168.7766671846875</v>
+        <v>196.5014849340741</v>
       </c>
       <c r="G27">
-        <v>0.4018652015838838</v>
+        <v>0.4047839646490428</v>
       </c>
       <c r="H27">
         <v>3.933333333333333</v>
@@ -2074,7 +2074,7 @@
         <v>0.5587002648975824</v>
       </c>
       <c r="S27">
-        <v>0.4767183428919147</v>
+        <v>0.4771353090440803</v>
       </c>
     </row>
     <row r="28">
@@ -2096,10 +2096,10 @@
         <v>0.8830837022171001</v>
       </c>
       <c r="F28">
-        <v>232.0746173662963</v>
+        <v>270.3988719609091</v>
       </c>
       <c r="G28">
-        <v>0.6364601231697685</v>
+        <v>0.6394953678415722</v>
       </c>
       <c r="H28">
         <v>12.86440677966102</v>
@@ -2137,7 +2137,7 @@
         <v>0.8774595492880565</v>
       </c>
       <c r="S28">
-        <v>0.6451374135252902</v>
+        <v>0.6455710199069764</v>
       </c>
     </row>
     <row r="29">
@@ -2159,10 +2159,10 @@
         <v>0.5780916197159226</v>
       </c>
       <c r="F29">
-        <v>164.713646173125</v>
+        <v>190.4956535322222</v>
       </c>
       <c r="G29">
-        <v>0.3868068293479019</v>
+        <v>0.3857083630292655</v>
       </c>
       <c r="H29">
         <v>6.135593220338983</v>
@@ -2200,7 +2200,7 @@
         <v>0.6528597475257988</v>
       </c>
       <c r="S29">
-        <v>0.4726451900413647</v>
+        <v>0.4724882662815595</v>
       </c>
     </row>
     <row r="30">
@@ -2222,10 +2222,10 @@
         <v>0.4821264930854841</v>
       </c>
       <c r="F30">
-        <v>93.236065658125</v>
+        <v>106.5558604737037</v>
       </c>
       <c r="G30">
-        <v>0.1218965542449143</v>
+        <v>0.1191004705837453</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -2263,7 +2263,7 @@
         <v>0.6124200573528666</v>
       </c>
       <c r="S30">
-        <v>0.3439699751180481</v>
+        <v>0.3435705345950239</v>
       </c>
     </row>
     <row r="31">
@@ -2285,10 +2285,10 @@
         <v>0.7210649319415701</v>
       </c>
       <c r="F31">
-        <v>144.923307941875</v>
+        <v>167.819820467037</v>
       </c>
       <c r="G31">
-        <v>0.313459859466606</v>
+        <v>0.3136858354214025</v>
       </c>
       <c r="H31">
         <v>6</v>
@@ -2326,7 +2326,7 @@
         <v>0.6400236385238157</v>
       </c>
       <c r="S31">
-        <v>0.5361884341820413</v>
+        <v>0.536220716461298</v>
       </c>
     </row>
     <row r="32">
@@ -2348,10 +2348,10 @@
         <v>0.4271450080044754</v>
       </c>
       <c r="F32">
-        <v>67.318532718125</v>
+        <v>76.97403623703704</v>
       </c>
       <c r="G32">
-        <v>0.02584096965940489</v>
+        <v>0.02514327189333068</v>
       </c>
       <c r="H32">
         <v>0.7333333333333333</v>
@@ -2389,7 +2389,7 @@
         <v>0.1791742072897486</v>
       </c>
       <c r="S32">
-        <v>0.3169935983074612</v>
+        <v>0.316893927198022</v>
       </c>
     </row>
     <row r="33">
@@ -2411,10 +2411,10 @@
         <v>0.5135956637831848</v>
       </c>
       <c r="F33">
-        <v>173.841501374375</v>
+        <v>196.8053963777778</v>
       </c>
       <c r="G33">
-        <v>0.4206364947484525</v>
+        <v>0.4057492421002207</v>
       </c>
       <c r="H33">
         <v>3.610169491525424</v>
@@ -2452,7 +2452,7 @@
         <v>0.4809445889191414</v>
       </c>
       <c r="S33">
-        <v>0.4584120797393729</v>
+        <v>0.456285329361054</v>
       </c>
     </row>
     <row r="34">
@@ -2474,10 +2474,10 @@
         <v>0.6362294846750176</v>
       </c>
       <c r="F34">
-        <v>124.1271808390625</v>
+        <v>140.1377522314815</v>
       </c>
       <c r="G34">
-        <v>0.2363852339380231</v>
+        <v>0.2257626037585675</v>
       </c>
       <c r="H34">
         <v>6.220338983050848</v>
@@ -2515,7 +2515,7 @@
         <v>0.6190463355929701</v>
       </c>
       <c r="S34">
-        <v>0.5599671240568403</v>
+        <v>0.5584496054597753</v>
       </c>
     </row>
     <row r="35">
@@ -2537,10 +2537,10 @@
         <v>0.6801308891122624</v>
       </c>
       <c r="F35">
-        <v>175.416226305</v>
+        <v>200.1776174840741</v>
       </c>
       <c r="G35">
-        <v>0.4264727417447518</v>
+        <v>0.4164600233548656</v>
       </c>
       <c r="H35">
         <v>11.2</v>
@@ -2578,7 +2578,7 @@
         <v>0.6217216854641848</v>
       </c>
       <c r="S35">
-        <v>0.5107716399908507</v>
+        <v>0.5093412516494384</v>
       </c>
     </row>
     <row r="36">
@@ -2600,10 +2600,10 @@
         <v>0.5944161584257603</v>
       </c>
       <c r="F36">
-        <v>161.3252078546875</v>
+        <v>184.1943009733333</v>
       </c>
       <c r="G36">
-        <v>0.3742485961139383</v>
+        <v>0.3656941330190682</v>
       </c>
       <c r="H36">
         <v>2</v>
@@ -2641,7 +2641,7 @@
         <v>0.4683722004833799</v>
       </c>
       <c r="S36">
-        <v>0.4369903364095117</v>
+        <v>0.4357682702531017</v>
       </c>
     </row>
     <row r="37">
@@ -2663,10 +2663,10 @@
         <v>0.5277366427817703</v>
       </c>
       <c r="F37">
-        <v>125.714529449375</v>
+        <v>144.7306987062963</v>
       </c>
       <c r="G37">
-        <v>0.2422682668276714</v>
+        <v>0.2403506285218856</v>
       </c>
       <c r="H37">
         <v>1.88135593220339</v>
@@ -2704,7 +2704,7 @@
         <v>0.4727623426593815</v>
       </c>
       <c r="S37">
-        <v>0.408662718244595</v>
+        <v>0.4083887699151971</v>
       </c>
     </row>
     <row r="38">
@@ -2726,10 +2726,10 @@
         <v>0.6956075427970684</v>
       </c>
       <c r="F38">
-        <v>151.1668673634375</v>
+        <v>174.5047560962963</v>
       </c>
       <c r="G38">
-        <v>0.3365997451772152</v>
+        <v>0.3349183943104657</v>
       </c>
       <c r="H38">
         <v>6.915254237288136</v>
@@ -2767,7 +2767,7 @@
         <v>0.7131341149161409</v>
       </c>
       <c r="S38">
-        <v>0.6261942424572879</v>
+        <v>0.6259540494763237</v>
       </c>
     </row>
     <row r="39">
@@ -2789,10 +2789,10 @@
         <v>0.8210194478581516</v>
       </c>
       <c r="F39">
-        <v>181.2209807528125</v>
+        <v>208.5559138366667</v>
       </c>
       <c r="G39">
-        <v>0.4479863280552536</v>
+        <v>0.4430710007168358</v>
       </c>
       <c r="H39">
         <v>11.22033898305085</v>
@@ -2830,7 +2830,7 @@
         <v>0.6764471899547364</v>
       </c>
       <c r="S39">
-        <v>0.6370063394134295</v>
+        <v>0.6363041497936556</v>
       </c>
     </row>
     <row r="40">
@@ -2852,10 +2852,10 @@
         <v>0.4390805957391429</v>
       </c>
       <c r="F40">
-        <v>133.0338306171875</v>
+        <v>152.0955397151852</v>
       </c>
       <c r="G40">
-        <v>0.2693950675945206</v>
+        <v>0.2637426892839051</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2893,7 +2893,7 @@
         <v>0.4996335043034948</v>
       </c>
       <c r="S40">
-        <v>0.4174890228783035</v>
+        <v>0.4166815402625013</v>
       </c>
     </row>
     <row r="41">
@@ -2915,10 +2915,10 @@
         <v>0.2968748841847817</v>
       </c>
       <c r="F41">
-        <v>108.986184225625</v>
+        <v>127.1470300633333</v>
       </c>
       <c r="G41">
-        <v>0.1802696582666082</v>
+        <v>0.1845017317406826</v>
       </c>
       <c r="H41">
         <v>1.932203389830508</v>
@@ -2956,7 +2956,7 @@
         <v>0.4603998087123266</v>
       </c>
       <c r="S41">
-        <v>0.3265993546361881</v>
+        <v>0.3272039365610559</v>
       </c>
     </row>
     <row r="42">
@@ -2978,10 +2978,10 @@
         <v>0.5122807381847606</v>
       </c>
       <c r="F42">
-        <v>119.8886665934375</v>
+        <v>137.3126007962963</v>
       </c>
       <c r="G42">
-        <v>0.2206764485154273</v>
+        <v>0.2167894142553594</v>
       </c>
       <c r="H42">
         <v>3.491525423728814</v>
@@ -3019,7 +3019,7 @@
         <v>0.4549699493610279</v>
       </c>
       <c r="S42">
-        <v>0.4827249565776124</v>
+        <v>0.4821696659690312</v>
       </c>
     </row>
     <row r="43">
@@ -3041,10 +3041,10 @@
         <v>0.5475455574012923</v>
       </c>
       <c r="F43">
-        <v>155.2948253259375</v>
+        <v>177.0335387388889</v>
       </c>
       <c r="G43">
-        <v>0.3518987868009025</v>
+        <v>0.3429502631801497</v>
       </c>
       <c r="H43">
         <v>6.35593220338983</v>
@@ -3076,7 +3076,7 @@
         <v>0.7769677965397922</v>
       </c>
       <c r="S43">
-        <v>0.4976488390422292</v>
+        <v>0.4961574184387704</v>
       </c>
     </row>
     <row r="44">
@@ -3098,10 +3098,10 @@
         <v>0.6505704254947626</v>
       </c>
       <c r="F44">
-        <v>112.6675989174194</v>
+        <v>128.5063440026923</v>
       </c>
       <c r="G44">
-        <v>0.1939137208068444</v>
+        <v>0.188819157497161</v>
       </c>
       <c r="H44">
         <v>5.491525423728813</v>
@@ -3139,7 +3139,7 @@
         <v>0.7131434838109965</v>
       </c>
       <c r="S44">
-        <v>0.5514051765935161</v>
+        <v>0.5506773818349899</v>
       </c>
     </row>
     <row r="45">
@@ -3161,10 +3161,10 @@
         <v>0.6028230402012745</v>
       </c>
       <c r="F45">
-        <v>202.9518392865625</v>
+        <v>233.8890457351852</v>
       </c>
       <c r="G45">
-        <v>0.5285252560788698</v>
+        <v>0.5235335877498996</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -3196,7 +3196,7 @@
         <v>0.5477830485890927</v>
       </c>
       <c r="S45">
-        <v>0.6561743309314412</v>
+        <v>0.6553423862099461</v>
       </c>
     </row>
     <row r="46">
@@ -3218,10 +3218,10 @@
         <v>0.5537858828691359</v>
       </c>
       <c r="F46">
-        <v>107.9302736590323</v>
+        <v>113.04228152</v>
       </c>
       <c r="G46">
-        <v>0.1763562415467805</v>
+        <v>0.1397025114234424</v>
       </c>
       <c r="H46">
         <v>6.203389830508475</v>
@@ -3259,7 +3259,7 @@
         <v>0.4893672453337708</v>
       </c>
       <c r="S46">
-        <v>0.5605146775977388</v>
+        <v>0.5552784304372619</v>
       </c>
     </row>
     <row r="47">
@@ -3281,10 +3281,10 @@
         <v>0.4184983987891018</v>
       </c>
       <c r="F47">
-        <v>115.11182788125</v>
+        <v>131.2954112092593</v>
       </c>
       <c r="G47">
-        <v>0.2029725244562933</v>
+        <v>0.1976777369948891</v>
       </c>
       <c r="H47">
         <v>1.864406779661017</v>
@@ -3316,7 +3316,7 @@
         <v>0.3514288875039369</v>
       </c>
       <c r="S47">
-        <v>0.4000617457049202</v>
+        <v>0.3991792811280195</v>
       </c>
     </row>
     <row r="48">
@@ -3338,10 +3338,10 @@
         <v>0.6881147050334921</v>
       </c>
       <c r="F48">
-        <v>254.4268867953125</v>
+        <v>288.1408273914815</v>
       </c>
       <c r="G48">
-        <v>0.7193021248289343</v>
+        <v>0.6958470119528418</v>
       </c>
       <c r="H48">
         <v>11.5</v>
@@ -3373,7 +3373,7 @@
         <v>0.8875126067532404</v>
       </c>
       <c r="S48">
-        <v>0.7069031037108603</v>
+        <v>0.7029939182315115</v>
       </c>
     </row>
     <row r="49">
@@ -3395,10 +3395,10 @@
         <v>0.5647279988701689</v>
       </c>
       <c r="F49">
-        <v>231.912202086875</v>
+        <v>260.7046894659259</v>
       </c>
       <c r="G49">
-        <v>0.635858179510758</v>
+        <v>0.6087048992235723</v>
       </c>
       <c r="H49">
         <v>3.254237288135593</v>
@@ -3436,7 +3436,7 @@
         <v>0.9804228446434465</v>
       </c>
       <c r="S49">
-        <v>0.5218447535011101</v>
+        <v>0.5179657134600837</v>
       </c>
     </row>
     <row r="50">
@@ -3458,10 +3458,10 @@
         <v>0.3551590788297286</v>
       </c>
       <c r="F50">
-        <v>115.4052684690625</v>
+        <v>134.3678353466667</v>
       </c>
       <c r="G50">
-        <v>0.2040600742346113</v>
+        <v>0.2074363091109994</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>0.4722015136365176</v>
       </c>
       <c r="S50">
-        <v>0.3708611723194072</v>
+        <v>0.3713434915874627</v>
       </c>
     </row>
     <row r="51">
@@ -3521,10 +3521,10 @@
         <v>0.6509749520708715</v>
       </c>
       <c r="F51">
-        <v>268.7253422890625</v>
+        <v>300.0112017037037</v>
       </c>
       <c r="G51">
-        <v>0.7722950738222517</v>
+        <v>0.7335494575106325</v>
       </c>
       <c r="H51">
         <v>3.033898305084746</v>
@@ -3556,7 +3556,7 @@
         <v>0.8661985237387249</v>
       </c>
       <c r="S51">
-        <v>0.6420613476676871</v>
+        <v>0.6356037449490839</v>
       </c>
     </row>
     <row r="52">
@@ -3578,10 +3578,10 @@
         <v>0.5761905996751149</v>
       </c>
       <c r="F52">
-        <v>102.683986036875</v>
+        <v>111.8974685614815</v>
       </c>
       <c r="G52">
-        <v>0.1569124455027409</v>
+        <v>0.1360663793936414</v>
       </c>
       <c r="H52">
         <v>10.33898305084746</v>
@@ -3619,7 +3619,7 @@
         <v>0.6543190589226516</v>
       </c>
       <c r="S52">
-        <v>0.5019408141296289</v>
+        <v>0.4989628046854718</v>
       </c>
     </row>
     <row r="53">
@@ -3641,10 +3641,10 @@
         <v>0.3200677323665221</v>
       </c>
       <c r="F53">
-        <v>89.29260579419355</v>
+        <v>103.3193545726923</v>
       </c>
       <c r="G53">
-        <v>0.107281299645013</v>
+        <v>0.1088207452506773</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -3682,7 +3682,7 @@
         <v>0.2300217547418851</v>
       </c>
       <c r="S53">
-        <v>0.338697663862537</v>
+        <v>0.3389175846633461</v>
       </c>
     </row>
     <row r="54">
@@ -3704,10 +3704,10 @@
         <v>0.4395619186599191</v>
       </c>
       <c r="F54">
-        <v>118.3972807875</v>
+        <v>136.8585653651852</v>
       </c>
       <c r="G54">
-        <v>0.2151490730602286</v>
+        <v>0.215347315996912</v>
       </c>
       <c r="H54">
         <v>1.983050847457627</v>
@@ -3745,7 +3745,7 @@
         <v>0.6549505545122504</v>
       </c>
       <c r="S54">
-        <v>0.3695520298920587</v>
+        <v>0.3695803503115849</v>
       </c>
     </row>
     <row r="55">
@@ -3767,10 +3767,10 @@
         <v>0.5408875110612112</v>
       </c>
       <c r="F55">
-        <v>151.9766271153571</v>
+        <v>181.0067190926087</v>
       </c>
       <c r="G55">
-        <v>0.3396008775197312</v>
+        <v>0.3555697991810629</v>
       </c>
       <c r="H55">
         <v>5.186440677966102</v>
@@ -3808,7 +3808,7 @@
         <v>0.6025622161214722</v>
       </c>
       <c r="S55">
-        <v>0.6394172148449796</v>
+        <v>0.641698489368027</v>
       </c>
     </row>
     <row r="56">
@@ -3830,10 +3830,10 @@
         <v>0.5493283902064392</v>
       </c>
       <c r="F56">
-        <v>143.5188982909375</v>
+        <v>167.4246362551852</v>
       </c>
       <c r="G56">
-        <v>0.3082548351176205</v>
+        <v>0.3124306592289128</v>
       </c>
       <c r="H56">
         <v>1.983050847457627</v>
@@ -3871,7 +3871,7 @@
         <v>0.4681075174785018</v>
       </c>
       <c r="S56">
-        <v>0.5292033314007514</v>
+        <v>0.5297998777023646</v>
       </c>
     </row>
     <row r="57">
@@ -3893,10 +3893,10 @@
         <v>0.7718758408691314</v>
       </c>
       <c r="F57">
-        <v>183.8040500878125</v>
+        <v>209.0077917292593</v>
       </c>
       <c r="G57">
-        <v>0.4575597020169162</v>
+        <v>0.4445062462445779</v>
       </c>
       <c r="H57">
         <v>12.3</v>
@@ -3934,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="S57">
-        <v>0.7221078720394447</v>
+        <v>0.7202430926433964</v>
       </c>
     </row>
     <row r="58">
@@ -3956,10 +3956,10 @@
         <v>0.7184684060747184</v>
       </c>
       <c r="F58">
-        <v>117.7899405009375</v>
+        <v>137.6317868540741</v>
       </c>
       <c r="G58">
-        <v>0.2128981479276881</v>
+        <v>0.2178032066303633</v>
       </c>
       <c r="H58">
         <v>3.416666666666667</v>
@@ -3997,7 +3997,7 @@
         <v>0.7193375451729008</v>
       </c>
       <c r="S58">
-        <v>0.592461695362043</v>
+        <v>0.5931624180338537</v>
       </c>
     </row>
     <row r="59">
@@ -4019,10 +4019,10 @@
         <v>0.5900632347324082</v>
       </c>
       <c r="F59">
-        <v>134.8362436684375</v>
+        <v>155.1610474259259</v>
       </c>
       <c r="G59">
-        <v>0.2760751725143514</v>
+        <v>0.2734792935839217</v>
       </c>
       <c r="H59">
         <v>11.28813559322034</v>
@@ -4060,7 +4060,7 @@
         <v>0.8052804788124337</v>
       </c>
       <c r="S59">
-        <v>0.6274211676974397</v>
+        <v>0.6270503278502354</v>
       </c>
     </row>
     <row r="60">
@@ -4082,10 +4082,10 @@
         <v>0.6853782943919974</v>
       </c>
       <c r="F60">
-        <v>200.0871802265625</v>
+        <v>229.7353989774074</v>
       </c>
       <c r="G60">
-        <v>0.5179082540176206</v>
+        <v>0.5103408579646083</v>
       </c>
       <c r="H60">
         <v>13</v>
@@ -4123,7 +4123,7 @@
         <v>0.8439022288162242</v>
       </c>
       <c r="S60">
-        <v>0.5982398362383838</v>
+        <v>0.597158779659382</v>
       </c>
     </row>
     <row r="61">
@@ -4145,10 +4145,10 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>146.71501500875</v>
+        <v>169.0143546955556</v>
       </c>
       <c r="G61">
-        <v>0.3201002858572309</v>
+        <v>0.3174798911548654</v>
       </c>
       <c r="H61">
         <v>2.95</v>
@@ -4186,7 +4186,7 @@
         <v>0.6007583638026363</v>
       </c>
       <c r="S61">
-        <v>0.5029674549310557</v>
+        <v>0.5025931128307177</v>
       </c>
     </row>
     <row r="62">
@@ -4208,10 +4208,10 @@
         <v>0.4822341256760957</v>
       </c>
       <c r="F62">
-        <v>190.33094006125</v>
+        <v>213.8371436925926</v>
       </c>
       <c r="G62">
-        <v>0.4817496676812886</v>
+        <v>0.4598451373939084</v>
       </c>
       <c r="H62">
         <v>7.689655172413793</v>
@@ -4249,7 +4249,7 @@
         <v>0.6577200663611824</v>
       </c>
       <c r="S62">
-        <v>0.4791251727646829</v>
+        <v>0.4759959541522</v>
       </c>
     </row>
     <row r="63">
@@ -4271,10 +4271,10 @@
         <v>0.3671409097550509</v>
       </c>
       <c r="F63">
-        <v>68.9591740921875</v>
+        <v>79.62046578629629</v>
       </c>
       <c r="G63">
-        <v>0.03192151623942003</v>
+        <v>0.0335488085157724</v>
       </c>
       <c r="H63">
         <v>2.694915254237288</v>
@@ -4312,7 +4312,7 @@
         <v>0.271727309955794</v>
       </c>
       <c r="S63">
-        <v>0.413397701812141</v>
+        <v>0.4136301721373342</v>
       </c>
     </row>
     <row r="64">
@@ -4334,10 +4334,10 @@
         <v>0.5977681191734737</v>
       </c>
       <c r="F64">
-        <v>154.55160473125</v>
+        <v>178.3186385296296</v>
       </c>
       <c r="G64">
-        <v>0.3491442619445448</v>
+        <v>0.3470319714416021</v>
       </c>
       <c r="H64">
         <v>6.677966101694915</v>
@@ -4375,7 +4375,7 @@
         <v>0.578059215922415</v>
       </c>
       <c r="S64">
-        <v>0.4295432909397365</v>
+        <v>0.4292415351536018</v>
       </c>
     </row>
     <row r="65">
@@ -4397,10 +4397,10 @@
         <v>0.5363960821200183</v>
       </c>
       <c r="F65">
-        <v>73.60762752531249</v>
+        <v>85.41424579185185</v>
       </c>
       <c r="G65">
-        <v>0.04914961865838969</v>
+        <v>0.05195089673032519</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -4438,7 +4438,7 @@
         <v>0.2024667529990534</v>
       </c>
       <c r="S65">
-        <v>0.4907230701504024</v>
+        <v>0.4911232527321074</v>
       </c>
     </row>
     <row r="66">
@@ -4460,7 +4460,7 @@
         <v>0.7780287209137213</v>
       </c>
       <c r="F66">
-        <v>330.164247171875</v>
+        <v>383.901454132963</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -4523,10 +4523,10 @@
         <v>0.4488973724545661</v>
       </c>
       <c r="F67">
-        <v>76.5980043496875</v>
+        <v>89.07657681111111</v>
       </c>
       <c r="G67">
-        <v>0.06023255601439794</v>
+        <v>0.06358311929015284</v>
       </c>
       <c r="H67">
         <v>3.779661016949153</v>
@@ -4564,7 +4564,7 @@
         <v>0.3929600629229978</v>
       </c>
       <c r="S67">
-        <v>0.4601836628180562</v>
+        <v>0.4606623147145926</v>
       </c>
     </row>
     <row r="68">
@@ -4586,10 +4586,10 @@
         <v>0.5051754831240297</v>
       </c>
       <c r="F68">
-        <v>162.0354838759375</v>
+        <v>190.2813164281481</v>
       </c>
       <c r="G68">
-        <v>0.3768810217617106</v>
+        <v>0.385027589804697</v>
       </c>
       <c r="H68">
         <v>0.9833333333333333</v>
@@ -4621,7 +4621,7 @@
         <v>0.3671890722886557</v>
       </c>
       <c r="S68">
-        <v>0.4008122997475896</v>
+        <v>0.4021700610880873</v>
       </c>
     </row>
     <row r="69">
@@ -4643,10 +4643,10 @@
         <v>0.3379120036940255</v>
       </c>
       <c r="F69">
-        <v>88.9824012521875</v>
+        <v>103.6936781292593</v>
       </c>
       <c r="G69">
-        <v>0.1061316192841371</v>
+        <v>0.1100096642469328</v>
       </c>
       <c r="H69">
         <v>0.9833333333333333</v>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="S69">
-        <v>0.3102788828933085</v>
+        <v>0.310832889316565</v>
       </c>
     </row>
     <row r="70">
@@ -4706,10 +4706,10 @@
         <v>0.5803707375306559</v>
       </c>
       <c r="F70">
-        <v>102.4966450978125</v>
+        <v>117.7034853077778</v>
       </c>
       <c r="G70">
-        <v>0.1562181223408834</v>
+        <v>0.1545073336994773</v>
       </c>
       <c r="H70">
         <v>2</v>
@@ -4747,7 +4747,7 @@
         <v>0.3555699805594751</v>
       </c>
       <c r="S70">
-        <v>0.4007582644216341</v>
+        <v>0.4005138660442904</v>
       </c>
     </row>
     <row r="71">
@@ -4769,7 +4769,7 @@
         <v>0.53293275740635</v>
       </c>
       <c r="F71">
-        <v>60.3461720246875</v>
+        <v>69.05783758222222</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -4832,10 +4832,10 @@
         <v>0.6040955263600328</v>
       </c>
       <c r="F72">
-        <v>135.46246887375</v>
+        <v>157.4820688440741</v>
       </c>
       <c r="G72">
-        <v>0.2783960889502532</v>
+        <v>0.2808512754064405</v>
       </c>
       <c r="H72">
         <v>6.35593220338983</v>
@@ -4873,7 +4873,7 @@
         <v>0.3793248757832806</v>
       </c>
       <c r="S72">
-        <v>0.4199460195376425</v>
+        <v>0.420296760459955</v>
       </c>
     </row>
     <row r="73">
@@ -4895,10 +4895,10 @@
         <v>0.38750825476394</v>
       </c>
       <c r="F73">
-        <v>104.8937559309375</v>
+        <v>120.6028010485185</v>
       </c>
       <c r="G73">
-        <v>0.1651022967306731</v>
+        <v>0.1637160823871721</v>
       </c>
       <c r="H73">
         <v>2</v>
@@ -4936,7 +4936,7 @@
         <v>0.197913378030515</v>
       </c>
       <c r="S73">
-        <v>0.436978979551457</v>
+        <v>0.4367809489309569</v>
       </c>
     </row>
     <row r="74">
@@ -4958,10 +4958,10 @@
         <v>0.7138177781831853</v>
       </c>
       <c r="F74">
-        <v>151.39790363125</v>
+        <v>174.2625411192593</v>
       </c>
       <c r="G74">
-        <v>0.337456012006954</v>
+        <v>0.334149075943174</v>
       </c>
       <c r="H74">
         <v>10.48333333333333</v>
@@ -4999,7 +4999,7 @@
         <v>0.5299726939760873</v>
       </c>
       <c r="S74">
-        <v>0.5770790759279339</v>
+        <v>0.5766066564902511</v>
       </c>
     </row>
     <row r="75">
@@ -5021,10 +5021,10 @@
         <v>0.6468651507261209</v>
       </c>
       <c r="F75">
-        <v>152.0578600525</v>
+        <v>174.0390576866667</v>
       </c>
       <c r="G75">
-        <v>0.3399019431066032</v>
+        <v>0.3334392523328339</v>
       </c>
       <c r="H75">
         <v>9.85</v>
@@ -5062,7 +5062,7 @@
         <v>0.410284121339076</v>
       </c>
       <c r="S75">
-        <v>0.5471463558572585</v>
+        <v>0.5462231143181486</v>
       </c>
     </row>
     <row r="76">
@@ -5084,10 +5084,10 @@
         <v>0.4296548459987961</v>
       </c>
       <c r="F76">
-        <v>61.79041457875</v>
+        <v>71.08605455481481</v>
       </c>
       <c r="G76">
-        <v>0.005352653091438228</v>
+        <v>0.006441982196789171</v>
       </c>
       <c r="H76">
         <v>1.9</v>
@@ -5125,7 +5125,7 @@
         <v>0.02939815742536144</v>
       </c>
       <c r="S76">
-        <v>0.2863759542326691</v>
+        <v>0.2865315726762906</v>
       </c>
     </row>
     <row r="77">
@@ -5147,10 +5147,10 @@
         <v>0.4584096699584418</v>
       </c>
       <c r="F77">
-        <v>114.1203750196875</v>
+        <v>127.5183824903704</v>
       </c>
       <c r="G77">
-        <v>0.1992980009425456</v>
+        <v>0.1856812138947291</v>
       </c>
       <c r="H77">
         <v>2.833333333333333</v>
@@ -5188,7 +5188,7 @@
         <v>0.6678280125044722</v>
       </c>
       <c r="S77">
-        <v>0.5230042136491669</v>
+        <v>0.5210589583566217</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         <v>214.3728571428572</v>
       </c>
       <c r="G78">
-        <v>0.5708538430353383</v>
+        <v>0.4615466597437452</v>
       </c>
       <c r="H78">
         <v>0.9523809523809523</v>
@@ -5227,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="S78">
-        <v>0.617095948842703</v>
+        <v>0.5806602210788387</v>
       </c>
     </row>
     <row r="79">
